--- a/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3200248077715508</v>
+        <v>0.3200248077715527</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1725035862797113</v>
+        <v>0.1725035862797109</v>
       </c>
       <c r="D2" t="n">
-        <v>0.646200933207539</v>
+        <v>0.646200933207538</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1725035862797113</v>
+        <v>0.1725035862797109</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1725035862797113</v>
+        <v>0.1725035862797109</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4239741791252266</v>
+        <v>0.4239741791252252</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9202012239982733</v>
+        <v>0.9202012239982706</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1725035862797113</v>
+        <v>0.1725035862797109</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3995039208146756</v>
+        <v>0.3995039208146738</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1795558205968492</v>
+        <v>0.1795558205968481</v>
       </c>
       <c r="L2" t="n">
-        <v>1.390530346894879</v>
+        <v>0.3443196001506525</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007470873836679293</v>
+        <v>0.007470873836679305</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007685811386972551</v>
+        <v>0.007685811386972575</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007685811386972549</v>
+        <v>0.007685811386972566</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008073727342082589</v>
+        <v>0.008073727342082542</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007944096396387551</v>
+        <v>0.007944096396387556</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008097900671048829</v>
+        <v>0.008097900671048821</v>
       </c>
     </row>
     <row r="4">
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02226526789362538</v>
+        <v>0.01290651139053427</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01233290893884339</v>
+        <v>0.01233290893884333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01355884042104224</v>
+        <v>0.01355876032107857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01179987543123613</v>
+        <v>0.01179987543123616</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01273679224207374</v>
+        <v>0.01273679224207376</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02224109456465915</v>
+        <v>0.02224109456465918</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0228488880747354</v>
+        <v>0.02284888807473532</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02211146361896413</v>
+        <v>0.01275270711587302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01342832128782565</v>
+        <v>0.01342832128782584</v>
       </c>
       <c r="K4" t="n">
         <v>0.01262172279810776</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01424437823063959</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="C5" t="n">
         <v>0.01409057395597836</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01424359705562576</v>
+        <v>0.01424359705562577</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01408095937872989</v>
+        <v>0.01408095937872991</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01408095937872989</v>
+        <v>0.01408095937872991</v>
       </c>
       <c r="G5" t="n">
         <v>0.01422020490167338</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01424437823063959</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="I5" t="n">
         <v>0.01409057395597836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01424437823063959</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01424437823063959</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01424437823063959</v>
+        <v>0.01424437823063958</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02254152165706287</v>
+        <v>0.02254152165706281</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03391187091874991</v>
+        <v>0.03391187091875002</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03646246913400734</v>
+        <v>0.03646246913400743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03075892031486317</v>
+        <v>0.03075892031486318</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02274793435741453</v>
+        <v>0.02274793435741462</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0340474534056681</v>
+        <v>0.03404745340566802</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03407162673463462</v>
+        <v>0.03407162673463501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03391782245997311</v>
+        <v>0.03391782245997296</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0340738927290721</v>
+        <v>0.03407389272907212</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02232734403580608</v>
+        <v>0.02232734403580607</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04611578561840537</v>
+        <v>0.04611578561840515</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03831753556804569</v>
+        <v>0.0383175355680457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04754518483410005</v>
+        <v>0.04754518483410006</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04769899155617487</v>
+        <v>0.04769899155617485</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05837116993258099</v>
+        <v>0.05837116993258098</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04754517236932496</v>
+        <v>0.0475451723693248</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0476748157797951</v>
+        <v>0.04767481577979515</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04769898910876121</v>
+        <v>0.04769898910876132</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04754518483410005</v>
+        <v>0.04754518483410006</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04769898910876121</v>
+        <v>0.04769898910876132</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03588606388314975</v>
+        <v>0.04226333911283266</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04769898910876121</v>
+        <v>0.04769898910876132</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01240184846061401</v>
+        <v>0.0124018484606143</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01592179478394065</v>
+        <v>0.01592179478394064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005601250150773664</v>
+        <v>0.005601250150773655</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01592179478394065</v>
+        <v>0.01592179478394064</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01592179478394065</v>
+        <v>0.01592179478394064</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01053026178132808</v>
+        <v>0.0105302617813281</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001956564190251746</v>
+        <v>0.001956564190251733</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01592179478394065</v>
+        <v>0.01592179478394064</v>
       </c>
       <c r="J8" t="n">
         <v>0.01134161377967443</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561093601513002</v>
+        <v>0.01561093601513003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01281113818404145</v>
+        <v>0.01281113818404144</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01603646216243222</v>
+        <v>0.01603646216243223</v>
       </c>
       <c r="C9" t="n">
         <v>0.01759329644133611</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01326698429419801</v>
+        <v>0.01326698429419802</v>
       </c>
       <c r="E9" t="n">
         <v>0.01759329644133611</v>
@@ -810,22 +810,22 @@
         <v>0.01759329644133611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01524896978316085</v>
+        <v>0.01524896978316087</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01179827847075926</v>
+        <v>0.01179827847075925</v>
       </c>
       <c r="I9" t="n">
         <v>0.01759329644133611</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01560765829087673</v>
+        <v>0.01560765829087672</v>
       </c>
       <c r="K9" t="n">
         <v>0.01734369647960354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01620798049566415</v>
+        <v>0.01620798049566416</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03171765838396703</v>
+        <v>0.03171765838396694</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07383882030974864</v>
+        <v>0.07383882030974856</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06120226852768291</v>
+        <v>0.06120226852768303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07383882030974864</v>
+        <v>0.07383882030974856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07383882030974864</v>
+        <v>0.07383882030974856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08995692349474428</v>
+        <v>0.08995692349474337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06651331966262709</v>
+        <v>0.06651331966262701</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07383882030974864</v>
+        <v>0.07383882030974856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1220467140547725</v>
+        <v>0.1220467140547726</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05188621860173541</v>
+        <v>0.0518862186017356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05498595511611996</v>
+        <v>0.03961091659524843</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005789862899941032</v>
+        <v>0.005789862899941019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005944703782980227</v>
+        <v>0.005944703782980197</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005944703782980227</v>
+        <v>0.0059447037829802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006317830237695916</v>
+        <v>0.006317830237695906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006213388540333796</v>
+        <v>0.006213388540333771</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006337093769356495</v>
+        <v>0.00633709376935649</v>
       </c>
     </row>
     <row r="4">
@@ -994,34 +994,34 @@
         <v>0.01599675171545213</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009718103612711955</v>
+        <v>0.009718103612711875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009894632212496358</v>
+        <v>0.01605165463394411</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009276655793716494</v>
+        <v>0.009276655793716474</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009822441168807683</v>
+        <v>0.009822441168807667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01597748818379153</v>
+        <v>0.0099311702327633</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01634702124659337</v>
+        <v>0.01634702124659335</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009826728535401183</v>
+        <v>0.009826728535401159</v>
       </c>
       <c r="J4" t="n">
         <v>0.01607284406079593</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009927643566777396</v>
+        <v>0.009927643566777538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00994942257416578</v>
+        <v>0.009949422574165773</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01016978460595654</v>
+        <v>0.01016978460595652</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01004607937693385</v>
+        <v>0.01004607937693381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01016912436841818</v>
+        <v>0.01016912436841816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003730854149149</v>
+        <v>0.01003730854149145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003730854149149</v>
+        <v>0.01003730854149145</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01015052107429596</v>
+        <v>0.01015052107429594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01016978460595654</v>
+        <v>0.01016978460595652</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01004607937693385</v>
+        <v>0.01004607937693381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01016978460595654</v>
+        <v>0.01016978460595652</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01016978460595654</v>
+        <v>0.01016978460595652</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01016978460595654</v>
+        <v>0.01016978460595652</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01604999951170844</v>
+        <v>0.01604999951170839</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02381128813943062</v>
+        <v>0.02381128813943052</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02557725918634794</v>
+        <v>0.02557725918634789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0216536379315043</v>
+        <v>0.0216536379315042</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01617158868063238</v>
+        <v>0.01617158868063232</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02392174378189804</v>
+        <v>0.02392174378189796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02394100731355839</v>
+        <v>0.02394100731355833</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02381730208453592</v>
+        <v>0.02381730208453587</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02394255812184687</v>
+        <v>0.02394255812184683</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01590341999060052</v>
+        <v>0.01590341999060047</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03218382479716105</v>
+        <v>0.03218382479716096</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0192820696812558</v>
+        <v>0.01928206968125573</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02348679527104203</v>
+        <v>0.02348679527104197</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02361050431112983</v>
+        <v>0.02361050431112975</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0284817150366562</v>
+        <v>0.02848171503665613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02348679441755748</v>
+        <v>0.02348679441755741</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02359123696840414</v>
+        <v>0.02359123696840407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02361050050006474</v>
+        <v>0.0236105005000647</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02348679527104203</v>
+        <v>0.02348679527104197</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02361050050006474</v>
+        <v>0.0236105005000647</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02110259228750662</v>
+        <v>0.02110259228750653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02361050050006474</v>
+        <v>0.0236105005000647</v>
       </c>
     </row>
     <row r="8">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01635101157193904</v>
+        <v>0.01635101157193903</v>
       </c>
       <c r="C8" t="n">
         <v>0.01473413886682382</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01556213059460179</v>
+        <v>0.01556213059460178</v>
       </c>
       <c r="E8" t="n">
         <v>0.01473413886682382</v>
@@ -1166,7 +1166,7 @@
         <v>0.01473413886682382</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01486816337811963</v>
+        <v>0.01486816337811962</v>
       </c>
       <c r="H8" t="n">
         <v>0.01562506165035029</v>
@@ -1181,7 +1181,7 @@
         <v>0.01577357398897924</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0158695173890057</v>
+        <v>0.01628248934125439</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1197,7 @@
         <v>0.01536065578959292</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01598953833300592</v>
+        <v>0.01598953833300589</v>
       </c>
       <c r="E9" t="n">
         <v>0.01536065578959292</v>
@@ -1209,19 +1209,19 @@
         <v>0.01570091960004305</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01601638261525833</v>
+        <v>0.01601638261525834</v>
       </c>
       <c r="I9" t="n">
         <v>0.01536065578959292</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01546718223961136</v>
+        <v>0.01546718223961135</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01607568376373346</v>
+        <v>0.01607568376373348</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01611551754937153</v>
+        <v>0.01611551754937152</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06932163909801374</v>
+        <v>0.069321639098014</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1056636416547754</v>
+        <v>0.1056636416547756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1853413815752256</v>
+        <v>0.1853413815752255</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09129560488911338</v>
+        <v>0.0912956048891136</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09129560488911338</v>
+        <v>0.0912956048891136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1677645278485818</v>
+        <v>0.1677645278485816</v>
       </c>
       <c r="H2" t="n">
-        <v>0.400958677990027</v>
+        <v>0.4009586779900271</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09129560488911338</v>
+        <v>0.0912956048891136</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3184141441699986</v>
+        <v>0.318414144169999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08425015759922527</v>
+        <v>0.0842501575992254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.27559779863545</v>
+        <v>0.2755977986354499</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006443548947301245</v>
+        <v>0.006443548947301356</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005548624677623856</v>
+        <v>0.00554862467762386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006443548947301245</v>
+        <v>0.006443548947301359</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006056539126451204</v>
+        <v>0.006056539126451183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006056539126451206</v>
+        <v>0.006056539126451184</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006419338588373682</v>
+        <v>0.006419338588373675</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006443548947301245</v>
+        <v>0.006443548947301359</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006287756124814372</v>
+        <v>0.006287756124814337</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006443548947301253</v>
+        <v>0.006443548947301359</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006443548947301245</v>
+        <v>0.006443548947301359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006443548947301245</v>
+        <v>0.006443548947301359</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01705216493481316</v>
+        <v>0.01015982706784131</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009906801803048034</v>
+        <v>0.009906801803048019</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01026157793173457</v>
+        <v>0.01026151495858555</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009353998697936577</v>
+        <v>0.009353998697936581</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009991520519516975</v>
+        <v>0.009991520519516982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01702795457588558</v>
+        <v>0.01702795457588554</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01767201654512469</v>
+        <v>0.01767201654512473</v>
       </c>
       <c r="I4" t="n">
         <v>0.0168963721123262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01711872710094948</v>
+        <v>0.01711872710094958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009992369460111615</v>
+        <v>0.009992369460111538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01019802931563757</v>
+        <v>0.01019802931563762</v>
       </c>
     </row>
     <row r="5">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01108280400470986</v>
+        <v>0.01108280400470998</v>
       </c>
       <c r="C5" t="n">
         <v>0.01106944484616778</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01108215876851223</v>
+        <v>0.0110821587685123</v>
       </c>
       <c r="E5" t="n">
         <v>0.01092773090313197</v>
@@ -1442,22 +1442,22 @@
         <v>0.01092773090313197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01105859364578225</v>
+        <v>0.01105859364578227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01108280400470986</v>
+        <v>0.01108280400470998</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01092701118222295</v>
+        <v>0.01092701118222294</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01108280400470986</v>
+        <v>0.01108280400470998</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01108280400470986</v>
+        <v>0.01108280400470998</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01108280400470986</v>
+        <v>0.01108280400470998</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0178261530401139</v>
+        <v>0.01782615304011395</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02702522554883869</v>
+        <v>0.02702522554889991</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02894487379351915</v>
+        <v>0.02894487379351912</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02436367348920618</v>
+        <v>0.02436367348920614</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01796309014640702</v>
+        <v>0.017963090146407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02701108730493796</v>
+        <v>0.02701108730493802</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02703529766388028</v>
+        <v>0.02703529766388021</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02687950484137868</v>
+        <v>0.02687950484137865</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02703710752303074</v>
+        <v>0.02703710752303072</v>
       </c>
       <c r="K6" t="n">
         <v>0.01765508845085932</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03665501927809693</v>
+        <v>0.03665501927809683</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02378384936160436</v>
+        <v>0.02378384936160443</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02942643195259486</v>
+        <v>0.02942643195259484</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02943979348168595</v>
+        <v>0.02943979348168604</v>
       </c>
       <c r="E7" t="n">
         <v>0.03581083117551995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02928399340090546</v>
+        <v>0.02928399340090545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02941558075220952</v>
+        <v>0.02941558075220939</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02943979111113709</v>
+        <v>0.02943979111113706</v>
       </c>
       <c r="I7" t="n">
         <v>0.02928399828865007</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02943979111113709</v>
+        <v>0.02943979111113706</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02231795025204907</v>
+        <v>0.02616271724590456</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02943979111113709</v>
+        <v>0.02943979111113706</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03390945247101707</v>
+        <v>0.03390945247101711</v>
       </c>
       <c r="C8" t="n">
         <v>0.01058904246727309</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01498340745328794</v>
+        <v>0.01498340745328789</v>
       </c>
       <c r="E8" t="n">
         <v>0.01365445537663141</v>
@@ -1562,22 +1562,22 @@
         <v>0.01365445537663141</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225089245784049</v>
+        <v>0.01225089245784048</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01108058176715214</v>
+        <v>0.01108058176715215</v>
       </c>
       <c r="I8" t="n">
         <v>0.01365445537663141</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01374784033338295</v>
+        <v>0.0137478403333829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0190819936334701</v>
+        <v>0.01908199363347011</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01512965722338237</v>
+        <v>0.01512965722338236</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03407704643693234</v>
+        <v>0.03407704643693238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01156402845446724</v>
+        <v>0.01156402845446723</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01698828865164176</v>
+        <v>0.01698828865164179</v>
       </c>
       <c r="E9" t="n">
         <v>0.01441527643810384</v>
@@ -1605,16 +1605,16 @@
         <v>0.01400168392118263</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01540606337088971</v>
+        <v>0.01540606337088974</v>
       </c>
       <c r="I9" t="n">
         <v>0.01441527643810384</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01733782857452563</v>
+        <v>0.01733782857452567</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01967013305939987</v>
+        <v>0.0196701330593999</v>
       </c>
       <c r="L9" t="n">
         <v>0.0178510731600291</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03566263228073666</v>
+        <v>0.03566263228073641</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07282172610564921</v>
+        <v>0.07282172610564898</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1279726206456742</v>
+        <v>0.127972620645674</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05700351401274989</v>
+        <v>0.05700351401274972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05700351401274989</v>
+        <v>0.05700351401274972</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1026380547335816</v>
+        <v>0.1026380547335806</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2031333632804173</v>
+        <v>0.203133363280417</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05700351401274989</v>
+        <v>0.05700351401274972</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2046314211194553</v>
+        <v>0.2046314211194552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04265089424436978</v>
+        <v>0.04265089424436948</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09325557312266927</v>
+        <v>0.09325557312266905</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126357</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005366565638422485</v>
+        <v>0.005366565638422487</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126357</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006369052987261421</v>
+        <v>0.006369052987261397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006369052987261419</v>
+        <v>0.006369052987261405</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006120303489705652</v>
+        <v>0.006120303489705606</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126357</v>
       </c>
       <c r="I3" t="n">
         <v>0.006001591968932133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126356</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006142162204126562</v>
+        <v>0.006142162204126357</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01611586754294772</v>
+        <v>0.01611586754294735</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009590466250090669</v>
+        <v>0.009590466250090492</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009878450288955756</v>
+        <v>0.01617797826330646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009139822477565292</v>
+        <v>0.009139822477565286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009687876379596914</v>
+        <v>0.009687876379596901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009768880688659255</v>
+        <v>0.009768880688659104</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01672202530411323</v>
+        <v>0.01672202530411301</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009650169167885699</v>
+        <v>0.009650169167885692</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01021792016524657</v>
+        <v>0.01021792016524649</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009709443606204217</v>
+        <v>0.009709443606204186</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009765505509769038</v>
+        <v>0.009765505509768792</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01030576999393321</v>
+        <v>0.01030576999393315</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01029407269388478</v>
+        <v>0.01029407269388479</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01030517064710301</v>
+        <v>0.01030517064710313</v>
       </c>
       <c r="E5" t="n">
         <v>0.01019978632987534</v>
@@ -1838,22 +1838,22 @@
         <v>0.01019978632987534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01028391127951228</v>
+        <v>0.01028391127951232</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01030576999393321</v>
+        <v>0.01030576999393315</v>
       </c>
       <c r="I5" t="n">
         <v>0.01016519975873882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01030576999393321</v>
+        <v>0.01030576999393315</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01030576999393321</v>
+        <v>0.01030576999393315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01030576999393321</v>
+        <v>0.01030576999393315</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01656055382757969</v>
+        <v>0.0165605538275794</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02506293196847968</v>
+        <v>0.02506293196854257</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02679728182882814</v>
+        <v>0.02679728182882801</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02261135152164121</v>
+        <v>0.02261135152164115</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01670973315043245</v>
+        <v>0.01670973315043241</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02501732415053146</v>
+        <v>0.02501732415053142</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0250391828649912</v>
+        <v>0.02503918286499117</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02489861262975795</v>
+        <v>0.024898612629758</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02504084915588882</v>
+        <v>0.02504084915588866</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01640305894047124</v>
+        <v>0.01640305894047098</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03389581986358153</v>
+        <v>0.03389581986358133</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0202183205768025</v>
+        <v>0.02021832057680234</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02490854761999742</v>
+        <v>0.0249085476199974</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02492024798986123</v>
+        <v>0.02492024798986105</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03020559552837915</v>
+        <v>0.03020559552837912</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02477967234347249</v>
+        <v>0.02477967234347246</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02489838620562503</v>
+        <v>0.02489838620562482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02492024492004586</v>
+        <v>0.02492024492004566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02477967468485145</v>
+        <v>0.02477967468485143</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02492024492004586</v>
+        <v>0.02492024492004566</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02219593278084162</v>
+        <v>0.02219593278084145</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02492024492004586</v>
+        <v>0.02492024492004566</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03446507729901035</v>
+        <v>0.0344650772990104</v>
       </c>
       <c r="C8" t="n">
         <v>0.01101234550741959</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01593926284127372</v>
+        <v>0.01593926284127368</v>
       </c>
       <c r="E8" t="n">
         <v>0.01425414714373325</v>
@@ -1961,19 +1961,19 @@
         <v>0.01342116340602262</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01467646645691801</v>
+        <v>0.01467646645691796</v>
       </c>
       <c r="I8" t="n">
         <v>0.01425414714373325</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01615871317859084</v>
+        <v>0.01615871317859079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01984327464660159</v>
+        <v>0.01984327464660147</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01604831699786587</v>
+        <v>0.01604831699786577</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03421497376061391</v>
+        <v>0.03421497376061381</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01160803455120232</v>
+        <v>0.01160803455120231</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01726006017697822</v>
+        <v>0.0172600601769782</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01459582287656698</v>
+        <v>0.01459582287656699</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01459582287656698</v>
+        <v>0.01459582287656699</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01438530467922014</v>
+        <v>0.01438530467922005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01674959089044862</v>
+        <v>0.01674959089044842</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01459582287656698</v>
+        <v>0.01459582287656699</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01841480783154361</v>
+        <v>0.01841480783154353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01989940088742905</v>
+        <v>0.01989940088742895</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01671127490148895</v>
+        <v>0.01671127490148886</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01754400429429661</v>
+        <v>0.0175440042942966</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0542622585754673</v>
+        <v>0.05426225857546736</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08315767618002053</v>
+        <v>0.08315767618002021</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02437973236168168</v>
+        <v>0.02437973236168147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02437973236168168</v>
+        <v>0.02437973236168147</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06108203974178979</v>
+        <v>0.06108203974178917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1016559286407242</v>
+        <v>0.101655928640724</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02437973236168168</v>
+        <v>0.02437973236168147</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09880409661339001</v>
+        <v>0.09880409661338993</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02331256625590567</v>
+        <v>0.02331256625590565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0376897352960532</v>
+        <v>0.03768973529605318</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005253650529548807</v>
+        <v>0.00525365052954881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006178528710492425</v>
+        <v>0.006178528710492405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006178528710492425</v>
+        <v>0.006178528710492406</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005977871753131948</v>
+        <v>0.005977871753131912</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005868080534416823</v>
+        <v>0.00586808053441685</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005998144059690715</v>
+        <v>0.005998144059690689</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01581103171960783</v>
+        <v>0.009631053651396299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009470729881833031</v>
+        <v>0.009470729881832037</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009666119466644337</v>
+        <v>0.009666119466643018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008976249033266603</v>
+        <v>0.008976249033266636</v>
       </c>
       <c r="F4" t="n">
         <v>0.009529526621254119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009610781344837548</v>
+        <v>0.01579075941304911</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01637150214330454</v>
+        <v>0.0163715021433046</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009500990126122441</v>
+        <v>0.01568096819433404</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01003134681705305</v>
+        <v>0.01586317281572167</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009609066119793256</v>
+        <v>0.009609066119793216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009584489144395782</v>
+        <v>0.00958448914439646</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009952521264511857</v>
+        <v>0.00995252126451189</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009942077908647</v>
+        <v>0.009942077908646971</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009951924278398047</v>
+        <v>0.009951924278397983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009866750908425002</v>
+        <v>0.009866750908424982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009866750908425002</v>
+        <v>0.009866750908424982</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009932248957953154</v>
+        <v>0.009932248957953123</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009952521264511857</v>
+        <v>0.00995252126451189</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009822457739238104</v>
+        <v>0.009822457739238072</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009952521264511857</v>
+        <v>0.00995252126451189</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009952521264511857</v>
+        <v>0.00995252126451189</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009952521264511857</v>
+        <v>0.00995252126451189</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01608042374477846</v>
+        <v>0.01608042374477832</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02437325926199104</v>
+        <v>0.02437325926192489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0260514843002417</v>
+        <v>0.02605148430024167</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02199012290741785</v>
+        <v>0.02199012290741786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01623892387970493</v>
+        <v>0.01623892387970494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02431873988066181</v>
+        <v>0.02431873988066172</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02433901218725547</v>
+        <v>0.02433901218725544</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02420894866194666</v>
+        <v>0.02420894866194664</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0243406352328031</v>
+        <v>0.02434063523280312</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01592701622479154</v>
+        <v>0.0159270162247915</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03296579838392252</v>
+        <v>0.03296579838392251</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01816480953167705</v>
+        <v>0.01816480953167702</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02232539049541163</v>
+        <v>0.0223253904954116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02233583700018865</v>
+        <v>0.02233583700018858</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02701904510657769</v>
+        <v>0.02701904510657765</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02220576897336921</v>
+        <v>0.02220576897336919</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02231556154471782</v>
+        <v>0.02231556154471775</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02233583385127656</v>
+        <v>0.02233583385127651</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02220577032600272</v>
+        <v>0.02220577032600268</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02233583385127656</v>
+        <v>0.02233583385127651</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01982107833891023</v>
+        <v>0.01708376889156326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02233583385127656</v>
+        <v>0.02233583385127651</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03476870185255925</v>
+        <v>0.03476870185255931</v>
       </c>
       <c r="C8" t="n">
         <v>0.01120204079907875</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01681738368983916</v>
+        <v>0.01681738368983918</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01399038906330047</v>
+        <v>0.01399038906330049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01399038906330047</v>
+        <v>0.01399038906330049</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01377671342028825</v>
+        <v>0.01377671342028827</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01664514933455586</v>
+        <v>0.01664514933455589</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01399038906330047</v>
+        <v>0.01399038906330049</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01538726844001862</v>
+        <v>0.01538726844001868</v>
       </c>
       <c r="K8" t="n">
         <v>0.02010964492375659</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01688115927417426</v>
+        <v>0.01688115927417428</v>
       </c>
     </row>
     <row r="9">
@@ -2379,28 +2379,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03426779005814702</v>
+        <v>0.03426779005814695</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01154175118289261</v>
+        <v>0.0115417511828926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01749476274607568</v>
+        <v>0.01749476274607567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01388269691088407</v>
+        <v>0.01388269691088408</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01388269691088407</v>
+        <v>0.01388269691088408</v>
       </c>
       <c r="G9" t="n">
         <v>0.0141684320445066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01742646914716201</v>
+        <v>0.01742646914716202</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01388269691088407</v>
+        <v>0.01388269691088408</v>
       </c>
       <c r="J9" t="n">
         <v>0.01624112189747666</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02443023302757103</v>
+        <v>0.02443023302757102</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0201360725975996</v>
+        <v>0.02013607259759962</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1026720407202198</v>
+        <v>0.10267204072022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05311527490082863</v>
+        <v>0.05311527490082869</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05311527490082863</v>
+        <v>0.05311527490082869</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1090403211372295</v>
+        <v>0.1090403211372291</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3136411234500874</v>
+        <v>0.3136411234500878</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05311527490082863</v>
+        <v>0.05311527490082869</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2987465353176097</v>
+        <v>0.2987465353176094</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05876428188221011</v>
+        <v>0.05876428188220997</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2573940493262491</v>
+        <v>0.2573940493262492</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005189054282197524</v>
+        <v>0.005189054282197529</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005938217678950701</v>
+        <v>0.005938217678950687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005938217678950691</v>
+        <v>0.005938217678950688</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006075155434047161</v>
+        <v>0.006075155434047162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00594883455376789</v>
+        <v>0.005948834553767884</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006098353289801018</v>
+        <v>0.006098353289801022</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01611991848979285</v>
+        <v>0.009570606516941639</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009255556826543212</v>
+        <v>0.009255556826543143</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009603556089452413</v>
+        <v>0.009603556089452245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008844461088363629</v>
+        <v>0.008844461088363738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009426063025988711</v>
+        <v>0.009426063025988703</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009547408661187778</v>
+        <v>0.009547408661187771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01667374375391158</v>
+        <v>0.01667374375391157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0159703997537597</v>
+        <v>0.009421087780908497</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01617232334907787</v>
+        <v>0.01617232334907786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00944516716177554</v>
+        <v>0.009445167161775528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009617419824393144</v>
+        <v>0.00961741982439315</v>
       </c>
     </row>
     <row r="5">
@@ -2618,25 +2618,25 @@
         <v>0.01047110472393839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01045804900118981</v>
+        <v>0.01045804900118979</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0104704627066159</v>
+        <v>0.01047046270661589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01038069739671474</v>
+        <v>0.01038069739671471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01038069739671474</v>
+        <v>0.01038069739671471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01044790686818453</v>
+        <v>0.01044790686818452</v>
       </c>
       <c r="H5" t="n">
         <v>0.01047110472393839</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01032158598790526</v>
+        <v>0.01032158598790525</v>
       </c>
       <c r="J5" t="n">
         <v>0.01047110472393839</v>
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01698536058598361</v>
+        <v>0.0169853605859836</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02586127361833023</v>
+        <v>0.02586127361833018</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02764627115695393</v>
+        <v>0.02764627115695388</v>
       </c>
       <c r="E6" t="n">
         <v>0.02330351689825451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01715138378963756</v>
+        <v>0.01715138378963752</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02579212342862387</v>
+        <v>0.02579212342862386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02581532128438238</v>
+        <v>0.02581532128438231</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02566580254834458</v>
+        <v>0.02566580254834454</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02581705662315587</v>
+        <v>0.02581705662315584</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01682133953281389</v>
+        <v>0.01682133953281387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03503895358181913</v>
+        <v>0.03503895358181905</v>
       </c>
     </row>
     <row r="7">
@@ -2698,34 +2698,34 @@
         <v>0.02187163180912523</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02705316889173426</v>
+        <v>0.02705316889173425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02706622672656268</v>
+        <v>0.02706622672656267</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03291115310320307</v>
+        <v>0.03291115310320308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02691670216745271</v>
+        <v>0.0269167021674527</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02704302675872897</v>
+        <v>0.02704302675872896</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.02706622461448281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0269167058784497</v>
+        <v>0.02691670587844968</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.02706622461448281</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205253044935963</v>
+        <v>0.02052530449359631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.02706622461448281</v>
       </c>
     </row>
     <row r="8">
@@ -2738,7 +2738,7 @@
         <v>0.03431480207805995</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01213199274176582</v>
+        <v>0.01213199274176581</v>
       </c>
       <c r="D8" t="n">
         <v>0.01650581600410645</v>
@@ -2750,10 +2750,10 @@
         <v>0.01426820738076992</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01327141788772327</v>
+        <v>0.01327141788772325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01247285226955434</v>
+        <v>0.01247285226955433</v>
       </c>
       <c r="I8" t="n">
         <v>0.01426820738076992</v>
@@ -2762,10 +2762,10 @@
         <v>0.0139347738907986</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01948032708772408</v>
+        <v>0.01948032708772404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01530000727861151</v>
+        <v>0.0153000072786115</v>
       </c>
     </row>
     <row r="9">
@@ -2778,7 +2778,7 @@
         <v>0.03389868897303069</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01197618212337001</v>
+        <v>0.01197618212337</v>
       </c>
       <c r="D9" t="n">
         <v>0.01738759981832649</v>
@@ -2793,16 +2793,16 @@
         <v>0.01424899380976625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01575076460809263</v>
+        <v>0.01575076460809262</v>
       </c>
       <c r="I9" t="n">
         <v>0.01451869132738935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01727572625999399</v>
+        <v>0.01727572625999398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01972698838153596</v>
+        <v>0.01972698838153594</v>
       </c>
       <c r="L9" t="n">
         <v>0.01781136674413967</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01469266076226583</v>
+        <v>0.01469266076226582</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01645242131151627</v>
+        <v>0.01645242131151628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02189983158972841</v>
+        <v>0.02189983158972842</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03594032844841775</v>
+        <v>0.03594032844841789</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03594032844841775</v>
+        <v>0.03594032844841789</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02870244859230365</v>
+        <v>0.02870244859230373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03485154433951677</v>
+        <v>0.03485154433951678</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03594032844841775</v>
+        <v>0.03594032844841789</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1014326194051136</v>
+        <v>0.1014326194051135</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01968717565083522</v>
+        <v>0.01968717565083523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0458975814360302</v>
+        <v>0.04589758143603023</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005036213104221765</v>
+        <v>0.005036213104221763</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006154773740727682</v>
+        <v>0.006154773740727679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006154773740727685</v>
+        <v>0.006154773740727679</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005718718681627693</v>
+        <v>0.005718718681627686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005611829457015651</v>
+        <v>0.005611829457015643</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005738348393955688</v>
+        <v>0.0057383483939557</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009095003687727048</v>
+        <v>0.009095003687727032</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008912936201063121</v>
+        <v>0.008912936201063201</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01497291759548521</v>
+        <v>0.009072452673899136</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008578973916397972</v>
+        <v>0.008578973916397963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009022414174055223</v>
+        <v>0.009022414174055205</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009075373975399056</v>
+        <v>0.01495213487347038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01539373479638967</v>
+        <v>0.01539373479638966</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008968484750787009</v>
+        <v>0.01484524564885833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009463895835868697</v>
+        <v>0.009463895835868695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009063137248967439</v>
+        <v>0.009063137248967432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009064244763347737</v>
+        <v>0.009064244763347674</v>
       </c>
     </row>
     <row r="5">
@@ -3014,25 +3014,25 @@
         <v>0.009482849849344851</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009473230527116655</v>
+        <v>0.009473230527116646</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009482241145564516</v>
+        <v>0.009482241145564521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009431490829727175</v>
+        <v>0.009431490829727177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009431490829727175</v>
+        <v>0.009431490829727177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009463220137016856</v>
+        <v>0.009463220137016852</v>
       </c>
       <c r="H5" t="n">
         <v>0.009482849849344851</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009356330912404804</v>
+        <v>0.009356330912404792</v>
       </c>
       <c r="J5" t="n">
         <v>0.009482849849344851</v>
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01537474211672335</v>
+        <v>0.01537474211672336</v>
       </c>
       <c r="C6" t="n">
         <v>0.0232943438808672</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02485865176958352</v>
+        <v>0.02485865176958351</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02102117315440481</v>
+        <v>0.02102117315440478</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01554241747364235</v>
+        <v>0.01554241747364233</v>
       </c>
       <c r="G6" t="n">
         <v>0.02321021530059299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02322984501293623</v>
+        <v>0.02322984501293622</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02310332607598096</v>
+        <v>0.02310332607598095</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02323138876409445</v>
+        <v>0.02323138876409447</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0152288295477287</v>
+        <v>0.01522882954772869</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03143515681960688</v>
+        <v>0.03143515681960685</v>
       </c>
     </row>
     <row r="7">
@@ -3091,16 +3091,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01808628822454985</v>
+        <v>0.01808628822454986</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02224551920587703</v>
+        <v>0.02224551920587704</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02225514154462052</v>
+        <v>0.02225514154462051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02693938691484159</v>
+        <v>0.0269393869148416</v>
       </c>
       <c r="F7" t="n">
         <v>0.02212861938349478</v>
@@ -3109,19 +3109,19 @@
         <v>0.0222355088157772</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02225513852810519</v>
+        <v>0.02225513852810521</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02212861959116517</v>
+        <v>0.02212861959116516</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02225513852810519</v>
+        <v>0.02225513852810521</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01983969155862145</v>
+        <v>0.01700581107696642</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02225513852810519</v>
+        <v>0.02225513852810521</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03418286467798955</v>
+        <v>0.03418286467798959</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01193768076083248</v>
+        <v>0.01193768076083247</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01804752854687247</v>
+        <v>0.01804752854687246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.01436668882565507</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.01436668882565507</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01472270094334751</v>
+        <v>0.01472270094334752</v>
       </c>
       <c r="H8" t="n">
         <v>0.0178184079667748</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.01436668882565507</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0179553468635823</v>
+        <v>0.01795534686358228</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02002348059799824</v>
+        <v>0.02002348059799828</v>
       </c>
       <c r="L8" t="n">
         <v>0.01670778218826463</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03365271927116751</v>
+        <v>0.03365271927116754</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0117490835482052</v>
+        <v>0.01174908354820521</v>
       </c>
       <c r="D9" t="n">
         <v>0.01784434615442351</v>
@@ -3186,7 +3186,7 @@
         <v>0.01441581422230267</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01465823210550366</v>
+        <v>0.01465823210550367</v>
       </c>
       <c r="H9" t="n">
         <v>0.01775158292905985</v>
@@ -3198,10 +3198,10 @@
         <v>0.0188053102915278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01975733385408003</v>
+        <v>0.01975733385408007</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01678529735659236</v>
+        <v>0.01678529735659237</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01305614759776526</v>
+        <v>0.01305614759776524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01556989171540074</v>
+        <v>0.0155698917154009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01962447481022701</v>
+        <v>0.01962447481022699</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02488835048629466</v>
+        <v>0.02488835048629454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02488835048629466</v>
+        <v>0.02488835048629454</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01947722552275836</v>
+        <v>0.01947722552275826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02213250556716202</v>
+        <v>0.02213250556716198</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02488835048629466</v>
+        <v>0.02488835048629454</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03168558803245444</v>
+        <v>0.03168558803245451</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01492466610695848</v>
+        <v>0.01492466610695843</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01957772479904773</v>
+        <v>0.0195777247990477</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005015384967029103</v>
+        <v>0.005015384967029106</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005912470534889201</v>
+        <v>0.005912470534889177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005912470534889198</v>
+        <v>0.005912470534889178</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005615803631815968</v>
+        <v>0.005615803631816197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005515273020013576</v>
+        <v>0.005515273020013959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00563433018788054</v>
+        <v>0.005634330187880539</v>
       </c>
     </row>
     <row r="4">
@@ -3370,34 +3370,34 @@
         <v>0.01483693823155877</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008874541359926033</v>
+        <v>0.008874541359925998</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008979878643483258</v>
+        <v>0.008979878643483265</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008486221699435473</v>
+        <v>0.008486221699435491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008947015611471496</v>
+        <v>0.008947015611471489</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0148184116754942</v>
+        <v>0.01481841167549418</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01522223061077749</v>
+        <v>0.01522223061077747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008907016333938084</v>
+        <v>0.008907016333938058</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01482537231632787</v>
+        <v>0.01482537231632786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009027852603792267</v>
+        <v>0.009027852603792212</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980211993040872</v>
+        <v>0.008980211993040882</v>
       </c>
     </row>
     <row r="5">
@@ -3410,25 +3410,25 @@
         <v>0.009221120162634287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009211941865994272</v>
+        <v>0.009211941865994271</v>
       </c>
       <c r="D5" t="n">
         <v>0.009220506126847633</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009163256856446218</v>
+        <v>0.009163256856446199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009163256856446218</v>
+        <v>0.009163256856446199</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009202593606569717</v>
+        <v>0.009202593606569713</v>
       </c>
       <c r="H5" t="n">
         <v>0.009221120162634287</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009102062994767329</v>
+        <v>0.009102062994767308</v>
       </c>
       <c r="J5" t="n">
         <v>0.009221120162634287</v>
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01502549467862042</v>
+        <v>0.01502549467862043</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02273884883675604</v>
+        <v>0.02273884883675601</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02427598890873328</v>
+        <v>0.02427598890873323</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02052696590113578</v>
+        <v>0.02052696590113573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0151861753666087</v>
+        <v>0.01518617536660866</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02266874334795187</v>
+        <v>0.02266874334795183</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02268726990403319</v>
+        <v>0.02268726990403316</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02256821273614951</v>
+        <v>0.02256821273614948</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02268877566085972</v>
+        <v>0.02268877566085968</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01488317327035196</v>
+        <v>0.01488317327035194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03069063479284786</v>
+        <v>0.03069063479284782</v>
       </c>
     </row>
     <row r="7">
@@ -3490,13 +3490,13 @@
         <v>0.01683380052436988</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02065953048093005</v>
+        <v>0.02065953048093006</v>
       </c>
       <c r="D7" t="n">
         <v>0.02066871160804125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02497505673144977</v>
+        <v>0.02497505673144976</v>
       </c>
       <c r="F7" t="n">
         <v>0.02054965141134851</v>
@@ -3505,19 +3505,19 @@
         <v>0.0206501822215055</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02066870877757007</v>
+        <v>0.02066870877757006</v>
       </c>
       <c r="I7" t="n">
         <v>0.02054965160970311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02066870877757007</v>
+        <v>0.02066870877757006</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01844674906530433</v>
+        <v>0.01835660123818635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02066870877757007</v>
+        <v>0.02066870877757006</v>
       </c>
     </row>
     <row r="8">
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03389077200188426</v>
+        <v>0.03389077200188421</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01173807249312139</v>
+        <v>0.01173807249312138</v>
       </c>
       <c r="D8" t="n">
         <v>0.01793543334125654</v>
@@ -3542,7 +3542,7 @@
         <v>0.01354602797210378</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01429988427947817</v>
+        <v>0.01429988427947815</v>
       </c>
       <c r="H8" t="n">
         <v>0.01792464820108218</v>
@@ -3551,10 +3551,10 @@
         <v>0.01354602797210378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01626343253988384</v>
+        <v>0.01626343253988382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987117204436598</v>
+        <v>0.01987117204436596</v>
       </c>
       <c r="L8" t="n">
         <v>0.01689934760191569</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03334288719622044</v>
+        <v>0.03334288719622041</v>
       </c>
       <c r="C9" t="n">
         <v>0.01154040159131051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01770191900045164</v>
+        <v>0.01770191900045162</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0134537550144797</v>
+        <v>0.01345375501447969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0134537550144797</v>
+        <v>0.01345375501447969</v>
       </c>
       <c r="G9" t="n">
         <v>0.01411581723360235</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01769783038181203</v>
+        <v>0.01769783038181202</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0134537550144797</v>
+        <v>0.01345375501447969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01620685886576988</v>
+        <v>0.01620685886576987</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01954057821876563</v>
+        <v>0.01954057821876562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01665292266594557</v>
+        <v>0.01665292266594556</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02139601711706898</v>
+        <v>0.02139601711706891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01827196383736493</v>
+        <v>0.01827196383736494</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03561803360860377</v>
+        <v>0.03561803360860355</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04814996855239503</v>
+        <v>0.04814996855239506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04814996855239503</v>
+        <v>0.04814996855239506</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05586561352728658</v>
+        <v>0.05586561352728583</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2613026517835402</v>
+        <v>0.2613026517835405</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04814996855239503</v>
+        <v>0.04814996855239506</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06935054329283197</v>
+        <v>0.06935054329283186</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0325176767077591</v>
+        <v>0.03251767670775894</v>
       </c>
       <c r="L2" t="n">
-        <v>0.209224882525898</v>
+        <v>0.2092248825258976</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005097037290959922</v>
+        <v>0.005097037290959924</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00588860637278538</v>
+        <v>0.00588860637278539</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005888606372785382</v>
+        <v>0.005888606372785389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005951676441429304</v>
+        <v>0.005951676441429265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005834425575268158</v>
+        <v>0.005834425575268189</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005973177899667528</v>
+        <v>0.00597317789966744</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01562546223550466</v>
+        <v>0.009263995279809365</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009024195211041721</v>
+        <v>0.009024195211041888</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009231990762865155</v>
+        <v>0.009231990762864881</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008633892735647224</v>
+        <v>0.008633892735647242</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009138743019248644</v>
+        <v>0.009138743019248646</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0156039607772664</v>
+        <v>0.01560396077726629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01615540272323948</v>
+        <v>0.01615540272323937</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00912524295541018</v>
+        <v>0.01548670991110532</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01566077786634362</v>
+        <v>0.01566077786634347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009154594300674562</v>
+        <v>0.009154594300674427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009297093805578319</v>
+        <v>0.009297093805578272</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01009945309639314</v>
+        <v>0.01009945309639311</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01008874956843793</v>
+        <v>0.01008874956843794</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0100988134924793</v>
+        <v>0.01009881349247921</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003025567124654</v>
+        <v>0.01003025567124655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003025567124654</v>
+        <v>0.01003025567124655</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01007795163815488</v>
+        <v>0.01007795163815481</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01009945309639314</v>
+        <v>0.01009945309639311</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009960700771993807</v>
+        <v>0.009960700771993805</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01009945309639314</v>
+        <v>0.01009945309639311</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01009945309639314</v>
+        <v>0.01009945309639311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01009945309639314</v>
+        <v>0.01009945309639311</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01644264373429128</v>
+        <v>0.01644264373429114</v>
       </c>
       <c r="C6" t="n">
         <v>0.02502090229462254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02672936665571586</v>
+        <v>0.02672936665571577</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02255527480319368</v>
+        <v>0.02255527480319373</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01661583787578831</v>
+        <v>0.01661583787578834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02494117989449649</v>
+        <v>0.02494117989449647</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02496268135273772</v>
+        <v>0.02496268135273777</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02482392902833539</v>
+        <v>0.02482392902833544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02496435578268349</v>
+        <v>0.02496435578268345</v>
       </c>
       <c r="K6" t="n">
         <v>0.01628437966145276</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03386257307775775</v>
+        <v>0.03386257307775786</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02050514186035936</v>
+        <v>0.02050514186035926</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02532631851707981</v>
+        <v>0.0253263185170798</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02533702302269737</v>
+        <v>0.0253370230226973</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03077415389017506</v>
+        <v>0.03077415389017507</v>
       </c>
       <c r="F7" t="n">
         <v>0.02519826652467275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02531552058679675</v>
+        <v>0.02531552058679667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02533702204503499</v>
+        <v>0.02533702204503495</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02519826972063566</v>
+        <v>0.02519826972063567</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02533702204503499</v>
+        <v>0.02533702204503495</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02242382834944492</v>
+        <v>0.02253741210097735</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02533702204503499</v>
+        <v>0.02533702204503494</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0341512290921765</v>
+        <v>0.03415122909217645</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01209373716043794</v>
+        <v>0.01209373716043795</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01790644875325068</v>
+        <v>0.01790644875325066</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.01423764923145976</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.01423764923145976</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0142722965156281</v>
+        <v>0.01427229651562807</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01339078954369529</v>
+        <v>0.01339078954369528</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.01423764923145976</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01859342025321833</v>
+        <v>0.01859342025321835</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987970321746415</v>
+        <v>0.01987970321746407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01612580737390197</v>
+        <v>0.01612580737390194</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03369835568831685</v>
+        <v>0.03369835568831674</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01191481527890707</v>
+        <v>0.01191481527890709</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01787260131850409</v>
+        <v>0.01787260131850402</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01442384892153845</v>
+        <v>0.01442384892153846</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01442384892153845</v>
+        <v>0.01442384892153846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01454625657768503</v>
+        <v>0.01454625657768502</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01603821332800032</v>
+        <v>0.01603821332800025</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01442384892153845</v>
+        <v>0.01442384892153846</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01895564288286613</v>
+        <v>0.01895564288286609</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01977208346611601</v>
+        <v>0.01977208346611598</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01806857661045548</v>
+        <v>0.01806857661045545</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01637788248865753</v>
+        <v>0.01637788248865747</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01702646375701896</v>
+        <v>0.01702646375701895</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02062721120133779</v>
+        <v>0.02062721120133777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03456644372086119</v>
+        <v>0.03456644372086102</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03456644372086119</v>
+        <v>0.03456644372086102</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02251032810071322</v>
+        <v>0.02251032810071286</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02372825352167936</v>
+        <v>0.02372825352167926</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03456644372086119</v>
+        <v>0.03456644372086102</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03760486951072428</v>
+        <v>0.03760486951072427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02194137942198521</v>
+        <v>0.02194137942198486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02130760939791639</v>
+        <v>0.02130760939791628</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005007851209893872</v>
+        <v>0.005007851209893869</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006188714664728939</v>
+        <v>0.006188714664728935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006188714664728938</v>
+        <v>0.006188714664728936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005691902781972517</v>
+        <v>0.005691902781972479</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005586397700253488</v>
+        <v>0.005586397700253464</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00571127020444579</v>
+        <v>0.005711270204445762</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01491295906377287</v>
+        <v>0.009051699614529131</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008877390106382754</v>
+        <v>0.008877390106382884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009032267351266355</v>
+        <v>0.009032203004537383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008552312685018305</v>
+        <v>0.008552312685018295</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00898389285899668</v>
+        <v>0.008983892858996669</v>
       </c>
       <c r="G4" t="n">
         <v>0.009032332192055839</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01532147154003821</v>
+        <v>0.0153214715400382</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008926827110336827</v>
+        <v>0.01478808655958055</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009397109408732729</v>
+        <v>0.01490563913361424</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009032116011430807</v>
+        <v>0.009032116011430794</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009012744769876653</v>
+        <v>0.009012744769876641</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009387237433805708</v>
+        <v>0.009387237433805677</v>
       </c>
       <c r="C5" t="n">
         <v>0.009377995710604665</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009386630867326082</v>
+        <v>0.009386630867326079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009353645048142808</v>
+        <v>0.009353645048142819</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009353645048142808</v>
+        <v>0.009353645048142819</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009367870011332389</v>
+        <v>0.009367870011332383</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009387237433805708</v>
+        <v>0.009387237433805677</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009262364929613364</v>
+        <v>0.009262364929613376</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009387237433805708</v>
+        <v>0.009387237433805677</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009387237433805708</v>
+        <v>0.009387237433805677</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009387237433805708</v>
+        <v>0.009387237433805677</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01523078983670689</v>
+        <v>0.01523078983670684</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02308124342956649</v>
+        <v>0.02308124342956645</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02461217964891897</v>
+        <v>0.02461217964891889</v>
       </c>
       <c r="E6" t="n">
         <v>0.02083093988692858</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01540703523404363</v>
+        <v>0.01540703523404358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0229816126608396</v>
+        <v>0.02298161266083946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.023000980083325</v>
+        <v>0.02300098008332493</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02287610757912058</v>
+        <v>0.0228761075791205</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02300250714659934</v>
+        <v>0.02300250714659927</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508645456378539</v>
+        <v>0.01508645456378536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111759352710069</v>
+        <v>0.03111759352710059</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01791253261333265</v>
+        <v>0.01791253261333262</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0220269404511754</v>
+        <v>0.02202694045117536</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02203618513805139</v>
+        <v>0.02203618513805132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02666991644935752</v>
+        <v>0.02666991644935748</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02191130962388284</v>
+        <v>0.02191130962388281</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02201681475190313</v>
+        <v>0.02201681475190309</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02203618217437643</v>
+        <v>0.02203618217437638</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0219113096701841</v>
+        <v>0.02191130967018407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02203618217437643</v>
+        <v>0.02203618217437638</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01684377054005883</v>
+        <v>0.01964692467039639</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02203618217437643</v>
+        <v>0.02203618217437638</v>
       </c>
     </row>
     <row r="8">
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03288542354812125</v>
+        <v>0.03288542354812124</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01195595600823171</v>
+        <v>0.01195595600823172</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01803727408127815</v>
+        <v>0.01803727408127816</v>
       </c>
       <c r="E8" t="n">
         <v>0.01438850185206195</v>
@@ -4337,19 +4337,19 @@
         <v>0.01474630502830657</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01801649643616658</v>
+        <v>0.01801649643616659</v>
       </c>
       <c r="I8" t="n">
         <v>0.01438850185206195</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01934710503856345</v>
+        <v>0.01934710503856342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02003048196639647</v>
+        <v>0.02003048196639652</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01720253680894133</v>
+        <v>0.01720253680894134</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03239875965486473</v>
+        <v>0.03239875965486469</v>
       </c>
       <c r="C9" t="n">
         <v>0.01177516605460205</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0178166391548094</v>
+        <v>0.01781663915480942</v>
       </c>
       <c r="E9" t="n">
         <v>0.01441846377179725</v>
@@ -4374,7 +4374,7 @@
         <v>0.01441846377179725</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01459711958691007</v>
+        <v>0.01459711958691006</v>
       </c>
       <c r="H9" t="n">
         <v>0.01780851102225482</v>
@@ -4383,13 +4383,13 @@
         <v>0.01441846377179725</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01932182031630982</v>
+        <v>0.01932182031630983</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01979613839114529</v>
+        <v>0.01979613839114532</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01697288318472573</v>
+        <v>0.01697288318472572</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01452925536178794</v>
+        <v>0.01452925536178796</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01582681261989338</v>
+        <v>0.01582681261989335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01881726918486955</v>
+        <v>0.01881726918486957</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02494009599691101</v>
+        <v>0.02494009599691095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02494009599691101</v>
+        <v>0.02494009599691095</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01945991174890808</v>
+        <v>0.01945991174890786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02135012597240804</v>
+        <v>0.02135012597240806</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02494009599691101</v>
+        <v>0.02494009599691095</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03202120472592161</v>
+        <v>0.03202120472592165</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01945715033856494</v>
+        <v>0.01945715033856495</v>
       </c>
       <c r="L2" t="n">
-        <v>0.019517428190072</v>
+        <v>0.01951742819007201</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004989146035842938</v>
+        <v>0.004989146035842912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005926883031751221</v>
+        <v>0.005926883031751239</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005926883031751214</v>
+        <v>0.005926883031751241</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005597644528369794</v>
+        <v>0.005597644528369811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005498288719621208</v>
+        <v>0.005498288719621223</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005615961176891394</v>
+        <v>0.00561596117689141</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01483189595755354</v>
+        <v>0.009026626639279165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008872817520468869</v>
+        <v>0.008872817520469076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008976872531022683</v>
+        <v>0.008976872531022686</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008490877820592104</v>
+        <v>0.008490877820592119</v>
       </c>
       <c r="F4" t="n">
         <v>0.008950485785739573</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01481357930903194</v>
+        <v>0.01481357930903193</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01521274449956764</v>
+        <v>0.01521274449956765</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008908954182008988</v>
+        <v>0.01471422350028338</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01482093559746565</v>
+        <v>0.009373188469637481</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009037656284100127</v>
+        <v>0.009037656284100132</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980151751440383</v>
+        <v>0.008980151751439781</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00915455624963051</v>
+        <v>0.009154556249630512</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009145424002047226</v>
+        <v>0.009145424002047207</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009153944208555361</v>
+        <v>0.009153944208555363</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009107388487643231</v>
+        <v>0.009107388487643238</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009107388487643231</v>
+        <v>0.009107388487643238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009136239601108912</v>
+        <v>0.009136239601108907</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00915455624963051</v>
+        <v>0.009154556249630512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009036883792360334</v>
+        <v>0.009036883792360338</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00915455624963051</v>
+        <v>0.009154556249630512</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00915455624963051</v>
+        <v>0.009154556249630512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00915455624963051</v>
+        <v>0.009154556249630512</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01492095495190045</v>
+        <v>0.01492095495190049</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02258033324915314</v>
+        <v>0.02258033324915317</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02409549736516707</v>
+        <v>0.02409549736516712</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02038605389605649</v>
+        <v>0.02038605389605656</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01508657945318925</v>
+        <v>0.01508657945318927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02250150599820321</v>
+        <v>0.02250150599820324</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02251982264674063</v>
+        <v>0.02251982264674066</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02240215018945463</v>
+        <v>0.02240215018945464</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0225213160403594</v>
+        <v>0.02252131604035943</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01477980208331734</v>
+        <v>0.01477980208331735</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03045747535955903</v>
+        <v>0.03045747535955909</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>0.01678348020978125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02059687013984998</v>
+        <v>0.02059687013984996</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02060600522066557</v>
+        <v>0.02060600522066556</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02489944184432974</v>
+        <v>0.02489944184432973</v>
       </c>
       <c r="F7" t="n">
-        <v>0.020488329778592</v>
+        <v>0.02048832977859199</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02058768573891166</v>
+        <v>0.02058768573891165</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02060600238743329</v>
+        <v>0.02060600238743327</v>
       </c>
       <c r="I7" t="n">
         <v>0.02048832993016308</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02060600238743329</v>
+        <v>0.02060600238743327</v>
       </c>
       <c r="K7" t="n">
         <v>0.0183013625512887</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02060600238743329</v>
+        <v>0.02060600238743327</v>
       </c>
     </row>
     <row r="8">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02938326219594543</v>
+        <v>0.02938326219594538</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01178739990999203</v>
+        <v>0.01178739990999202</v>
       </c>
       <c r="D8" t="n">
         <v>0.01792907028572759</v>
@@ -4730,7 +4730,7 @@
         <v>0.0135345598572942</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01391845053449593</v>
+        <v>0.01391845053449592</v>
       </c>
       <c r="H8" t="n">
         <v>0.01791544757057358</v>
@@ -4739,13 +4739,13 @@
         <v>0.0135345598572942</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0162256368578133</v>
+        <v>0.01622563685781332</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01979397711978835</v>
+        <v>0.01979397711978831</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0168838791899756</v>
+        <v>0.01688387918997559</v>
       </c>
     </row>
     <row r="9">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02892620217890743</v>
+        <v>0.02892620217890739</v>
       </c>
       <c r="C9" t="n">
         <v>0.01159260844076965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01768448196384158</v>
+        <v>0.01768448196384159</v>
       </c>
       <c r="E9" t="n">
         <v>0.01344336161326409</v>
@@ -4770,19 +4770,19 @@
         <v>0.01344336161326409</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01374030257679913</v>
+        <v>0.01374030257679912</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01767922261264911</v>
+        <v>0.01767922261264912</v>
       </c>
       <c r="I9" t="n">
         <v>0.01344336161326409</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01617433056128537</v>
+        <v>0.01617433056128538</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01952833678923927</v>
+        <v>0.01952833678923918</v>
       </c>
       <c r="L9" t="n">
         <v>0.01663713894158896</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2389431243237639</v>
+        <v>0.2389431243237635</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09524105664293592</v>
+        <v>0.09524105664293624</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2870188602747543</v>
+        <v>0.2870188602747544</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09524105664293592</v>
+        <v>0.09524105664293624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09524105664293592</v>
+        <v>0.09524105664293624</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2972813302547627</v>
+        <v>0.2972813302547628</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7618618037462794</v>
+        <v>0.7618618037462811</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09524105664293592</v>
+        <v>0.09524105664293624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.360861831393904</v>
+        <v>0.3608618313939033</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1331362577190272</v>
+        <v>0.1331362577190277</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3137813506713618</v>
+        <v>0.3137813506713616</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006159380652871553</v>
+        <v>0.006159380652871527</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006355381061930062</v>
+        <v>0.006355381061930047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006355381061930063</v>
+        <v>0.006355381061930046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007071625880220777</v>
+        <v>0.007071625880220758</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006930522161783389</v>
+        <v>0.006930522161783392</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007097714620081555</v>
+        <v>0.007097714620081548</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01902288269249184</v>
+        <v>0.01902288269249183</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01051993262966378</v>
+        <v>0.01051993262966372</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01125853553365519</v>
+        <v>0.01125853553365506</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01005879807142517</v>
+        <v>0.01005879807142514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01088955738618473</v>
+        <v>0.0108895573861847</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01108586864090361</v>
+        <v>0.01899679395263103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01129574845124767</v>
+        <v>0.01952137590291941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01885569023419371</v>
+        <v>0.01885569023419367</v>
       </c>
       <c r="J4" t="n">
         <v>0.01909189616747737</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01086493091182928</v>
+        <v>0.01086493091182925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01144635977971158</v>
+        <v>0.01144635977971156</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01219132608665817</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01202413362836003</v>
+        <v>0.01202413362836</v>
       </c>
       <c r="D5" t="n">
         <v>0.01219061582344471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01201490627370038</v>
+        <v>0.01201490627370034</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01201490627370038</v>
+        <v>0.01201490627370034</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01216523734679738</v>
+        <v>0.01216523734679737</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01219132608665817</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01202413362836003</v>
+        <v>0.01202413362836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01219132608665817</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01219132608665817</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01219132608665817</v>
+        <v>0.01219132608665816</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01938429305466474</v>
+        <v>0.01938429305466472</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0290698380287665</v>
+        <v>0.02906983802876653</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03128730796120117</v>
+        <v>0.03128730796120123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02637401867096106</v>
+        <v>0.02637401867096112</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0195245265985846</v>
+        <v>0.01952452659858463</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02921694509660379</v>
+        <v>0.0292169450966038</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0292430338364649</v>
+        <v>0.02924303383646498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02907584137816634</v>
+        <v>0.02907584137816635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02924497136012544</v>
+        <v>0.0292449713601255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01920116188326454</v>
+        <v>0.01920116188326456</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03954131295628509</v>
+        <v>0.03954131295628517</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02783777072219439</v>
+        <v>0.02783777072219438</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03429948172116129</v>
+        <v>0.03429948172116125</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03446667488250332</v>
+        <v>0.03446667488250334</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04194908291088665</v>
+        <v>0.04194908291088664</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0342994709371302</v>
+        <v>0.03429947093713018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03444058543959866</v>
+        <v>0.03444058543959865</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03446667417945948</v>
+        <v>0.03446667417945946</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03429948172116129</v>
+        <v>0.03429948172116125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03446667417945948</v>
+        <v>0.03446667417945946</v>
       </c>
       <c r="K7" t="n">
         <v>0.03062586177830534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03446667417945948</v>
+        <v>0.03446667417945946</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01301487821921215</v>
+        <v>0.01301487821921214</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01632827272988693</v>
+        <v>0.01632827272988695</v>
       </c>
       <c r="D8" t="n">
         <v>0.01204337982147764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01632827272988693</v>
+        <v>0.01632827272988695</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01632827272988693</v>
+        <v>0.01632827272988695</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01192449536045164</v>
+        <v>0.01192449536045166</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003107281604186628</v>
+        <v>0.00310728160418661</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01632827272988693</v>
+        <v>0.01632827272988695</v>
       </c>
       <c r="J8" t="n">
         <v>0.01084603797643393</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561126653778333</v>
+        <v>0.01561126653778332</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.006015118684144937</v>
+        <v>0.01220760844604422</v>
       </c>
     </row>
     <row r="9">
@@ -5166,10 +5166,10 @@
         <v>0.01713752023318419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0153714650039372</v>
+        <v>0.01537146500393719</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01181784750271856</v>
+        <v>0.01181784750271854</v>
       </c>
       <c r="I9" t="n">
         <v>0.01713752023318419</v>
@@ -5178,10 +5178,10 @@
         <v>0.01495838452363548</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01689646522961175</v>
+        <v>0.01689646522961173</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008106591467124211</v>
+        <v>0.01551471924140679</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1774303745276819</v>
+        <v>0.1774303745276818</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09567154855820098</v>
+        <v>0.09567154855820105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2564896721441024</v>
+        <v>0.256489672144101</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09567154855820098</v>
+        <v>0.09567154855820105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09567154855820098</v>
+        <v>0.09567154855820105</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2568097637464229</v>
+        <v>0.2568097637464232</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5957086622644449</v>
+        <v>0.5957086622644447</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09567154855820098</v>
+        <v>0.09567154855820105</v>
       </c>
       <c r="J2" t="n">
         <v>0.248621519775417</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1161748839000134</v>
+        <v>0.1161748839000135</v>
       </c>
       <c r="L2" t="n">
-        <v>1.088940967111485</v>
+        <v>0.3347929526472376</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330634</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006087929061855329</v>
+        <v>0.006087929061855324</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330636</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006260893544026587</v>
+        <v>0.006260893544026582</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00626089354402659</v>
+        <v>0.006260893544026582</v>
       </c>
       <c r="G3" t="n">
         <v>0.00681100969564311</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006680242835001684</v>
+        <v>0.006680242835001669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330636</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006835208131330631</v>
+        <v>0.006835208131330636</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01077736902422673</v>
+        <v>0.01806922377053089</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0102807498813089</v>
+        <v>0.01028074988130893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01091977529491971</v>
+        <v>0.01091977529492011</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009830170392009268</v>
+        <v>0.009830170392009275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.010583250549723</v>
+        <v>0.01058325054972299</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01075317058853922</v>
+        <v>0.01804502533484337</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01845128697611775</v>
+        <v>0.01845128697611772</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01062240372789777</v>
+        <v>0.01791425847420193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01121272884043833</v>
+        <v>0.01809294367404582</v>
       </c>
       <c r="K4" t="n">
         <v>0.01062474910446135</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01103031717855165</v>
+        <v>0.01103031717855167</v>
       </c>
     </row>
     <row r="5">
@@ -5390,16 +5390,16 @@
         <v>0.01143192842232782</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01127696312599888</v>
+        <v>0.01127696312599887</v>
       </c>
       <c r="D5" t="n">
         <v>0.01143126554451479</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01126587497442954</v>
+        <v>0.01126587497442955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01126587497442954</v>
+        <v>0.01126587497442955</v>
       </c>
       <c r="G5" t="n">
         <v>0.01140772998664032</v>
@@ -5408,7 +5408,7 @@
         <v>0.01143192842232782</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01127696312599888</v>
+        <v>0.01127696312599887</v>
       </c>
       <c r="J5" t="n">
         <v>0.01143192842232782</v>
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01800105983813535</v>
+        <v>0.0180010598381353</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02681015863458203</v>
+        <v>0.0268101586346287</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02883356369905248</v>
+        <v>0.02883356369905243</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02435706131244215</v>
+        <v>0.02435706131244212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0181242765643654</v>
+        <v>0.01812427656436538</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0269489452334129</v>
+        <v>0.02694894523341285</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02697314366910193</v>
+        <v>0.02697314366910184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02681817837277146</v>
+        <v>0.02681817837277144</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0269749069393383</v>
+        <v>0.02697490693933823</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0178343987748048</v>
+        <v>0.01783439877480475</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03634523546279597</v>
+        <v>0.03634523546279587</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02439150538428108</v>
+        <v>0.02439150538428107</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02990898011201974</v>
+        <v>0.02990898011201966</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0300639469460535</v>
+        <v>0.03006394694605348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03645484650108919</v>
+        <v>0.03645484650108909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02990897170113854</v>
+        <v>0.02990897170113846</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03003974697266115</v>
+        <v>0.03003974697266114</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0300639454083487</v>
+        <v>0.03006394540834866</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02990898011201974</v>
+        <v>0.02990898011201966</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0300639454083487</v>
+        <v>0.03006394540834866</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02292133049254489</v>
+        <v>0.02292133049254486</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0300639454083487</v>
+        <v>0.03006394540834866</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01415658409643563</v>
+        <v>0.01415658409643564</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01600155056878717</v>
+        <v>0.01600155056878718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01213049806876919</v>
+        <v>0.01213049806876924</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01600155056878717</v>
+        <v>0.01600155056878718</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01600155056878717</v>
+        <v>0.01600155056878718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225585350590066</v>
+        <v>0.01225585350590067</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005548936987645413</v>
+        <v>0.005548936987645443</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01600155056878717</v>
+        <v>0.01600155056878718</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01280219226782457</v>
+        <v>0.01280219226782458</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0155631420880061</v>
+        <v>0.01556314208800611</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.004273995642159009</v>
+        <v>0.01111453795856697</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01625136049680886</v>
+        <v>0.01625136049680887</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01693400882662076</v>
+        <v>0.01693400882662077</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01542631511064975</v>
+        <v>0.01542631511064978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01693400882662076</v>
+        <v>0.01693400882662077</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01693400882662076</v>
+        <v>0.01693400882662077</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01545681770509392</v>
+        <v>0.01545681770509393</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01275749140005928</v>
+        <v>0.0127574914000593</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01693400882662076</v>
+        <v>0.01693400882662077</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01570186367065654</v>
+        <v>0.01570186367065657</v>
       </c>
       <c r="K9" t="n">
         <v>0.01682439310772103</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01501779760922978</v>
+        <v>0.01501779760922979</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1486442751462757</v>
+        <v>0.148644275146275</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1198356427697942</v>
+        <v>0.1198356427697938</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2077814287750752</v>
+        <v>0.207781428775075</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1198356427697942</v>
+        <v>0.1198356427697938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1198356427697942</v>
+        <v>0.1198356427697938</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2177788056536312</v>
+        <v>0.2177788056536303</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4134816518931376</v>
+        <v>0.4134816518931386</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1198356427697942</v>
+        <v>0.1198356427697938</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1621959267236878</v>
+        <v>0.1621959267236875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09693985202474166</v>
+        <v>0.09693985202474084</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9698782020112813</v>
+        <v>0.9698782020112817</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088886</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006217573401584223</v>
+        <v>0.006217573401584193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006382512115142903</v>
+        <v>0.006382512115142886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006382512115142906</v>
+        <v>0.00638251211514288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006828681865320554</v>
+        <v>0.006828681865320546</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088887</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006707172617743469</v>
+        <v>0.006707172617743443</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088887</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006851130598088907</v>
+        <v>0.006851130598088887</v>
       </c>
     </row>
     <row r="4">
@@ -5743,34 +5743,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01082078423171831</v>
+        <v>0.01082078423171832</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01045655167494495</v>
+        <v>0.01045655167494491</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01796263364274665</v>
+        <v>0.0179626336427466</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009999506167517262</v>
+        <v>0.009999506167517224</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01066999379658873</v>
+        <v>0.01066999379658871</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01079833549894999</v>
+        <v>0.01079833549894998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01831679567070514</v>
+        <v>0.01831679567070508</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01781770282968827</v>
+        <v>0.01781770282968822</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01797652996593503</v>
+        <v>0.01123685800016055</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01070574553140052</v>
+        <v>0.0107057455314005</v>
       </c>
       <c r="L4" t="n">
         <v>0.01109274518118148</v>
@@ -5786,34 +5786,34 @@
         <v>0.01130806557867215</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01116410759832674</v>
+        <v>0.01116410759832669</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01130740053172412</v>
+        <v>0.0113074005317241</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01115243260293485</v>
+        <v>0.01115243260293483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01115243260293485</v>
+        <v>0.01115243260293483</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01128561684590382</v>
+        <v>0.01128561684590379</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01130806557867215</v>
+        <v>0.01130806557867214</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01116410759832674</v>
+        <v>0.01116410759832669</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01130806557867215</v>
+        <v>0.01130806557867214</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01130806557867215</v>
+        <v>0.01130806557867214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01130806557867215</v>
+        <v>0.01130806557867214</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01771734370458513</v>
+        <v>0.01771734370458512</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02631488539798687</v>
+        <v>0.0263148853979868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02828185414801132</v>
+        <v>0.02828185414801124</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02392255258876731</v>
+        <v>0.02392255258876723</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01784418294577632</v>
+        <v>0.01784418294577626</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02644501170830845</v>
+        <v>0.02644501170830839</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02646746044107898</v>
+        <v>0.02646746044107891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02632350246073138</v>
+        <v>0.02632350246073132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02646918008848114</v>
+        <v>0.0264691800884811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01755480579398676</v>
+        <v>0.01755480579398673</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03560768904406873</v>
+        <v>0.03560768904406859</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02260556911960585</v>
+        <v>0.02260556911960584</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02762199179382337</v>
+        <v>0.02762199179382335</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02776595211030159</v>
+        <v>0.02776595211030158</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03357695615210968</v>
+        <v>0.03357695615210961</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02762198570490278</v>
+        <v>0.02762198570490271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02774350104140044</v>
+        <v>0.02774350104140048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02776594977416881</v>
+        <v>0.0277659497741688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02762199179382337</v>
+        <v>0.02762199179382335</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02776594977416881</v>
+        <v>0.0277659497741688</v>
       </c>
       <c r="K7" t="n">
         <v>0.02477600593910513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02776594977416881</v>
+        <v>0.0277659497741688</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01393995873913699</v>
+        <v>0.01393995873913701</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01405668137238119</v>
+        <v>0.01405668137238121</v>
       </c>
       <c r="D8" t="n">
         <v>0.01236392325280498</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01405668137238119</v>
+        <v>0.01405668137238121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01405668137238119</v>
+        <v>0.01405668137238121</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01227253781414093</v>
+        <v>0.0122725378141409</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008314051774868127</v>
+        <v>0.008314051774868143</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01405668137238119</v>
+        <v>0.01405668137238121</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01399088483075399</v>
+        <v>0.013990884830754</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01512297878964874</v>
+        <v>0.01512297878964877</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002912223207905746</v>
+        <v>-0.002912223207905702</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01568503898656478</v>
+        <v>0.01568503898656481</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01540817162531533</v>
+        <v>0.01540817162531532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01504326816589676</v>
+        <v>0.01504326816589677</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01540817162531533</v>
+        <v>0.01540817162531532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01540817162531533</v>
+        <v>0.01540817162531532</v>
       </c>
       <c r="G9" t="n">
         <v>0.01499201345884942</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0134022687035109</v>
+        <v>0.01340226870351091</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01540817162531533</v>
+        <v>0.01540817162531532</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01570714987397139</v>
+        <v>0.01570714987397141</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01616700550703156</v>
+        <v>0.01616700550703157</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008836774366242169</v>
+        <v>0.0088367743662422</v>
       </c>
     </row>
   </sheetData>
@@ -6062,34 +6062,34 @@
         <v>0.05777764656677118</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05300955914536697</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09171357731877851</v>
+        <v>0.0917135773187784</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05300955914536697</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05300955914536697</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1140831256167158</v>
+        <v>0.1140831256167157</v>
       </c>
       <c r="H2" t="n">
-        <v>0.242208623219436</v>
+        <v>0.2422086232194359</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05300955914536697</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2085323700656422</v>
+        <v>0.2085323700656418</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08859345426517273</v>
+        <v>0.08859345426517259</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1439489888677226</v>
+        <v>0.3006221624800973</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005692137888009052</v>
+        <v>0.005692137888009049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005876651308820715</v>
+        <v>0.005876651308820709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005876651308820713</v>
+        <v>0.005876651308820708</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006493052249563096</v>
+        <v>0.006493052249563077</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00637804305110212</v>
+        <v>0.006378043051102113</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006514283297246301</v>
+        <v>0.006514283297246267</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01008132140334893</v>
+        <v>0.01008132140334891</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009698309706462762</v>
+        <v>0.009698309706462809</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01008750587453992</v>
+        <v>0.01682920653991103</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009258992387161647</v>
+        <v>0.009258992387161625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009896495789342125</v>
+        <v>0.009896495789342121</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01670020405965798</v>
+        <v>0.01006009035566571</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0171682969107473</v>
+        <v>0.01716829691074724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01658519486119701</v>
+        <v>0.009945081157204759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01682341969651335</v>
+        <v>0.01682341969651332</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009998124147940306</v>
+        <v>0.009998124147940298</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01013653690959573</v>
+        <v>0.0101365369095957</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.01077834638093547</v>
       </c>
       <c r="C5" t="n">
         <v>0.01064210613479133</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01077764625816932</v>
+        <v>0.01077764625816931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01063267299386828</v>
+        <v>0.01063267299386829</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01063267299386828</v>
+        <v>0.01063267299386829</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01075711533325229</v>
+        <v>0.01075711533325227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.01077834638093547</v>
       </c>
       <c r="I5" t="n">
         <v>0.01064210613479133</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.01077834638093547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.01077834638093547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.01077834638093547</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01724745956465504</v>
+        <v>0.01724745956465505</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02581122743185443</v>
+        <v>0.02581122743180729</v>
       </c>
       <c r="D6" t="n">
         <v>0.02775924416854228</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02343059776684546</v>
+        <v>0.0234305977668455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01738199055252118</v>
+        <v>0.01738199055252119</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02593267477260181</v>
+        <v>0.02593267477260185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0259539058202852</v>
+        <v>0.02595390582028522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02581766557414083</v>
+        <v>0.02581766557414087</v>
       </c>
       <c r="J6" t="n">
         <v>0.02595561688542515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0170857328556304</v>
+        <v>0.01708573285563039</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03504851695456854</v>
+        <v>0.03504851695456856</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02278823969557128</v>
+        <v>0.02278823969557124</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02797383967704006</v>
+        <v>0.02797383967704003</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02811008227367243</v>
+        <v>0.02811008227367241</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03411512787704465</v>
+        <v>0.03411512787704463</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02797383591207001</v>
+        <v>0.02797383591206999</v>
       </c>
       <c r="G7" t="n">
         <v>0.02808884887550104</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.02811007992318424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02797383967704006</v>
+        <v>0.02797383967704003</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.02811007992318424</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02140893252230331</v>
+        <v>0.02502658578343235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.02811007992318424</v>
       </c>
     </row>
     <row r="8">
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01655519313327906</v>
+        <v>0.01655519313327904</v>
       </c>
       <c r="C8" t="n">
         <v>0.01668880886496856</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01564424996522459</v>
+        <v>0.01564424996522457</v>
       </c>
       <c r="E8" t="n">
         <v>0.01668880886496856</v>
@@ -6314,22 +6314,22 @@
         <v>0.01668880886496856</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01519276132541995</v>
+        <v>0.01519276132541993</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01244897464464123</v>
+        <v>0.01244897464464122</v>
       </c>
       <c r="I8" t="n">
         <v>0.01668880886496856</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01338646563238576</v>
+        <v>0.01338646563238575</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01576779930636941</v>
+        <v>0.01576779930636939</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01176033169803861</v>
+        <v>0.01490039027648756</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01684472817750935</v>
+        <v>0.01684472817750933</v>
       </c>
       <c r="C9" t="n">
         <v>0.01690935248591564</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01647376270072155</v>
+        <v>0.01647376270072153</v>
       </c>
       <c r="E9" t="n">
         <v>0.01690935248591564</v>
@@ -6354,22 +6354,22 @@
         <v>0.01690935248591564</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01627882622430357</v>
+        <v>0.01627882622430356</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01517722619251929</v>
+        <v>0.01517722619251927</v>
       </c>
       <c r="I9" t="n">
         <v>0.01690935248591564</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01555579017290015</v>
+        <v>0.01555579017290014</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0165241325356438</v>
+        <v>0.01652413253564378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01617286402905779</v>
+        <v>0.01489634808732653</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06211109992219609</v>
+        <v>0.0621110999221961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07518351383021823</v>
+        <v>0.07518351383021819</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06125588512178417</v>
+        <v>0.06125588512178418</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07518351383021823</v>
+        <v>0.07518351383021819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07518351383021823</v>
+        <v>0.07518351383021819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08735374863258108</v>
+        <v>0.08735374863258041</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0447073388521087</v>
+        <v>0.04470733885210875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07518351383021823</v>
+        <v>0.07518351383021819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1569848479640742</v>
+        <v>0.1569848479640741</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09750887604861549</v>
+        <v>0.09750887604861559</v>
       </c>
       <c r="L2" t="n">
         <v>0.04809896448050024</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005726458914782743</v>
+        <v>0.005726458914782732</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005885029298118466</v>
+        <v>0.00588502929811846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005885029298118464</v>
+        <v>0.005885029298118467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00631167826779929</v>
+        <v>0.006311678267799273</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006211407700532553</v>
+        <v>0.00621140770053254</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006330199977848963</v>
+        <v>0.006330199977848983</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009928328009744865</v>
+        <v>0.01595977328055099</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009662555930617848</v>
+        <v>0.009662555930617824</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00988348727367583</v>
+        <v>0.009883432152001735</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00922705537728658</v>
+        <v>0.009227055377286568</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009775855600220158</v>
+        <v>0.009775855600220155</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009909806299695173</v>
+        <v>0.009909806299695189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01623805197279777</v>
+        <v>0.009870072367013132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009809535732428445</v>
+        <v>0.009809535732428428</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01029718166788823</v>
+        <v>0.01598956937640373</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009947232174158408</v>
+        <v>0.009947232174158434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009856272807822914</v>
+        <v>0.00985627280782291</v>
       </c>
     </row>
     <row r="5">
@@ -6578,25 +6578,25 @@
         <v>0.0101561329661378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01003734068882139</v>
+        <v>0.01003734068882137</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01015547461582264</v>
+        <v>0.01015547461582263</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01002887423747512</v>
+        <v>0.01002887423747511</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01002887423747512</v>
+        <v>0.01002887423747511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0101376112560881</v>
+        <v>0.01013761125608811</v>
       </c>
       <c r="H5" t="n">
         <v>0.0101561329661378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01003734068882139</v>
+        <v>0.01003734068882137</v>
       </c>
       <c r="J5" t="n">
         <v>0.0101561329661378</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01602703644671293</v>
+        <v>0.01602703644671295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02378042550252395</v>
+        <v>0.02378042550252394</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02553848719085043</v>
+        <v>0.02553848719085038</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02162633129047018</v>
+        <v>0.02162633129047015</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01615330396696871</v>
+        <v>0.01615330396696868</v>
       </c>
       <c r="G6" t="n">
         <v>0.02388642870060078</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02390495041064913</v>
+        <v>0.0239049504106491</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02378615813333404</v>
+        <v>0.02378615813333403</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02390649864561934</v>
+        <v>0.02390649864561931</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01588070015036552</v>
+        <v>0.01588070015036553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0321340902856617</v>
+        <v>0.03213409028566166</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02022469164244702</v>
+        <v>0.020224691642447</v>
       </c>
       <c r="C7" t="n">
         <v>0.02469566819537634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02481446457378962</v>
+        <v>0.02481446457378956</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02999216714106583</v>
+        <v>0.02999216714106579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02469566765705633</v>
+        <v>0.02469566765705632</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02479593876264307</v>
+        <v>0.02479593876264306</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.02481446047269273</v>
       </c>
       <c r="I7" t="n">
         <v>0.02469566819537634</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.02481446047269273</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0220472396347235</v>
+        <v>0.02204723963472349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.02481446047269273</v>
       </c>
     </row>
     <row r="8">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01632279811815221</v>
+        <v>0.0163227981181522</v>
       </c>
       <c r="C8" t="n">
         <v>0.01593297184592378</v>
@@ -6713,7 +6713,7 @@
         <v>0.01560341242310701</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0168220820345582</v>
+        <v>0.01682208203455821</v>
       </c>
       <c r="I8" t="n">
         <v>0.01593297184592378</v>
@@ -6725,7 +6725,7 @@
         <v>0.01530277069021867</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0173242488508222</v>
+        <v>0.01732424885082221</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6741,7 @@
         <v>0.01657744419468104</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01669322327785566</v>
+        <v>0.01669322327785567</v>
       </c>
       <c r="E9" t="n">
         <v>0.01657744419468104</v>
@@ -6750,7 +6750,7 @@
         <v>0.01657744419468104</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01642700502110404</v>
+        <v>0.01642700502110402</v>
       </c>
       <c r="H9" t="n">
         <v>0.01692994281243581</v>
@@ -6765,7 +6765,7 @@
         <v>0.01631044011873511</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01690663103871509</v>
+        <v>0.01713393800829329</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09571661922626916</v>
+        <v>0.09571661922626903</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08448659935808735</v>
+        <v>0.08448659935808742</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04612730253318388</v>
+        <v>0.04612730253318386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08448659935808735</v>
+        <v>0.08448659935808742</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08448659935808735</v>
+        <v>0.08448659935808742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08329153802561545</v>
+        <v>0.08329153802561604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04125026386576728</v>
+        <v>0.04125026386576734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08448659935808735</v>
+        <v>0.08448659935808742</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1376689234589983</v>
+        <v>0.137668923458998</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08921748421698548</v>
+        <v>0.08921748421698565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06691660886201187</v>
+        <v>0.03819448740465449</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005818423239062584</v>
+        <v>0.005818423239062591</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005971679511946055</v>
+        <v>0.005971679511946073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005971679511946056</v>
+        <v>0.005971679511946066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006330141299112337</v>
+        <v>0.006330141299112449</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0062288780109324</v>
+        <v>0.006228878010932424</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006348811740034554</v>
+        <v>0.00634881174003449</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01003040324760129</v>
+        <v>0.01003040324760099</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009788857697305725</v>
+        <v>0.009788857697305812</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01606798859511298</v>
+        <v>0.009903372253542304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00934546160465234</v>
+        <v>0.009345461604652347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009878024488260369</v>
+        <v>0.009878024488260388</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01001173280667889</v>
+        <v>0.01610356794062879</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01633782658345219</v>
+        <v>0.01633782658345228</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009910469518498973</v>
+        <v>0.009910469518499028</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01038667216976512</v>
+        <v>0.01609208355478795</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0100530594374876</v>
+        <v>0.01005305943748741</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009994568346965341</v>
+        <v>0.009994568346965339</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01013018487118362</v>
+        <v>0.01013018487118383</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01001025114208174</v>
+        <v>0.01001025114208176</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01012952430386274</v>
+        <v>0.01012952430386276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0100015774769322</v>
+        <v>0.01000157747693222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0100015774769322</v>
+        <v>0.01000157747693222</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01011151443026189</v>
+        <v>0.01011151443026179</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01013018487118362</v>
+        <v>0.01013018487118383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01001025114208174</v>
+        <v>0.01001025114208176</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01013018487118362</v>
+        <v>0.01013018487118383</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01013018487118362</v>
+        <v>0.01013018487118383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01013018487118362</v>
+        <v>0.01013018487118383</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01595893556384987</v>
+        <v>0.01595893556384975</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02364554836973719</v>
+        <v>0.02364554836977639</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02539138749015347</v>
+        <v>0.02539138749015342</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02150936584378638</v>
+        <v>0.02150936584378639</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01608186527288932</v>
+        <v>0.01608186527288933</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02375274786013501</v>
+        <v>0.02375274786013484</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02377141830105508</v>
+        <v>0.02377141830105511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02365148457195478</v>
+        <v>0.02365148457195483</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02377295367697367</v>
+        <v>0.02377295367697333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01581381468612547</v>
+        <v>0.01581381468612527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03193220978853401</v>
+        <v>0.03193220978853392</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01920370633677838</v>
+        <v>0.01920370633677836</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02338153752671159</v>
+        <v>0.02338153752671163</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02350147506928081</v>
+        <v>0.02350147506928082</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02834106998983689</v>
+        <v>0.02834106998983693</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02338153706799212</v>
+        <v>0.02338153706799215</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02348280081489161</v>
+        <v>0.02348280081489165</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02350147125581377</v>
+        <v>0.02350147125581372</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02338153752671159</v>
+        <v>0.02338153752671163</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02350147125581377</v>
+        <v>0.02350147125581372</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02101133098702885</v>
+        <v>0.02091030269608886</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02350147125581377</v>
+        <v>0.02350147125581372</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01472504082873562</v>
+        <v>0.01472504082873558</v>
       </c>
       <c r="C8" t="n">
         <v>0.01446062513950029</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01598267636968195</v>
+        <v>0.01598267636968188</v>
       </c>
       <c r="E8" t="n">
         <v>0.01446062513950029</v>
@@ -7106,22 +7106,22 @@
         <v>0.01446062513950029</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01504282129472929</v>
+        <v>0.01504282129472917</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01622197183521585</v>
+        <v>0.01622197183521583</v>
       </c>
       <c r="I8" t="n">
         <v>0.01446062513950029</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01382594598510549</v>
+        <v>0.01382594598510547</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01475911270687693</v>
+        <v>0.01475911270687692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01561086640779012</v>
+        <v>0.01561086640779007</v>
       </c>
     </row>
     <row r="9">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01565848301168999</v>
+        <v>0.01565848301169002</v>
       </c>
       <c r="C9" t="n">
         <v>0.01524985235520904</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01617073660688609</v>
+        <v>0.016170736606886</v>
       </c>
       <c r="E9" t="n">
         <v>0.01524985235520904</v>
@@ -7146,22 +7146,22 @@
         <v>0.01524985235520904</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01578380675405752</v>
+        <v>0.0157838067540575</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0162688841485823</v>
+        <v>0.01626888414858235</v>
       </c>
       <c r="I9" t="n">
         <v>0.01524985235520904</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01529349276651841</v>
+        <v>0.01529349276651844</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01567247807320497</v>
+        <v>0.01567247807320487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01602030003864897</v>
+        <v>0.01631029086020841</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1534878398514367</v>
+        <v>0.1534878398514368</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08220904438192</v>
+        <v>0.08220904438191992</v>
       </c>
       <c r="D2" t="n">
         <v>0.2641006983932205</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08220904438192</v>
+        <v>0.08220904438191992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08220904438192</v>
+        <v>0.08220904438191992</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2556727300849514</v>
+        <v>0.2556727300849509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6857262642249888</v>
+        <v>0.6857262642249898</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08220904438192</v>
+        <v>0.08220904438191992</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2475036427026193</v>
+        <v>0.2475036427026197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1264406264832021</v>
+        <v>0.1264406264832024</v>
       </c>
       <c r="L2" t="n">
-        <v>1.084763338907979</v>
+        <v>1.08476333890798</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006023630834756176</v>
+        <v>0.006023630834756192</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00621757444649711</v>
+        <v>0.006217574446497121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006217574446497109</v>
+        <v>0.006217574446497121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006921139261006529</v>
+        <v>0.006921139261006534</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006784113615635031</v>
+        <v>0.006784113615635049</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006946466718419812</v>
+        <v>0.00694646671841981</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01083275234754194</v>
+        <v>0.01083275234754195</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01027451913167801</v>
+        <v>0.01027451913167803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01100809176863979</v>
+        <v>0.01100809176863981</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009822421206978184</v>
+        <v>0.009822421206978167</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0106167070797858</v>
+        <v>0.01061670707978579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01844228721766851</v>
+        <v>0.01844228721766852</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01903247796293361</v>
+        <v>0.01903247796293362</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01067039924475716</v>
+        <v>0.01830526157229702</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01859552779040558</v>
+        <v>0.01859552779040559</v>
       </c>
       <c r="K4" t="n">
         <v>0.0106306422830478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01112029465798979</v>
+        <v>0.0111202946579898</v>
       </c>
     </row>
     <row r="5">
@@ -7370,25 +7370,25 @@
         <v>0.01181479784875141</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01165244474596664</v>
+        <v>0.01165244474596666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01181409113246687</v>
+        <v>0.01181409113246688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01164259189794137</v>
+        <v>0.0116425918979414</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01164259189794137</v>
+        <v>0.0116425918979414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01178947039133813</v>
+        <v>0.01178947039133812</v>
       </c>
       <c r="H5" t="n">
         <v>0.01181479784875141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01165244474596664</v>
+        <v>0.01165244474596666</v>
       </c>
       <c r="J5" t="n">
         <v>0.01181479784875141</v>
@@ -7410,34 +7410,34 @@
         <v>0.01882497275480009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02821319769038434</v>
+        <v>0.02821319769043754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03036397227600452</v>
+        <v>0.03036397227600451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02559990610179747</v>
+        <v>0.02559990610179751</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01896011338503146</v>
+        <v>0.0189601133850315</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02835688823576082</v>
+        <v>0.02835688823576084</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02838221569317532</v>
+        <v>0.0283822156931753</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02821986259038934</v>
+        <v>0.02821986259038938</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02838409396393608</v>
+        <v>0.02838409396393611</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01864744206062429</v>
+        <v>0.0186474420606243</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03836555510475935</v>
+        <v>0.03836555510475936</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02675646139488925</v>
+        <v>0.02675646139488926</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03294742574841936</v>
+        <v>0.03294742574841939</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0331097788308119</v>
+        <v>0.03310977883081195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0402790062675216</v>
+        <v>0.04027900626752165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03294741527245</v>
+        <v>0.03294741527245007</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03308445139379083</v>
+        <v>0.03308445139379088</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03310977885120413</v>
+        <v>0.03310977885120417</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03294742574841936</v>
+        <v>0.03294742574841939</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03310977885120413</v>
+        <v>0.03310977885120417</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02927929337598026</v>
+        <v>0.02942864175703584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03310977885120413</v>
+        <v>0.03310977885120417</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01481744814277614</v>
+        <v>0.01481744814277615</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01642818812970993</v>
+        <v>0.01642818812970992</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01209675814120394</v>
+        <v>0.01209675814120396</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01642818812970993</v>
+        <v>0.01642818812970992</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01642818812970993</v>
+        <v>0.01642818812970992</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01249339866725566</v>
+        <v>0.01249339866725565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00321072490988078</v>
+        <v>0.003210724909880783</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01642818812970993</v>
+        <v>0.01642818812970992</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01309175325110725</v>
+        <v>0.01309175325110726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01549155765742372</v>
+        <v>0.01549155765742371</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01387332067786568</v>
+        <v>-0.002927113009827059</v>
       </c>
     </row>
     <row r="9">
@@ -7530,16 +7530,16 @@
         <v>0.01645238876259898</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01705735825148182</v>
+        <v>0.01705735825148181</v>
       </c>
       <c r="D9" t="n">
-        <v>0.015344433392531</v>
+        <v>0.01534443339253101</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01705735825148182</v>
+        <v>0.01705735825148181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01705735825148182</v>
+        <v>0.01705735825148181</v>
       </c>
       <c r="G9" t="n">
         <v>0.0154844508487506</v>
@@ -7548,7 +7548,7 @@
         <v>0.01173908336007339</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01705735825148182</v>
+        <v>0.01705735825148181</v>
       </c>
       <c r="J9" t="n">
         <v>0.01575150759436398</v>
@@ -7557,7 +7557,7 @@
         <v>0.01672709738115639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01607114857218256</v>
+        <v>0.009241213744327211</v>
       </c>
     </row>
   </sheetData>
@@ -7646,34 +7646,34 @@
         <v>0.03667350620756225</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06082485173358163</v>
+        <v>0.06082485173358164</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2219569749899298</v>
+        <v>0.22195697498993</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06082485173358163</v>
+        <v>0.06082485173358164</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06082485173358163</v>
+        <v>0.06082485173358164</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1588652974792444</v>
+        <v>0.1588652974792445</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1013099793809688</v>
+        <v>0.1013099793809687</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06082485173358163</v>
+        <v>0.06082485173358164</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1766579140926515</v>
+        <v>0.1766579140926513</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05636705571802671</v>
+        <v>0.05636705571802663</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5938535837851513</v>
+        <v>0.07112096148045337</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00645654977087865</v>
+        <v>0.006456549770878642</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005764919539658987</v>
+        <v>0.005764919539658974</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00645654977087865</v>
+        <v>0.006456549770878642</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005930473637661463</v>
+        <v>0.005930473637661455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005930473637661463</v>
+        <v>0.005930473637661453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006434611436784773</v>
+        <v>0.00643461143678475</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00645654977087864</v>
+        <v>0.006456549770878642</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006315982616431856</v>
+        <v>0.006315982616431845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00645654977087865</v>
+        <v>0.006456549770878642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00645654977087865</v>
+        <v>0.006456549770878642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00645654977087865</v>
+        <v>0.006456549770878642</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01012478791750581</v>
+        <v>0.01672355920436598</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009721800302615487</v>
+        <v>0.009721800302615465</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01036939821416523</v>
+        <v>0.0103693982141645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009284522403174351</v>
+        <v>0.009284522403174279</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00994708106123582</v>
+        <v>0.00994708106123581</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01670162087027214</v>
+        <v>0.01010284958341192</v>
       </c>
       <c r="H4" t="n">
         <v>0.01704307279128361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01658299204991922</v>
+        <v>0.01658299204991918</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01677861344616087</v>
+        <v>0.01052242894925218</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009986769853961439</v>
+        <v>0.009986769853961458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01024309775679528</v>
+        <v>0.01024309775679527</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01057355664955255</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="C5" t="n">
         <v>0.01043298949510575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01057289860157948</v>
+        <v>0.01057289860157944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01042305497707065</v>
+        <v>0.01042305497707066</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01042305497707065</v>
+        <v>0.01042305497707066</v>
       </c>
       <c r="G5" t="n">
         <v>0.01055161831545866</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01057355664955255</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="I5" t="n">
         <v>0.01043298949510575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01057355664955255</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01057355664955255</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01057355664955255</v>
+        <v>0.01057355664955254</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01676004885832681</v>
+        <v>0.01676004885832682</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02494207484728026</v>
+        <v>0.02494207484732297</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02681689558236894</v>
+        <v>0.02681689558236888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02266457716610811</v>
+        <v>0.0226645771661081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01687798460820281</v>
+        <v>0.01687798460820277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02506775185569794</v>
+        <v>0.02506775185569792</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02508969018979103</v>
+        <v>0.02508969018979101</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02494912303534502</v>
+        <v>0.02494912303534499</v>
       </c>
       <c r="J6" t="n">
         <v>0.02509132720194606</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01660532149422986</v>
+        <v>0.01660532149422985</v>
       </c>
       <c r="L6" t="n">
         <v>0.03379069707284486</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02186190842324578</v>
+        <v>0.02186190842324576</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02675778703371955</v>
+        <v>0.02675778703371953</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02689835960689411</v>
+        <v>0.02689835960689412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03256974118757736</v>
+        <v>0.03256974118757735</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02675778513981859</v>
+        <v>0.02675778513981857</v>
       </c>
       <c r="G7" t="n">
         <v>0.02687641585407247</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02689835418816639</v>
+        <v>0.02689835418816634</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02675778703371955</v>
+        <v>0.02675778703371953</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02689835418816639</v>
+        <v>0.02689835418816634</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02398022001141854</v>
+        <v>0.0205565685633247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02689835418816639</v>
+        <v>0.02689835418816634</v>
       </c>
     </row>
     <row r="8">
@@ -7883,19 +7883,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01718431818131128</v>
+        <v>0.01718431818131129</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01647147268226702</v>
+        <v>0.01647147268226701</v>
       </c>
       <c r="D8" t="n">
         <v>0.01211325435319017</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01647147268226702</v>
+        <v>0.01647147268226701</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01647147268226702</v>
+        <v>0.01647147268226701</v>
       </c>
       <c r="G8" t="n">
         <v>0.01400612823544513</v>
@@ -7904,16 +7904,16 @@
         <v>0.01568466055491712</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01647147268226702</v>
+        <v>0.01647147268226701</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0139766883916565</v>
+        <v>0.01397668839165649</v>
       </c>
       <c r="K8" t="n">
         <v>0.01663642694961523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01647348020895195</v>
+        <v>0.005211535985127114</v>
       </c>
     </row>
     <row r="9">
@@ -7926,34 +7926,34 @@
         <v>0.01719903186195467</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01687081781305346</v>
+        <v>0.01687081781305345</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01513377380815652</v>
+        <v>0.01513377380815651</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01687081781305346</v>
+        <v>0.01687081781305345</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01687081781305346</v>
+        <v>0.01687081781305345</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01588955400618786</v>
+        <v>0.01588955400618787</v>
       </c>
       <c r="H9" t="n">
         <v>0.01659030866283574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01687081781305346</v>
+        <v>0.01687081781305345</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01589408776261564</v>
+        <v>0.01589408776261563</v>
       </c>
       <c r="K9" t="n">
         <v>0.01697594698841716</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01691058914450757</v>
+        <v>0.0123322175363578</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3200248077715527</v>
+        <v>0.3200248077715542</v>
       </c>
       <c r="C2" t="n">
         <v>0.1725035862797109</v>
       </c>
       <c r="D2" t="n">
-        <v>0.646200933207538</v>
+        <v>0.6462009332075392</v>
       </c>
       <c r="E2" t="n">
         <v>0.1725035862797109</v>
@@ -530,22 +530,22 @@
         <v>0.1725035862797109</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4239741791252252</v>
+        <v>0.4239741791252248</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9202012239982706</v>
+        <v>0.9202012239982696</v>
       </c>
       <c r="I2" t="n">
         <v>0.1725035862797109</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3995039208146738</v>
+        <v>0.3995039208146753</v>
       </c>
       <c r="K2" t="n">
         <v>0.1795558205968481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3443196001506525</v>
+        <v>1.390530346894881</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007470873836679305</v>
+        <v>0.0074708738366793</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007685811386972575</v>
+        <v>0.007685811386972561</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007685811386972566</v>
+        <v>0.007685811386972561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008073727342082542</v>
+        <v>0.008073727342082612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007944096396387556</v>
+        <v>0.007944096396387577</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008097900671048821</v>
+        <v>0.008097900671048828</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01290651139053427</v>
+        <v>0.01290651139053425</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01233290893884333</v>
+        <v>0.0123329089388432</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01355876032107857</v>
+        <v>0.01355884042104223</v>
       </c>
       <c r="E4" t="n">
         <v>0.01179987543123616</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01273679224207376</v>
+        <v>0.01273679224207375</v>
       </c>
       <c r="G4" t="n">
         <v>0.02224109456465918</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02284888807473532</v>
+        <v>0.02284888807473538</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01275270711587302</v>
+        <v>0.02211146361896416</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01342832128782584</v>
+        <v>0.02226539882086545</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01262172279810776</v>
+        <v>0.01262172279810774</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01328506123010094</v>
+        <v>0.01328506123010095</v>
       </c>
     </row>
     <row r="5">
@@ -638,25 +638,25 @@
         <v>0.01424437823063958</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01409057395597836</v>
+        <v>0.01409057395597834</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01424359705562577</v>
+        <v>0.01424359705562575</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01408095937872991</v>
+        <v>0.01408095937872988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01408095937872991</v>
+        <v>0.01408095937872988</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01422020490167338</v>
+        <v>0.01422020490167337</v>
       </c>
       <c r="H5" t="n">
         <v>0.01424437823063958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01409057395597836</v>
+        <v>0.01409057395597834</v>
       </c>
       <c r="J5" t="n">
         <v>0.01424437823063958</v>
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02254152165706281</v>
+        <v>0.02254152165706283</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03391187091875002</v>
+        <v>0.03391187091881299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03646246913400743</v>
+        <v>0.03646246913400731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03075892031486318</v>
+        <v>0.03075892031486312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02274793435741462</v>
+        <v>0.02274793435741453</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03404745340566802</v>
+        <v>0.03404745340566809</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03407162673463501</v>
+        <v>0.03407162673463469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03391782245997296</v>
+        <v>0.03391782245997305</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03407389272907212</v>
+        <v>0.03407389272907204</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02232734403580607</v>
+        <v>0.02232734403580608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04611578561840515</v>
+        <v>0.04611578561840538</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0383175355680457</v>
+        <v>0.03831753556804572</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04754518483410006</v>
+        <v>0.04754518483409999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04769899155617485</v>
+        <v>0.0476989915561748</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05837116993258098</v>
+        <v>0.05837116993258096</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0475451723693248</v>
+        <v>0.04754517236932478</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04767481577979515</v>
+        <v>0.0476748157797951</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04769898910876132</v>
+        <v>0.04769898910876127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04754518483410006</v>
+        <v>0.04754518483409999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04769898910876132</v>
+        <v>0.04769898910876127</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04226333911283266</v>
+        <v>0.03588606388314973</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04769898910876132</v>
+        <v>0.04769898910876127</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0124018484606143</v>
+        <v>0.01240184846061422</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01592179478394064</v>
+        <v>0.01592179478394062</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005601250150773655</v>
+        <v>0.005601250150773633</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01592179478394064</v>
+        <v>0.01592179478394062</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01592179478394064</v>
+        <v>0.01592179478394062</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0105302617813281</v>
+        <v>0.01053026178132812</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001956564190251733</v>
+        <v>0.001956564190251749</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01592179478394064</v>
+        <v>0.01592179478394062</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01134161377967443</v>
+        <v>0.01134161377967442</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561093601513003</v>
+        <v>0.01561093601513007</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01281113818404144</v>
+        <v>0.01281113818404143</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01603646216243223</v>
+        <v>0.01603646216243224</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01759329644133611</v>
+        <v>0.0175932964413361</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01326698429419802</v>
+        <v>0.01326698429419801</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01759329644133611</v>
+        <v>0.0175932964413361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01759329644133611</v>
+        <v>0.0175932964413361</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01524896978316087</v>
+        <v>0.01524896978316085</v>
       </c>
       <c r="H9" t="n">
         <v>0.01179827847075925</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01759329644133611</v>
+        <v>0.0175932964413361</v>
       </c>
       <c r="J9" t="n">
         <v>0.01560765829087672</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01734369647960354</v>
+        <v>0.01734369647960353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01620798049566416</v>
+        <v>0.008511433752000282</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03171765838396694</v>
+        <v>0.03171765838396698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07383882030974856</v>
+        <v>0.07383882030974867</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06120226852768303</v>
+        <v>0.06120226852768299</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07383882030974856</v>
+        <v>0.07383882030974867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07383882030974856</v>
+        <v>0.07383882030974867</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08995692349474337</v>
+        <v>0.08995692349474327</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06651331966262701</v>
+        <v>0.06651331966262716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07383882030974856</v>
+        <v>0.07383882030974867</v>
       </c>
       <c r="J2" t="n">
         <v>0.1220467140547726</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0518862186017356</v>
+        <v>0.05188621860173552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03961091659524843</v>
+        <v>0.0396109165952484</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005789862899941019</v>
+        <v>0.005789862899941017</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005944703782980197</v>
+        <v>0.005944703782980213</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0059447037829802</v>
+        <v>0.005944703782980208</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006317830237695906</v>
+        <v>0.006317830237695896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006213388540333771</v>
+        <v>0.006213388540333786</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00633709376935649</v>
+        <v>0.006337093769356484</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01599675171545213</v>
+        <v>0.009950433764423876</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009718103612711875</v>
+        <v>0.009718103612711996</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01605165463394411</v>
+        <v>0.01605165463394408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009276655793716474</v>
+        <v>0.009276655793716417</v>
       </c>
       <c r="F4" t="n">
         <v>0.009822441168807667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0099311702327633</v>
+        <v>0.01597748818379158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01634702124659335</v>
+        <v>0.01634702124659337</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009826728535401159</v>
+        <v>0.009826728535401169</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01607284406079593</v>
+        <v>0.01033386821761948</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009927643566777538</v>
+        <v>0.009927643566777403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009949422574165773</v>
+        <v>0.009949422574165786</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01016978460595652</v>
+        <v>0.01016978460595656</v>
       </c>
       <c r="C5" t="n">
         <v>0.01004607937693381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01016912436841816</v>
+        <v>0.0101691243684182</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003730854149145</v>
+        <v>0.01003730854149147</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003730854149145</v>
+        <v>0.01003730854149147</v>
       </c>
       <c r="G5" t="n">
         <v>0.01015052107429594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01016978460595652</v>
+        <v>0.01016978460595656</v>
       </c>
       <c r="I5" t="n">
         <v>0.01004607937693381</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01016978460595652</v>
+        <v>0.01016978460595656</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01016978460595652</v>
+        <v>0.01016978460595656</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01016978460595652</v>
+        <v>0.01016978460595656</v>
       </c>
     </row>
     <row r="6">
@@ -1074,34 +1074,34 @@
         <v>0.01604999951170839</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02381128813943052</v>
+        <v>0.0238112881394702</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02557725918634789</v>
+        <v>0.02557725918634797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0216536379315042</v>
+        <v>0.02165363793150426</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01617158868063232</v>
+        <v>0.01617158868063236</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02392174378189796</v>
+        <v>0.02392174378189804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02394100731355833</v>
+        <v>0.0239410073135584</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02381730208453587</v>
+        <v>0.02381730208453592</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02394255812184683</v>
+        <v>0.02394255812184684</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01590341999060047</v>
+        <v>0.01590341999060053</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03218382479716096</v>
+        <v>0.03218382479716106</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01928206968125573</v>
+        <v>0.01928206968125574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02348679527104197</v>
+        <v>0.023486795271042</v>
       </c>
       <c r="D7" t="n">
         <v>0.02361050431112975</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02848171503665613</v>
+        <v>0.02848171503665616</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02348679441755741</v>
+        <v>0.02348679441755738</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02359123696840407</v>
+        <v>0.02359123696840409</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0236105005000647</v>
+        <v>0.02361050050006472</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02348679527104197</v>
+        <v>0.023486795271042</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0236105005000647</v>
+        <v>0.02361050050006472</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02110259228750653</v>
+        <v>0.02110259228750656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0236105005000647</v>
+        <v>0.02361050050006472</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01635101157193903</v>
+        <v>0.01635101157193901</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01473413886682382</v>
+        <v>0.01473413886682383</v>
       </c>
       <c r="D8" t="n">
         <v>0.01556213059460178</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01473413886682382</v>
+        <v>0.01473413886682383</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01473413886682382</v>
+        <v>0.01473413886682383</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01486816337811962</v>
+        <v>0.01486816337811961</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01562506165035029</v>
+        <v>0.01562506165035026</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01473413886682382</v>
+        <v>0.01473413886682383</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01427719688578537</v>
+        <v>0.01427719688578538</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01577357398897924</v>
+        <v>0.0157735739889792</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01628248934125439</v>
+        <v>0.01628248934125434</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01631080721356142</v>
+        <v>0.01631080721356141</v>
       </c>
       <c r="C9" t="n">
         <v>0.01536065578959292</v>
@@ -1206,22 +1206,22 @@
         <v>0.01536065578959292</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01570091960004305</v>
+        <v>0.01570091960004304</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01601638261525834</v>
+        <v>0.01601638261525831</v>
       </c>
       <c r="I9" t="n">
         <v>0.01536065578959292</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01546718223961135</v>
+        <v>0.01546718223961134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01607568376373348</v>
+        <v>0.01607568376373346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01611551754937152</v>
+        <v>0.01628341755470585</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.069321639098014</v>
+        <v>0.06932163909801392</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1056636416547756</v>
+        <v>0.1056636416547755</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1853413815752255</v>
+        <v>0.1853413815752257</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0912956048891136</v>
+        <v>0.09129560488911352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0912956048891136</v>
+        <v>0.09129560488911352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1677645278485816</v>
+        <v>0.1677645278485818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4009586779900271</v>
+        <v>0.400958677990027</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0912956048891136</v>
+        <v>0.09129560488911352</v>
       </c>
       <c r="J2" t="n">
-        <v>0.318414144169999</v>
+        <v>0.3184141441699984</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0842501575992254</v>
+        <v>0.0842501575992252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2755977986354499</v>
+        <v>0.2755977986354497</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006443548947301356</v>
+        <v>0.006443548947301362</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00554862467762386</v>
+        <v>0.005548624677623853</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006443548947301359</v>
+        <v>0.006443548947301358</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006056539126451183</v>
+        <v>0.006056539126451196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006056539126451184</v>
+        <v>0.006056539126451196</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006419338588373675</v>
+        <v>0.006419338588373701</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006443548947301359</v>
+        <v>0.006443548947301361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006287756124814337</v>
+        <v>0.006287756124814338</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006443548947301359</v>
+        <v>0.006443548947301361</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006443548947301359</v>
+        <v>0.006443548947301358</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006443548947301359</v>
+        <v>0.006443548947301358</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01015982706784131</v>
+        <v>0.01705216493481322</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009906801803048019</v>
+        <v>0.009906801803048032</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01026151495858555</v>
+        <v>0.01026157793173455</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009353998697936581</v>
+        <v>0.00935399869793657</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009991520519516982</v>
+        <v>0.009991520519516968</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01702795457588554</v>
+        <v>0.01013561670891362</v>
       </c>
       <c r="H4" t="n">
         <v>0.01767201654512473</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0168963721123262</v>
+        <v>0.01000403424535427</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01711872710094958</v>
+        <v>0.01711872710094959</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009992369460111538</v>
+        <v>0.009992369460111537</v>
       </c>
       <c r="L4" t="n">
         <v>0.01019802931563762</v>
@@ -1430,25 +1430,25 @@
         <v>0.01108280400470998</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01106944484616778</v>
+        <v>0.01106944484616779</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0110821587685123</v>
+        <v>0.01108215876851229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01092773090313197</v>
+        <v>0.01092773090313196</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01092773090313197</v>
+        <v>0.01092773090313196</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01105859364578227</v>
+        <v>0.01105859364578228</v>
       </c>
       <c r="H5" t="n">
         <v>0.01108280400470998</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01092701118222294</v>
+        <v>0.01092701118222295</v>
       </c>
       <c r="J5" t="n">
         <v>0.01108280400470998</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01782615304011395</v>
+        <v>0.017826153040114</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02702522554889991</v>
+        <v>0.02702522554889992</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02894487379351912</v>
+        <v>0.02894487379351923</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02436367348920614</v>
+        <v>0.02436367348920617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.017963090146407</v>
+        <v>0.01796309014640703</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02701108730493802</v>
+        <v>0.02701108730493804</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02703529766388021</v>
+        <v>0.02703529766388028</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02687950484137865</v>
+        <v>0.02687950484137867</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02703710752303072</v>
+        <v>0.0270371075230308</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01765508845085932</v>
+        <v>0.01765508845085936</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03665501927809683</v>
+        <v>0.03665501927809692</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02378384936160443</v>
+        <v>0.02378384936160442</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02942643195259484</v>
+        <v>0.02942643195259483</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02943979348168604</v>
+        <v>0.02943979348168608</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03581083117551995</v>
+        <v>0.03581083117551992</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02928399340090545</v>
+        <v>0.02928399340090544</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02941558075220939</v>
+        <v>0.0294155807522094</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02943979111113706</v>
+        <v>0.02943979111113709</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02928399828865007</v>
+        <v>0.02928399828865006</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02943979111113706</v>
+        <v>0.02943979111113709</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02616271724590456</v>
+        <v>0.02616271724590455</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02943979111113706</v>
+        <v>0.0294397911111371</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03390945247101711</v>
+        <v>0.03390945247101712</v>
       </c>
       <c r="C8" t="n">
         <v>0.01058904246727309</v>
@@ -1556,13 +1556,13 @@
         <v>0.01498340745328789</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01365445537663141</v>
+        <v>0.0136544553766314</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01365445537663141</v>
+        <v>0.0136544553766314</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225089245784048</v>
+        <v>0.01225089245784049</v>
       </c>
       <c r="H8" t="n">
         <v>0.01108058176715215</v>
@@ -1571,10 +1571,10 @@
         <v>0.01365445537663141</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0137478403333829</v>
+        <v>0.01374784033338289</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01908199363347011</v>
+        <v>0.01908199363347013</v>
       </c>
       <c r="L8" t="n">
         <v>0.01512965722338236</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03407704643693238</v>
+        <v>0.03407704643693241</v>
       </c>
       <c r="C9" t="n">
         <v>0.01156402845446723</v>
@@ -1596,28 +1596,28 @@
         <v>0.01698828865164179</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01441527643810384</v>
+        <v>0.01441527643810383</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01441527643810384</v>
+        <v>0.01441527643810383</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01400168392118263</v>
+        <v>0.01400168392118264</v>
       </c>
       <c r="H9" t="n">
         <v>0.01540606337088974</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01441527643810384</v>
+        <v>0.01441527643810383</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01733782857452567</v>
+        <v>0.01733782857452565</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0196701330593999</v>
+        <v>0.01967013305939991</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0178510731600291</v>
+        <v>0.01785107316002911</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03566263228073641</v>
+        <v>0.03566263228073646</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07282172610564898</v>
+        <v>0.07282172610564916</v>
       </c>
       <c r="D2" t="n">
         <v>0.127972620645674</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05700351401274972</v>
+        <v>0.05700351401274982</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05700351401274972</v>
+        <v>0.05700351401274982</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1026380547335806</v>
+        <v>0.1026380547335815</v>
       </c>
       <c r="H2" t="n">
-        <v>0.203133363280417</v>
+        <v>0.2031333632804171</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05700351401274972</v>
+        <v>0.05700351401274982</v>
       </c>
       <c r="J2" t="n">
         <v>0.2046314211194552</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04265089424436948</v>
+        <v>0.04265089424436951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09325557312266905</v>
+        <v>0.09325557312266913</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006142162204126357</v>
+        <v>0.006142162204126492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005366565638422487</v>
+        <v>0.005366565638422484</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006142162204126357</v>
+        <v>0.006142162204126492</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006369052987261397</v>
+        <v>0.006369052987261419</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006369052987261405</v>
+        <v>0.006369052987261419</v>
       </c>
       <c r="G3" t="n">
         <v>0.006120303489705606</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006142162204126357</v>
+        <v>0.006142162204126492</v>
       </c>
       <c r="I3" t="n">
         <v>0.006001591968932133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006142162204126356</v>
+        <v>0.006142162204126492</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006142162204126357</v>
+        <v>0.006142162204126492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006142162204126357</v>
+        <v>0.006142162204126492</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01611586754294735</v>
+        <v>0.01611586754294746</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009590466250090492</v>
+        <v>0.00959046625009034</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01617797826330646</v>
+        <v>0.01617797826330676</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009139822477565286</v>
+        <v>0.00913982247756529</v>
       </c>
       <c r="F4" t="n">
         <v>0.009687876379596901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009768880688659104</v>
+        <v>0.01609400882852658</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01672202530411301</v>
+        <v>0.0167220253041131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009650169167885692</v>
+        <v>0.00965016916788569</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01021792016524649</v>
+        <v>0.01021792016524645</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009709443606204186</v>
+        <v>0.009709443606204241</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009765505509768792</v>
+        <v>0.009765505509768868</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01030576999393315</v>
+        <v>0.01030576999393318</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01029407269388479</v>
+        <v>0.01029407269388478</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01030517064710313</v>
+        <v>0.01030517064710297</v>
       </c>
       <c r="E5" t="n">
         <v>0.01019978632987534</v>
@@ -1838,22 +1838,22 @@
         <v>0.01019978632987534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01028391127951232</v>
+        <v>0.01028391127951228</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01030576999393315</v>
+        <v>0.01030576999393318</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01016519975873882</v>
+        <v>0.01016519975873881</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01030576999393315</v>
+        <v>0.01030576999393318</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01030576999393315</v>
+        <v>0.01030576999393318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01030576999393315</v>
+        <v>0.01030576999393318</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0165605538275794</v>
+        <v>0.01656055382757956</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02506293196854257</v>
+        <v>0.0250629319684797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02679728182882801</v>
+        <v>0.02679728182882806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02261135152164115</v>
+        <v>0.0226113515216412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01670973315043241</v>
+        <v>0.01670973315043243</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02501732415053142</v>
+        <v>0.02501732415053141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02503918286499117</v>
+        <v>0.02503918286499119</v>
       </c>
       <c r="I6" t="n">
-        <v>0.024898612629758</v>
+        <v>0.02489861262975792</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02504084915588866</v>
+        <v>0.02504084915588883</v>
       </c>
       <c r="K6" t="n">
         <v>0.01640305894047098</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03389581986358133</v>
+        <v>0.03389581986358139</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02021832057680234</v>
+        <v>0.02021832057680241</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0249085476199974</v>
+        <v>0.02490854761999739</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02492024798986105</v>
+        <v>0.02492024798986126</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03020559552837912</v>
+        <v>0.03020559552837916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02477967234347246</v>
+        <v>0.0247796723434725</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02489838620562482</v>
+        <v>0.02489838620562492</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02492024492004566</v>
+        <v>0.02492024492004585</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02477967468485143</v>
+        <v>0.02477967468485144</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02492024492004566</v>
+        <v>0.02492024492004585</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02219593278084145</v>
+        <v>0.02219593278084146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02492024492004566</v>
+        <v>0.02492024492004585</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0344650772990104</v>
+        <v>0.03446507729901041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01101234550741959</v>
+        <v>0.0110123455074196</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01593926284127368</v>
+        <v>0.01593926284127374</v>
       </c>
       <c r="E8" t="n">
         <v>0.01425414714373325</v>
@@ -1958,7 +1958,7 @@
         <v>0.01425414714373325</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01342116340602262</v>
+        <v>0.0134211634060226</v>
       </c>
       <c r="H8" t="n">
         <v>0.01467646645691796</v>
@@ -1970,10 +1970,10 @@
         <v>0.01615871317859079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01984327464660147</v>
+        <v>0.01984327464660158</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01604831699786577</v>
+        <v>0.01604831699786582</v>
       </c>
     </row>
     <row r="9">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03421497376061381</v>
+        <v>0.03421497376061383</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01160803455120231</v>
+        <v>0.01160803455120232</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0172600601769782</v>
+        <v>0.01726006017697815</v>
       </c>
       <c r="E9" t="n">
         <v>0.01459582287656699</v>
@@ -1998,22 +1998,22 @@
         <v>0.01459582287656699</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01438530467922005</v>
+        <v>0.01438530467922006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01674959089044842</v>
+        <v>0.01674959089044853</v>
       </c>
       <c r="I9" t="n">
         <v>0.01459582287656699</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01841480783154353</v>
+        <v>0.01841480783154359</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01989940088742895</v>
+        <v>0.01989940088742899</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01671127490148886</v>
+        <v>0.01671127490148891</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0175440042942966</v>
+        <v>0.01754400429429657</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05426225857546736</v>
+        <v>0.05426225857546724</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08315767618002021</v>
+        <v>0.08315767618002008</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02437973236168147</v>
+        <v>0.02437973236168144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02437973236168147</v>
+        <v>0.02437973236168144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06108203974178917</v>
+        <v>0.06108203974178943</v>
       </c>
       <c r="H2" t="n">
-        <v>0.101655928640724</v>
+        <v>0.1016559286407238</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02437973236168147</v>
+        <v>0.02437973236168144</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09880409661338993</v>
+        <v>0.09880409661338992</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02331256625590565</v>
+        <v>0.02331256625590554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03768973529605318</v>
+        <v>0.03768973529605314</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690678</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00525365052954881</v>
+        <v>0.005253650529548798</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006178528710492405</v>
+        <v>0.006178528710492401</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006178528710492406</v>
+        <v>0.006178528710492403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005977871753131912</v>
+        <v>0.005977871753131908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00586808053441685</v>
+        <v>0.005868080534416852</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690677</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005998144059690689</v>
+        <v>0.005998144059690677</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009631053651396299</v>
+        <v>0.009631053651396266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009470729881832037</v>
+        <v>0.009470729881832068</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009666119466643018</v>
+        <v>0.00966605218299213</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008976249033266636</v>
+        <v>0.008976249033266583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009529526621254119</v>
+        <v>0.009529526621254093</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01579075941304911</v>
+        <v>0.0157907594130491</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0163715021433046</v>
+        <v>0.01637150214330458</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01568096819433404</v>
+        <v>0.01568096819433401</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01586317281572167</v>
+        <v>0.01586317281572165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009609066119793216</v>
+        <v>0.009609066119792861</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00958448914439646</v>
+        <v>0.009584489144395816</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00995252126451189</v>
+        <v>0.009952521264511882</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009942077908646971</v>
+        <v>0.009942077908646969</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009951924278397983</v>
+        <v>0.009951924278397958</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009866750908424982</v>
+        <v>0.009866750908424966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009866750908424982</v>
+        <v>0.009866750908424966</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009932248957953123</v>
+        <v>0.009932248957953112</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00995252126451189</v>
+        <v>0.009952521264511882</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009822457739238072</v>
+        <v>0.009822457739238059</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00995252126451189</v>
+        <v>0.009952521264511882</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00995252126451189</v>
+        <v>0.009952521264511882</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00995252126451189</v>
+        <v>0.009952521264511882</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01608042374477832</v>
+        <v>0.0160804237447783</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02437325926192489</v>
+        <v>0.02437325926199103</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02605148430024167</v>
+        <v>0.02605148430024164</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02199012290741786</v>
+        <v>0.02199012290741785</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01623892387970494</v>
+        <v>0.01623892387970491</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02431873988066172</v>
+        <v>0.02431873988066171</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02433901218725544</v>
+        <v>0.02433901218725545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02420894866194664</v>
+        <v>0.02420894866194663</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02434063523280312</v>
+        <v>0.02434063523280307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0159270162247915</v>
+        <v>0.01592701622479147</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03296579838392251</v>
+        <v>0.03296579838392246</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01816480953167702</v>
+        <v>0.018164809531677</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0223253904954116</v>
+        <v>0.02232539049541153</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02233583700018858</v>
+        <v>0.02233583700018852</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02701904510657765</v>
+        <v>0.02701904510657758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02220576897336919</v>
+        <v>0.02220576897336915</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02231556154471775</v>
+        <v>0.02231556154471766</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02233583385127651</v>
+        <v>0.0223358338512765</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02220577032600268</v>
+        <v>0.02220577032600264</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02233583385127651</v>
+        <v>0.0223358338512765</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01708376889156326</v>
+        <v>0.01982107833891018</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02233583385127651</v>
+        <v>0.0223358338512765</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03476870185255931</v>
+        <v>0.03476870185255929</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01120204079907875</v>
+        <v>0.01120204079907874</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01681738368983918</v>
+        <v>0.01681738368983917</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01399038906330049</v>
+        <v>0.01399038906330048</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01399038906330049</v>
+        <v>0.01399038906330048</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01377671342028827</v>
+        <v>0.01377671342028826</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01664514933455589</v>
+        <v>0.01664514933455588</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01399038906330049</v>
+        <v>0.01399038906330048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01538726844001868</v>
+        <v>0.01538726844001866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02010964492375659</v>
+        <v>0.02010964492375656</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01688115927417428</v>
+        <v>0.01688115927417427</v>
       </c>
     </row>
     <row r="9">
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03426779005814695</v>
+        <v>0.03426779005814697</v>
       </c>
       <c r="C9" t="n">
         <v>0.0115417511828926</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01749476274607567</v>
+        <v>0.01749476274607566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01388269691088408</v>
+        <v>0.01388269691088407</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01388269691088408</v>
+        <v>0.01388269691088407</v>
       </c>
       <c r="G9" t="n">
         <v>0.0141684320445066</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01742646914716202</v>
+        <v>0.01742646914716201</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01388269691088408</v>
+        <v>0.01388269691088407</v>
       </c>
       <c r="J9" t="n">
         <v>0.01624112189747666</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01989176822099889</v>
+        <v>0.01989176822099888</v>
       </c>
       <c r="L9" t="n">
         <v>0.01685488738050324</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02443023302757102</v>
+        <v>0.02443023302757101</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02013607259759962</v>
+        <v>0.02013607259759961</v>
       </c>
       <c r="D2" t="n">
-        <v>0.10267204072022</v>
+        <v>0.1026720407202198</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05311527490082869</v>
+        <v>0.05311527490082856</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05311527490082869</v>
+        <v>0.05311527490082856</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1090403211372291</v>
+        <v>0.1090403211372298</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3136411234500878</v>
+        <v>0.3136411234500877</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05311527490082869</v>
+        <v>0.05311527490082856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2987465353176094</v>
+        <v>0.2987465353176096</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05876428188220997</v>
+        <v>0.05876428188221008</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2573940493262492</v>
+        <v>0.257394049326249</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005189054282197529</v>
+        <v>0.005189054282197531</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005938217678950687</v>
+        <v>0.005938217678950697</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005938217678950688</v>
+        <v>0.005938217678950697</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006075155434047162</v>
+        <v>0.006075155434047164</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005948834553767884</v>
+        <v>0.00594883455376789</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006098353289801022</v>
+        <v>0.006098353289801029</v>
       </c>
     </row>
     <row r="4">
@@ -2578,34 +2578,34 @@
         <v>0.009570606516941639</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009255556826543143</v>
+        <v>0.009255556826542981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009603556089452245</v>
+        <v>0.009603491696131332</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008844461088363738</v>
+        <v>0.008844461088363684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009426063025988703</v>
+        <v>0.009426063025988701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009547408661187771</v>
+        <v>0.00954740866118778</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01667374375391157</v>
+        <v>0.01667374375391158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009421087780908497</v>
+        <v>0.0159703997537597</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01617232334907786</v>
+        <v>0.01000082907865955</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009445167161775528</v>
+        <v>0.009445167161775531</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00961741982439315</v>
+        <v>0.009617419824393148</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01047110472393839</v>
+        <v>0.0104711047239384</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01045804900118979</v>
+        <v>0.01045804900118981</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01047046270661589</v>
+        <v>0.0104704627066159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01038069739671471</v>
+        <v>0.01038069739671472</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01038069739671471</v>
+        <v>0.01038069739671472</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01044790686818452</v>
+        <v>0.01044790686818453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01047110472393839</v>
+        <v>0.0104711047239384</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01032158598790525</v>
+        <v>0.01032158598790526</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01047110472393839</v>
+        <v>0.0104711047239384</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01047110472393839</v>
+        <v>0.0104711047239384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01047110472393839</v>
+        <v>0.0104711047239384</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0169853605859836</v>
+        <v>0.01698536058598364</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02586127361833018</v>
+        <v>0.02586127361838941</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02764627115695388</v>
+        <v>0.02764627115695391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02330351689825451</v>
+        <v>0.02330351689825455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01715138378963752</v>
+        <v>0.01715138378963755</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02579212342862386</v>
+        <v>0.0257921234286239</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02581532128438231</v>
+        <v>0.02581532128438241</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02566580254834454</v>
+        <v>0.02566580254834461</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02581705662315584</v>
+        <v>0.02581705662315587</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01682133953281387</v>
+        <v>0.01682133953281389</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03503895358181905</v>
+        <v>0.03503895358181913</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02187163180912523</v>
+        <v>0.02187163180912522</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02705316889173425</v>
+        <v>0.02705316889173424</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02706622672656267</v>
+        <v>0.02706622672656266</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03291115310320308</v>
+        <v>0.03291115310320303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0269167021674527</v>
+        <v>0.02691670216745269</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02704302675872896</v>
+        <v>0.02704302675872897</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02706622461448281</v>
+        <v>0.02706622461448283</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02691670587844968</v>
+        <v>0.02691670587844969</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02706622461448281</v>
+        <v>0.02706622461448283</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02052530449359631</v>
+        <v>0.02405645803065128</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02706622461448281</v>
+        <v>0.02706622461448283</v>
       </c>
     </row>
     <row r="8">
@@ -2735,28 +2735,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03431480207805995</v>
+        <v>0.03431480207805999</v>
       </c>
       <c r="C8" t="n">
         <v>0.01213199274176581</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01650581600410645</v>
+        <v>0.01650581600410646</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01426820738076992</v>
+        <v>0.01426820738076993</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01426820738076992</v>
+        <v>0.01426820738076993</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01327141788772325</v>
+        <v>0.01327141788772327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01247285226955433</v>
+        <v>0.01247285226955435</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01426820738076992</v>
+        <v>0.01426820738076993</v>
       </c>
       <c r="J8" t="n">
         <v>0.0139347738907986</v>
@@ -2765,7 +2765,7 @@
         <v>0.01948032708772404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0153000072786115</v>
+        <v>0.01530000727861151</v>
       </c>
     </row>
     <row r="9">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03389868897303069</v>
+        <v>0.03389868897303071</v>
       </c>
       <c r="C9" t="n">
         <v>0.01197618212337</v>
@@ -2793,7 +2793,7 @@
         <v>0.01424899380976625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01575076460809262</v>
+        <v>0.01575076460809263</v>
       </c>
       <c r="I9" t="n">
         <v>0.01451869132738935</v>
@@ -2802,7 +2802,7 @@
         <v>0.01727572625999398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01972698838153594</v>
+        <v>0.01972698838153592</v>
       </c>
       <c r="L9" t="n">
         <v>0.01781136674413967</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01469266076226582</v>
+        <v>0.01469266076226581</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01645242131151628</v>
+        <v>0.0164524213115163</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02189983158972842</v>
+        <v>0.02189983158972843</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03594032844841789</v>
+        <v>0.03594032844841771</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03594032844841789</v>
+        <v>0.03594032844841771</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02870244859230373</v>
+        <v>0.02870244859230287</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03485154433951678</v>
+        <v>0.03485154433951674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03594032844841789</v>
+        <v>0.03594032844841771</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1014326194051135</v>
+        <v>0.1014326194051136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01968717565083523</v>
+        <v>0.01968717565083522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04589758143603023</v>
+        <v>0.04589758143603024</v>
       </c>
     </row>
     <row r="3">
@@ -2934,7 +2934,7 @@
         <v>0.0057383483939557</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005036213104221763</v>
+        <v>0.005036213104221773</v>
       </c>
       <c r="D3" t="n">
         <v>0.0057383483939557</v>
@@ -2943,16 +2943,16 @@
         <v>0.006154773740727679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006154773740727679</v>
+        <v>0.006154773740727678</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005718718681627686</v>
+        <v>0.005718718681627691</v>
       </c>
       <c r="H3" t="n">
         <v>0.0057383483939557</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005611829457015643</v>
+        <v>0.005611829457015641</v>
       </c>
       <c r="J3" t="n">
         <v>0.0057383483939557</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009095003687727032</v>
+        <v>0.009095003687727062</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008912936201063201</v>
+        <v>0.008912936201063124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009072452673899136</v>
+        <v>0.01497291759548522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008578973916397963</v>
+        <v>0.008578973916397959</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009022414174055205</v>
+        <v>0.009022414174055219</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01495213487347038</v>
+        <v>0.009075373975399061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01539373479638966</v>
+        <v>0.01539373479638963</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01484524564885833</v>
+        <v>0.01484524564885834</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009463895835868695</v>
+        <v>0.01496451119499656</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009063137248967432</v>
+        <v>0.009063137248967434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009064244763347674</v>
+        <v>0.009064244763347678</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009482849849344851</v>
+        <v>0.009482849849344846</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009473230527116646</v>
+        <v>0.009473230527116652</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009482241145564521</v>
+        <v>0.009482241145564512</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009431490829727177</v>
+        <v>0.009431490829727168</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009431490829727177</v>
+        <v>0.009431490829727168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009463220137016852</v>
+        <v>0.009463220137016851</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009482849849344851</v>
+        <v>0.009482849849344846</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009356330912404792</v>
+        <v>0.009356330912404811</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009482849849344851</v>
+        <v>0.009482849849344846</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009482849849344851</v>
+        <v>0.009482849849344846</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009482849849344851</v>
+        <v>0.009482849849344846</v>
       </c>
     </row>
     <row r="6">
@@ -3051,25 +3051,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01537474211672336</v>
+        <v>0.01537474211672333</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0232943438808672</v>
+        <v>0.02329434388080852</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02485865176958351</v>
+        <v>0.02485865176958352</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02102117315440478</v>
+        <v>0.02102117315440473</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01554241747364233</v>
+        <v>0.01554241747364229</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321021530059299</v>
+        <v>0.02321021530059296</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02322984501293622</v>
+        <v>0.02322984501293616</v>
       </c>
       <c r="I6" t="n">
         <v>0.02310332607598095</v>
@@ -3078,10 +3078,10 @@
         <v>0.02323138876409447</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01522882954772869</v>
+        <v>0.01522882954772868</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03143515681960685</v>
+        <v>0.03143515681960678</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01808628822454986</v>
+        <v>0.01808628822454987</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02224551920587704</v>
+        <v>0.022245519205877</v>
       </c>
       <c r="D7" t="n">
         <v>0.02225514154462051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0269393869148416</v>
+        <v>0.02693938691484158</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02212861938349478</v>
+        <v>0.0221286193834948</v>
       </c>
       <c r="G7" t="n">
         <v>0.0222355088157772</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02225513852810521</v>
+        <v>0.02225513852810518</v>
       </c>
       <c r="I7" t="n">
         <v>0.02212861959116516</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02225513852810521</v>
+        <v>0.02225513852810518</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01700581107696642</v>
+        <v>0.01983969155862145</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02225513852810521</v>
+        <v>0.02225513852810518</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03418286467798959</v>
+        <v>0.03418286467798955</v>
       </c>
       <c r="C8" t="n">
         <v>0.01193768076083247</v>
@@ -3140,10 +3140,10 @@
         <v>0.01804752854687246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01436668882565507</v>
+        <v>0.01436668882565508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01436668882565507</v>
+        <v>0.01436668882565508</v>
       </c>
       <c r="G8" t="n">
         <v>0.01472270094334752</v>
@@ -3152,13 +3152,13 @@
         <v>0.0178184079667748</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01436668882565507</v>
+        <v>0.01436668882565508</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01795534686358228</v>
+        <v>0.0179553468635823</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02002348059799828</v>
+        <v>0.02002348059799822</v>
       </c>
       <c r="L8" t="n">
         <v>0.01670778218826463</v>
@@ -3186,10 +3186,10 @@
         <v>0.01441581422230267</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01465823210550367</v>
+        <v>0.01465823210550366</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01775158292905985</v>
+        <v>0.01775158292905986</v>
       </c>
       <c r="I9" t="n">
         <v>0.01441581422230267</v>
@@ -3198,10 +3198,10 @@
         <v>0.0188053102915278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01975733385408007</v>
+        <v>0.01975733385408002</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01678529735659237</v>
+        <v>0.01678529735659236</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01305614759776524</v>
+        <v>0.01305614759776515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0155698917154009</v>
+        <v>0.01556989171540091</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01962447481022699</v>
+        <v>0.01962447481022692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02488835048629454</v>
+        <v>0.0248883504862945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02488835048629454</v>
+        <v>0.0248883504862945</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01947722552275826</v>
+        <v>0.01947722552275833</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02213250556716198</v>
+        <v>0.02213250556716191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02488835048629454</v>
+        <v>0.0248883504862945</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03168558803245451</v>
+        <v>0.03168558803245445</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01492466610695843</v>
+        <v>0.01492466610695831</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0195777247990477</v>
+        <v>0.01957772479904769</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880427</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005015384967029106</v>
+        <v>0.005015384967029112</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880427</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005912470534889177</v>
+        <v>0.005912470534889181</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005912470534889178</v>
+        <v>0.005912470534889182</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005615803631816197</v>
+        <v>0.00561580363181582</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880426</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005515273020013959</v>
+        <v>0.00551527302001355</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880426</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880427</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005634330187880539</v>
+        <v>0.005634330187880427</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01483693823155877</v>
+        <v>0.01483693823155871</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008874541359925998</v>
+        <v>0.008874541359925841</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008979878643483265</v>
+        <v>0.008979878643483208</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008486221699435491</v>
+        <v>0.008486221699435472</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008947015611471489</v>
+        <v>0.008947015611471517</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01481841167549418</v>
+        <v>0.01481841167549417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01522223061077747</v>
+        <v>0.008992336716212919</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008907016333938058</v>
+        <v>0.01471788106369177</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01482537231632786</v>
+        <v>0.009373953151422044</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009027852603792212</v>
+        <v>0.009027852603792271</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980211993040882</v>
+        <v>0.008980211993040773</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009221120162634287</v>
+        <v>0.00922112016263427</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009211941865994271</v>
+        <v>0.009211941865994276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009220506126847633</v>
+        <v>0.009220506126847591</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009163256856446199</v>
+        <v>0.009163256856446211</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009163256856446199</v>
+        <v>0.009163256856446211</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009202593606569713</v>
+        <v>0.009202593606569656</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009221120162634287</v>
+        <v>0.00922112016263427</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009102062994767308</v>
+        <v>0.009102062994767339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009221120162634287</v>
+        <v>0.00922112016263427</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009221120162634287</v>
+        <v>0.00922112016263427</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009221120162634287</v>
+        <v>0.00922112016263427</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01502549467862043</v>
+        <v>0.01502549467862041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02273884883675601</v>
+        <v>0.02273884883681684</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02427598890873323</v>
+        <v>0.02427598890873318</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02052696590113573</v>
+        <v>0.02052696590113575</v>
       </c>
       <c r="F6" t="n">
         <v>0.01518617536660866</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02266874334795183</v>
+        <v>0.02266874334795187</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02268726990403316</v>
+        <v>0.02268726990403314</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02256821273614948</v>
+        <v>0.02256821273614945</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02268877566085968</v>
+        <v>0.02268877566085957</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01488317327035194</v>
+        <v>0.01488317327035187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03069063479284782</v>
+        <v>0.03069063479284784</v>
       </c>
     </row>
     <row r="7">
@@ -3490,34 +3490,34 @@
         <v>0.01683380052436988</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02065953048093006</v>
+        <v>0.02065953048093008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02066871160804125</v>
+        <v>0.02066871160804129</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02497505673144976</v>
+        <v>0.0249750567314498</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02054965141134851</v>
+        <v>0.02054965141134852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0206501822215055</v>
+        <v>0.02065018222150551</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02066870877757006</v>
+        <v>0.02066870877757</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02054965160970311</v>
+        <v>0.02054965160970312</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02066870877757006</v>
+        <v>0.02066870877757</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01835660123818635</v>
+        <v>0.01844674906530442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02066870877757006</v>
+        <v>0.02066870877757</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03389077200188421</v>
+        <v>0.0338907720018842</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01173807249312138</v>
+        <v>0.01173807249312139</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01793543334125654</v>
+        <v>0.01793543334125653</v>
       </c>
       <c r="E8" t="n">
         <v>0.01354602797210378</v>
@@ -3542,10 +3542,10 @@
         <v>0.01354602797210378</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01429988427947815</v>
+        <v>0.01429988427947812</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01792464820108218</v>
+        <v>0.01792464820108216</v>
       </c>
       <c r="I8" t="n">
         <v>0.01354602797210378</v>
@@ -3554,10 +3554,10 @@
         <v>0.01626343253988382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987117204436596</v>
+        <v>0.01987117204436594</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01689934760191569</v>
+        <v>0.0168993476019157</v>
       </c>
     </row>
     <row r="9">
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03334288719622041</v>
+        <v>0.03334288719622042</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01154040159131051</v>
+        <v>0.01154040159131052</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01770191900045162</v>
+        <v>0.01770191900045167</v>
       </c>
       <c r="E9" t="n">
         <v>0.01345375501447969</v>
@@ -3582,22 +3582,22 @@
         <v>0.01345375501447969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01411581723360235</v>
+        <v>0.01411581723360232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01769783038181202</v>
+        <v>0.017697830381812</v>
       </c>
       <c r="I9" t="n">
         <v>0.01345375501447969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01620685886576987</v>
+        <v>0.01620685886576988</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01954057821876562</v>
+        <v>0.01954057821876558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01665292266594556</v>
+        <v>0.01665292266594552</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02139601711706891</v>
+        <v>0.02139601711706897</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01827196383736494</v>
+        <v>0.01827196383736493</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03561803360860355</v>
+        <v>0.03561803360860368</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04814996855239506</v>
+        <v>0.04814996855239512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04814996855239506</v>
+        <v>0.04814996855239512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05586561352728583</v>
+        <v>0.05586561352728539</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2613026517835405</v>
+        <v>0.2613026517835408</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04814996855239506</v>
+        <v>0.04814996855239512</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06935054329283186</v>
+        <v>0.06935054329283184</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03251767670775894</v>
+        <v>0.03251767670775916</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2092248825258976</v>
+        <v>0.2092248825258979</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005097037290959924</v>
+        <v>0.005097037290959923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00588860637278539</v>
+        <v>0.005888606372785381</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005888606372785389</v>
+        <v>0.005888606372785382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005951676441429265</v>
+        <v>0.005951676441429237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005834425575268189</v>
+        <v>0.005834425575268198</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00597317789966744</v>
+        <v>0.005973177899667545</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009263995279809365</v>
+        <v>0.009263995279809537</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009024195211041888</v>
+        <v>0.009024195211041712</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009231990762864881</v>
+        <v>0.009231990762864977</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008633892735647242</v>
+        <v>0.008633892735647226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009138743019248646</v>
+        <v>0.009138743019248625</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01560396077726629</v>
+        <v>0.009242493821571237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01615540272323937</v>
+        <v>0.01615540272323946</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01548670991110532</v>
+        <v>0.009125242955410178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01566077786634347</v>
+        <v>0.009607639518358989</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009154594300674427</v>
+        <v>0.009154594300674796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009297093805578272</v>
+        <v>0.0092970938055783</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01009945309639311</v>
+        <v>0.01009945309639319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01008874956843794</v>
+        <v>0.01008874956843792</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01009881349247921</v>
+        <v>0.01009881349247932</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003025567124655</v>
+        <v>0.01003025567124654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003025567124655</v>
+        <v>0.01003025567124654</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01007795163815481</v>
+        <v>0.01007795163815491</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01009945309639311</v>
+        <v>0.01009945309639319</v>
       </c>
       <c r="I5" t="n">
         <v>0.009960700771993805</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01009945309639311</v>
+        <v>0.01009945309639319</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01009945309639311</v>
+        <v>0.01009945309639319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01009945309639311</v>
+        <v>0.01009945309639319</v>
       </c>
     </row>
     <row r="6">
@@ -3843,22 +3843,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01644264373429114</v>
+        <v>0.01644264373429125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02502090229462254</v>
+        <v>0.0250209022945642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02672936665571577</v>
+        <v>0.02672936665571589</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02255527480319373</v>
+        <v>0.02255527480319372</v>
       </c>
       <c r="F6" t="n">
         <v>0.01661583787578834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02494117989449647</v>
+        <v>0.02494117989449661</v>
       </c>
       <c r="H6" t="n">
         <v>0.02496268135273777</v>
@@ -3867,13 +3867,13 @@
         <v>0.02482392902833544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02496435578268345</v>
+        <v>0.02496435578268355</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01628437966145276</v>
+        <v>0.01628437966145279</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03386257307775786</v>
+        <v>0.03386257307775793</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02050514186035926</v>
+        <v>0.02050514186035934</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0253263185170798</v>
+        <v>0.02532631851707976</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0253370230226973</v>
+        <v>0.02533702302269739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03077415389017507</v>
+        <v>0.03077415389017501</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02519826652467275</v>
+        <v>0.02519826652467272</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02531552058679667</v>
+        <v>0.02531552058679672</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02533702204503495</v>
+        <v>0.02533702204503498</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02519826972063567</v>
+        <v>0.02519826972063561</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02533702204503495</v>
+        <v>0.02533702204503498</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02253741210097735</v>
+        <v>0.02253741210097736</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02533702204503494</v>
+        <v>0.02533702204503498</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03415122909217645</v>
+        <v>0.03415122909217654</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01209373716043795</v>
+        <v>0.01209373716043794</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01790644875325066</v>
+        <v>0.01790644875325068</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01423764923145976</v>
+        <v>0.01423764923145975</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01423764923145976</v>
+        <v>0.01423764923145975</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01427229651562807</v>
+        <v>0.01427229651562812</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01339078954369528</v>
+        <v>0.01339078954369531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01423764923145976</v>
+        <v>0.01423764923145975</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01859342025321835</v>
+        <v>0.01859342025321832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987970321746407</v>
+        <v>0.01987970321746414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01612580737390194</v>
+        <v>0.01612580737390198</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03369835568831674</v>
+        <v>0.03369835568831688</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01191481527890709</v>
+        <v>0.01191481527890708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01787260131850402</v>
+        <v>0.01787260131850409</v>
       </c>
       <c r="E9" t="n">
         <v>0.01442384892153846</v>
@@ -3981,19 +3981,19 @@
         <v>0.01454625657768502</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01603821332800025</v>
+        <v>0.01603821332800034</v>
       </c>
       <c r="I9" t="n">
         <v>0.01442384892153846</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01895564288286609</v>
+        <v>0.01895564288286613</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01977208346611598</v>
+        <v>0.01977208346611602</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01806857661045545</v>
+        <v>0.01806857661045549</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01637788248865747</v>
+        <v>0.01637788248865744</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01702646375701895</v>
+        <v>0.01702646375701892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02062721120133777</v>
+        <v>0.02062721120133768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03456644372086102</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03456644372086102</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02251032810071286</v>
+        <v>0.02251032810071185</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02372825352167926</v>
+        <v>0.02372825352167917</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03456644372086102</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03760486951072427</v>
+        <v>0.03760486951072425</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02194137942198486</v>
+        <v>0.02194137942198481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02130760939791628</v>
+        <v>0.02130760939791624</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005007851209893869</v>
+        <v>0.005007851209893855</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
       <c r="E3" t="n">
         <v>0.006188714664728935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006188714664728936</v>
+        <v>0.006188714664728935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005691902781972479</v>
+        <v>0.005691902781972472</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005586397700253464</v>
+        <v>0.005586397700253472</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005711270204445762</v>
+        <v>0.005711270204445756</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009051699614529131</v>
+        <v>0.0149129590637728</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008877390106382884</v>
+        <v>0.008877390106382665</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009032203004537383</v>
+        <v>0.009032267351266766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008552312685018295</v>
+        <v>0.008552312685018302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008983892858996669</v>
+        <v>0.008983892858996652</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009032332192055839</v>
+        <v>0.009032332192055821</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0153214715400382</v>
+        <v>0.01532147154003818</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01478808655958055</v>
+        <v>0.01478808655958051</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01490563913361424</v>
+        <v>0.009397109408732703</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009032116011430794</v>
+        <v>0.009032116011430773</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009012744769876641</v>
+        <v>0.009012744769876626</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009387237433805677</v>
+        <v>0.009387237433805666</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009377995710604665</v>
+        <v>0.009377995710604641</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009386630867326079</v>
+        <v>0.009386630867326056</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009353645048142819</v>
+        <v>0.009353645048142808</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009353645048142819</v>
+        <v>0.009353645048142808</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009367870011332383</v>
+        <v>0.009367870011332364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009387237433805677</v>
+        <v>0.009387237433805666</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009262364929613376</v>
+        <v>0.009262364929613369</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009387237433805677</v>
+        <v>0.009387237433805666</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009387237433805677</v>
+        <v>0.009387237433805666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009387237433805677</v>
+        <v>0.009387237433805666</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01523078983670684</v>
+        <v>0.01523078983670679</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02308124342956645</v>
+        <v>0.02308124342956636</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02461217964891889</v>
+        <v>0.02461217964891879</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02083093988692858</v>
+        <v>0.02083093988692853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01540703523404358</v>
+        <v>0.01540703523404357</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02298161266083946</v>
+        <v>0.02298161266083943</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02300098008332493</v>
+        <v>0.02300098008332481</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0228761075791205</v>
+        <v>0.02287610757912044</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02300250714659927</v>
+        <v>0.02300250714659913</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508645456378536</v>
+        <v>0.01508645456378532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111759352710059</v>
+        <v>0.03111759352710051</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01791253261333262</v>
+        <v>0.01791253261333253</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02202694045117536</v>
+        <v>0.02202694045117529</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02203618513805132</v>
+        <v>0.02203618513805123</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02666991644935748</v>
+        <v>0.02666991644935741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02191130962388281</v>
+        <v>0.02191130962388278</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02201681475190309</v>
+        <v>0.02201681475190305</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02203618217437638</v>
+        <v>0.0220361821743763</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02191130967018407</v>
+        <v>0.02191130967018403</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02203618217437638</v>
+        <v>0.0220361821743763</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01964692467039639</v>
+        <v>0.01684377054005875</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02203618217437638</v>
+        <v>0.0220361821743763</v>
       </c>
     </row>
     <row r="8">
@@ -4328,28 +4328,28 @@
         <v>0.01803727408127816</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01438850185206195</v>
+        <v>0.01438850185206194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01438850185206195</v>
+        <v>0.01438850185206194</v>
       </c>
       <c r="G8" t="n">
         <v>0.01474630502830657</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01801649643616659</v>
+        <v>0.01801649643616657</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01438850185206195</v>
+        <v>0.01438850185206194</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01934710503856342</v>
+        <v>0.01934710503856341</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02003048196639652</v>
+        <v>0.02003048196639647</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01720253680894134</v>
+        <v>0.01720253680894133</v>
       </c>
     </row>
     <row r="9">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03239875965486469</v>
+        <v>0.0323987596548647</v>
       </c>
       <c r="C9" t="n">
         <v>0.01177516605460205</v>
@@ -4368,25 +4368,25 @@
         <v>0.01781663915480942</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01441846377179725</v>
+        <v>0.01441846377179724</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01441846377179725</v>
+        <v>0.01441846377179724</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01459711958691006</v>
+        <v>0.01459711958691005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01780851102225482</v>
+        <v>0.0178085110222548</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01441846377179725</v>
+        <v>0.01441846377179724</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01932182031630983</v>
+        <v>0.0193218203163098</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01979613839114532</v>
+        <v>0.01979613839114528</v>
       </c>
       <c r="L9" t="n">
         <v>0.01697288318472572</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01452925536178796</v>
+        <v>0.01452925536178795</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01582681261989335</v>
+        <v>0.0158268126198933</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01881726918486957</v>
+        <v>0.01881726918486955</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02494009599691095</v>
+        <v>0.02494009599691089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02494009599691095</v>
+        <v>0.02494009599691089</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01945991174890786</v>
+        <v>0.01945991174890782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02135012597240806</v>
+        <v>0.02135012597240802</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02494009599691095</v>
+        <v>0.02494009599691089</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03202120472592165</v>
+        <v>0.03202120472592161</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01945715033856495</v>
+        <v>0.01945715033856498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01951742819007201</v>
+        <v>0.01951742819007203</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004989146035842912</v>
+        <v>0.004989146035842907</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005926883031751239</v>
+        <v>0.005926883031751219</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005926883031751241</v>
+        <v>0.005926883031751219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005597644528369811</v>
+        <v>0.005597644528369807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005498288719621223</v>
+        <v>0.005498288719621207</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00561596117689141</v>
+        <v>0.005615961176891413</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009026626639279165</v>
+        <v>0.0148318959575536</v>
       </c>
       <c r="C4" t="n">
         <v>0.008872817520469076</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008976872531022686</v>
+        <v>0.008976806403708635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008490877820592119</v>
+        <v>0.008490877820592112</v>
       </c>
       <c r="F4" t="n">
         <v>0.008950485785739573</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01481357930903193</v>
+        <v>0.009008309990757565</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01521274449956765</v>
+        <v>0.01521274449956766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01471422350028338</v>
+        <v>0.008908954182008984</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009373188469637481</v>
+        <v>0.01482093559746565</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009037656284100132</v>
+        <v>0.009037656284100118</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980151751439781</v>
+        <v>0.008980151751440365</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009154556249630512</v>
+        <v>0.009154556249630508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009145424002047207</v>
+        <v>0.0091454240020472</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009153944208555363</v>
+        <v>0.009153944208555413</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009107388487643238</v>
+        <v>0.009107388487643227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009107388487643238</v>
+        <v>0.009107388487643227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009136239601108907</v>
+        <v>0.009136239601108929</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009154556249630512</v>
+        <v>0.009154556249630508</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009036883792360338</v>
+        <v>0.00903688379236032</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009154556249630512</v>
+        <v>0.009154556249630508</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009154556249630512</v>
+        <v>0.009154556249630508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009154556249630512</v>
+        <v>0.009154556249630508</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01492095495190049</v>
+        <v>0.01492095495190048</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02258033324915317</v>
+        <v>0.02258033324909286</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02409549736516712</v>
+        <v>0.02409549736516707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02038605389605656</v>
+        <v>0.02038605389605647</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01508657945318927</v>
+        <v>0.01508657945318924</v>
       </c>
       <c r="G6" t="n">
         <v>0.02250150599820324</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02251982264674066</v>
+        <v>0.02251982264674063</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02240215018945464</v>
+        <v>0.02240215018945461</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02252131604035943</v>
+        <v>0.02252131604035937</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01477980208331735</v>
+        <v>0.01477980208331732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03045747535955909</v>
+        <v>0.03045747535955904</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>0.01678348020978125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02059687013984996</v>
+        <v>0.02059687013984993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02060600522066556</v>
+        <v>0.02060600522066553</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02489944184432973</v>
+        <v>0.02489944184432968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02048832977859199</v>
+        <v>0.02048832977859198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02058768573891165</v>
+        <v>0.02058768573891163</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02060600238743327</v>
+        <v>0.02060600238743328</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02048832993016308</v>
+        <v>0.02048832993016303</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02060600238743327</v>
+        <v>0.02060600238743328</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0183013625512887</v>
+        <v>0.01830136255128872</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02060600238743327</v>
+        <v>0.02060600238743328</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02938326219594538</v>
+        <v>0.02938326219594543</v>
       </c>
       <c r="C8" t="n">
         <v>0.01178739990999202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01792907028572759</v>
+        <v>0.0179290702857276</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0135345598572942</v>
+        <v>0.01353455985729419</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0135345598572942</v>
+        <v>0.01353455985729419</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01391845053449592</v>
+        <v>0.01391845053449591</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01791544757057358</v>
+        <v>0.01791544757057361</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0135345598572942</v>
+        <v>0.01353455985729419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01622563685781332</v>
+        <v>0.01622563685781334</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01979397711978831</v>
+        <v>0.01979397711978833</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01688387918997559</v>
+        <v>0.01688387918997558</v>
       </c>
     </row>
     <row r="9">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02892620217890739</v>
+        <v>0.02892620217890741</v>
       </c>
       <c r="C9" t="n">
         <v>0.01159260844076965</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01768448196384159</v>
+        <v>0.0176844819638416</v>
       </c>
       <c r="E9" t="n">
         <v>0.01344336161326409</v>
@@ -4782,10 +4782,10 @@
         <v>0.01617433056128538</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01952833678923918</v>
+        <v>0.01952833678923921</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01663713894158896</v>
+        <v>0.01663713894158898</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2389431243237635</v>
+        <v>0.238943124323766</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09524105664293624</v>
+        <v>0.09524105664293595</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2870188602747544</v>
+        <v>0.2870188602747542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09524105664293624</v>
+        <v>0.09524105664293595</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09524105664293624</v>
+        <v>0.09524105664293595</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2972813302547628</v>
+        <v>0.2972813302547633</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7618618037462811</v>
+        <v>0.7618618037462793</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09524105664293624</v>
+        <v>0.09524105664293595</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3608618313939033</v>
+        <v>0.3608618313939032</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1331362577190277</v>
+        <v>0.1331362577190282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3137813506713616</v>
+        <v>0.3137813506713617</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006159380652871527</v>
+        <v>0.006159380652871534</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006355381061930047</v>
+        <v>0.006355381061930058</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006355381061930046</v>
+        <v>0.006355381061930057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007071625880220758</v>
+        <v>0.007071625880220763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006930522161783392</v>
+        <v>0.006930522161783395</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007097714620081548</v>
+        <v>0.007097714620081565</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01902288269249183</v>
+        <v>0.01111195738076439</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01051993262966372</v>
+        <v>0.01051993262966376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01125853553365506</v>
+        <v>0.01125858932725746</v>
       </c>
       <c r="E4" t="n">
         <v>0.01005879807142514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0108895573861847</v>
+        <v>0.01088955738618471</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01899679395263103</v>
+        <v>0.01108586864090359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01952137590291941</v>
+        <v>0.01952137590291943</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01885569023419367</v>
+        <v>0.0188556902341937</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01909189616747737</v>
+        <v>0.0115828477601816</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01086493091182925</v>
+        <v>0.01086493091182923</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01144635977971156</v>
+        <v>0.01144635977971159</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01219132608665816</v>
+        <v>0.01219132608665814</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01202413362836</v>
+        <v>0.01202413362836001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01219061582344471</v>
+        <v>0.01219061582344472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01201490627370034</v>
+        <v>0.01201490627370035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01201490627370034</v>
+        <v>0.01201490627370035</v>
       </c>
       <c r="G5" t="n">
         <v>0.01216523734679737</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01219132608665816</v>
+        <v>0.01219132608665814</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01202413362836</v>
+        <v>0.01202413362836001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01219132608665816</v>
+        <v>0.01219132608665814</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01219132608665816</v>
+        <v>0.01219132608665814</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01219132608665816</v>
+        <v>0.01219132608665814</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01938429305466472</v>
+        <v>0.01938429305466473</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02906983802876653</v>
+        <v>0.02906983802882184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03128730796120123</v>
+        <v>0.0312873079612012</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02637401867096112</v>
+        <v>0.02637401867096111</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01952452659858463</v>
+        <v>0.0195245265985846</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0292169450966038</v>
+        <v>0.02921694509660377</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02924303383646498</v>
+        <v>0.02924303383646497</v>
       </c>
       <c r="I6" t="n">
         <v>0.02907584137816635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0292449713601255</v>
+        <v>0.02924497136012547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01920116188326456</v>
+        <v>0.01920116188326454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03954131295628517</v>
+        <v>0.03954131295628511</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02783777072219438</v>
+        <v>0.02783777072219436</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03429948172116125</v>
+        <v>0.03429948172116127</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03446667488250334</v>
+        <v>0.03446667488250336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04194908291088664</v>
+        <v>0.04194908291088666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03429947093713018</v>
+        <v>0.0342994709371302</v>
       </c>
       <c r="G7" t="n">
         <v>0.03444058543959865</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03446667417945946</v>
+        <v>0.03446667417945944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03429948172116125</v>
+        <v>0.03429948172116127</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03446667417945946</v>
+        <v>0.03446667417945944</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03062586177830534</v>
+        <v>0.03062586177830535</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03446667417945946</v>
+        <v>0.03446667417945944</v>
       </c>
     </row>
     <row r="8">
@@ -5117,7 +5117,7 @@
         <v>0.01632827272988695</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01204337982147764</v>
+        <v>0.01204337982147767</v>
       </c>
       <c r="E8" t="n">
         <v>0.01632827272988695</v>
@@ -5126,22 +5126,22 @@
         <v>0.01632827272988695</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01192449536045166</v>
+        <v>0.01192449536045164</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00310728160418661</v>
+        <v>0.003107281604186642</v>
       </c>
       <c r="I8" t="n">
         <v>0.01632827272988695</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01084603797643393</v>
+        <v>0.01084603797643394</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561126653778332</v>
+        <v>0.01561126653778334</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01220760844604422</v>
+        <v>0.01220760844604424</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01583882002848024</v>
+        <v>0.01583882002848023</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01713752023318419</v>
+        <v>0.0171375202331842</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01544330620468001</v>
+        <v>0.01544330620468003</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01713752023318419</v>
+        <v>0.0171375202331842</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01713752023318419</v>
+        <v>0.0171375202331842</v>
       </c>
       <c r="G9" t="n">
         <v>0.01537146500393719</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01181784750271854</v>
+        <v>0.01181784750271856</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01713752023318419</v>
+        <v>0.0171375202331842</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01495838452363548</v>
+        <v>0.0149583845236355</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01689646522961173</v>
+        <v>0.01689646522961174</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01551471924140679</v>
+        <v>0.008106591467124207</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1774303745276818</v>
+        <v>0.1774303745276819</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09567154855820105</v>
+        <v>0.09567154855820094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.256489672144101</v>
+        <v>0.2564896721441022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09567154855820105</v>
+        <v>0.09567154855820094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09567154855820105</v>
+        <v>0.09567154855820094</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2568097637464232</v>
+        <v>0.2568097637464242</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5957086622644447</v>
+        <v>0.5957086622644435</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09567154855820105</v>
+        <v>0.09567154855820094</v>
       </c>
       <c r="J2" t="n">
-        <v>0.248621519775417</v>
+        <v>0.2486215197754174</v>
       </c>
       <c r="K2" t="n">
         <v>0.1161748839000135</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3347929526472376</v>
+        <v>0.3347929526472379</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006835208131330634</v>
+        <v>0.006835208131330633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006087929061855324</v>
+        <v>0.00608792906185533</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006835208131330636</v>
+        <v>0.006835208131330628</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006260893544026582</v>
+        <v>0.006260893544026586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006260893544026582</v>
+        <v>0.006260893544026587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00681100969564311</v>
+        <v>0.006811009695643132</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006835208131330636</v>
+        <v>0.006835208131330628</v>
       </c>
       <c r="I3" t="n">
         <v>0.006680242835001669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006835208131330636</v>
+        <v>0.006835208131330628</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006835208131330636</v>
+        <v>0.006835208131330628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006835208131330636</v>
+        <v>0.006835208131330628</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01806922377053089</v>
+        <v>0.01077736902422674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01028074988130893</v>
+        <v>0.01028074988130887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01091977529492011</v>
+        <v>0.01091977529491971</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009830170392009275</v>
+        <v>0.009830170392009277</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01058325054972299</v>
+        <v>0.01058325054972301</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01804502533484337</v>
+        <v>0.0107531705885392</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01845128697611772</v>
+        <v>0.01845128697611773</v>
       </c>
       <c r="I4" t="n">
         <v>0.01791425847420193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01809294367404582</v>
+        <v>0.01121272884043814</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01062474910446135</v>
+        <v>0.01062474910446137</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01103031717855167</v>
+        <v>0.01103031717855166</v>
       </c>
     </row>
     <row r="5">
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01143192842232782</v>
+        <v>0.01143192842232787</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01127696312599887</v>
+        <v>0.01127696312599888</v>
       </c>
       <c r="D5" t="n">
         <v>0.01143126554451479</v>
@@ -5402,22 +5402,22 @@
         <v>0.01126587497442955</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01140772998664032</v>
+        <v>0.01140772998664031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01143192842232782</v>
+        <v>0.01143192842232787</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01127696312599887</v>
+        <v>0.01127696312599888</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01143192842232782</v>
+        <v>0.01143192842232787</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01143192842232782</v>
+        <v>0.01143192842232787</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01143192842232782</v>
+        <v>0.01143192842232787</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0180010598381353</v>
+        <v>0.01800105983813534</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0268101586346287</v>
+        <v>0.02681015863462875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02883356369905243</v>
+        <v>0.02883356369905247</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02435706131244212</v>
+        <v>0.02435706131244217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01812427656436538</v>
+        <v>0.01812427656436542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02694894523341285</v>
+        <v>0.02694894523341287</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02697314366910184</v>
+        <v>0.02697314366910187</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02681817837277144</v>
+        <v>0.02681817837277145</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02697490693933823</v>
+        <v>0.0269749069393383</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01783439877480475</v>
+        <v>0.01783439877480479</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03634523546279587</v>
+        <v>0.03634523546279594</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02439150538428107</v>
+        <v>0.02439150538428111</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02990898011201966</v>
+        <v>0.02990898011201973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03006394694605348</v>
+        <v>0.03006394694605352</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03645484650108909</v>
+        <v>0.03645484650108916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02990897170113846</v>
+        <v>0.02990897170113852</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03003974697266114</v>
+        <v>0.03003974697266117</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03006394540834866</v>
+        <v>0.03006394540834874</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02990898011201966</v>
+        <v>0.02990898011201973</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03006394540834866</v>
+        <v>0.03006394540834874</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02292133049254486</v>
+        <v>0.02677731202776604</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03006394540834866</v>
+        <v>0.03006394540834874</v>
       </c>
     </row>
     <row r="8">
@@ -5513,7 +5513,7 @@
         <v>0.01600155056878718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01213049806876924</v>
+        <v>0.01213049806876919</v>
       </c>
       <c r="E8" t="n">
         <v>0.01600155056878718</v>
@@ -5522,10 +5522,10 @@
         <v>0.01600155056878718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225585350590067</v>
+        <v>0.01225585350590065</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005548936987645443</v>
+        <v>0.005548936987645458</v>
       </c>
       <c r="I8" t="n">
         <v>0.01600155056878718</v>
@@ -5534,10 +5534,10 @@
         <v>0.01280219226782458</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01556314208800611</v>
+        <v>0.01556314208800613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01111453795856697</v>
+        <v>0.01111453795856696</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01625136049680887</v>
+        <v>0.01625136049680888</v>
       </c>
       <c r="C9" t="n">
         <v>0.01693400882662077</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01542631511064978</v>
+        <v>0.01542631511064976</v>
       </c>
       <c r="E9" t="n">
         <v>0.01693400882662077</v>
@@ -5562,7 +5562,7 @@
         <v>0.01693400882662077</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01545681770509393</v>
+        <v>0.01545681770509391</v>
       </c>
       <c r="H9" t="n">
         <v>0.0127574914000593</v>
@@ -5574,10 +5574,10 @@
         <v>0.01570186367065657</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01682439310772103</v>
+        <v>0.01682439310772105</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01501779760922979</v>
+        <v>0.008761883053660671</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.148644275146275</v>
+        <v>0.1486442751462755</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1198356427697938</v>
+        <v>0.1198356427697941</v>
       </c>
       <c r="D2" t="n">
-        <v>0.207781428775075</v>
+        <v>0.2077814287750752</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1198356427697938</v>
+        <v>0.1198356427697941</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1198356427697938</v>
+        <v>0.1198356427697941</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2177788056536303</v>
+        <v>0.217778805653631</v>
       </c>
       <c r="H2" t="n">
         <v>0.4134816518931386</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1198356427697938</v>
+        <v>0.1198356427697941</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1621959267236875</v>
+        <v>0.1621959267236876</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09693985202474084</v>
+        <v>0.09693985202474062</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9698782020112817</v>
+        <v>0.225194315713206</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006851130598088886</v>
+        <v>0.006851130598088958</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006217573401584193</v>
+        <v>0.006217573401584203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006851130598088887</v>
+        <v>0.006851130598088958</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006382512115142886</v>
+        <v>0.006382512115142887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00638251211514288</v>
+        <v>0.006382512115142884</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006828681865320546</v>
+        <v>0.006828681865320541</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006851130598088887</v>
+        <v>0.006851130598088958</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006707172617743443</v>
+        <v>0.006707172617743452</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006851130598088887</v>
+        <v>0.006851130598088958</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006851130598088887</v>
+        <v>0.006851130598088958</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006851130598088887</v>
+        <v>0.006851130598088958</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01082078423171832</v>
+        <v>0.01082078423171837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01045655167494491</v>
+        <v>0.01045655167494516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0179626336427466</v>
+        <v>0.01088151829783068</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009999506167517224</v>
+        <v>0.009999506167517205</v>
       </c>
       <c r="F4" t="n">
         <v>0.01066999379658871</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01079833549894998</v>
+        <v>0.0179392120772654</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01831679567070508</v>
+        <v>0.01831679567070513</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01781770282968822</v>
+        <v>0.0106768262513729</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01123685800016055</v>
+        <v>0.01797652996593504</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0107057455314005</v>
+        <v>0.01070574553140051</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01109274518118148</v>
+        <v>0.0110927451811815</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01130806557867215</v>
+        <v>0.01130806557867218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01116410759832669</v>
+        <v>0.01116410759832671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0113074005317241</v>
+        <v>0.01130740053172412</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01115243260293483</v>
+        <v>0.01115243260293484</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01115243260293483</v>
+        <v>0.01115243260293484</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01128561684590379</v>
+        <v>0.01128561684590381</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01130806557867214</v>
+        <v>0.01130806557867217</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01116410759832669</v>
+        <v>0.01116410759832671</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01130806557867214</v>
+        <v>0.01130806557867217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01130806557867214</v>
+        <v>0.01130806557867217</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01130806557867214</v>
+        <v>0.01130806557867217</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01771734370458512</v>
+        <v>0.01771734370458515</v>
       </c>
       <c r="C6" t="n">
         <v>0.0263148853979868</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02828185414801124</v>
+        <v>0.02828185414801128</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02392255258876723</v>
+        <v>0.02392255258876731</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01784418294577626</v>
+        <v>0.0178441829457763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02644501170830839</v>
+        <v>0.02644501170830846</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02646746044107891</v>
+        <v>0.02646746044107902</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02632350246073132</v>
+        <v>0.02632350246073138</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0264691800884811</v>
+        <v>0.0264691800884812</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01755480579398673</v>
+        <v>0.01755480579398677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03560768904406859</v>
+        <v>0.03560768904406867</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02260556911960584</v>
+        <v>0.02260556911960589</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02762199179382335</v>
+        <v>0.02762199179382339</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02776595211030158</v>
+        <v>0.0277659521103016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03357695615210961</v>
+        <v>0.03357695615210962</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02762198570490271</v>
+        <v>0.02762198570490277</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02774350104140048</v>
+        <v>0.02774350104140044</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0277659497741688</v>
+        <v>0.02776594977416879</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02762199179382335</v>
+        <v>0.02762199179382339</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0277659497741688</v>
+        <v>0.02776594977416879</v>
       </c>
       <c r="K7" t="n">
         <v>0.02477600593910513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0277659497741688</v>
+        <v>0.02776594977416879</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01393995873913701</v>
+        <v>0.01393995873913702</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01405668137238121</v>
+        <v>0.0140566813723812</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01236392325280498</v>
+        <v>0.012363923252805</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01405668137238121</v>
+        <v>0.0140566813723812</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01405668137238121</v>
+        <v>0.0140566813723812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0122725378141409</v>
+        <v>0.01227253781414092</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008314051774868143</v>
+        <v>0.008314051774868152</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01405668137238121</v>
+        <v>0.0140566813723812</v>
       </c>
       <c r="J8" t="n">
-        <v>0.013990884830754</v>
+        <v>0.01399088483075402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01512297878964877</v>
+        <v>0.01512297878964878</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002912223207905702</v>
+        <v>-0.002912223207905703</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01568503898656481</v>
+        <v>0.01568503898656482</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01540817162531532</v>
+        <v>0.01540817162531533</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01504326816589677</v>
+        <v>0.01504326816589678</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01540817162531532</v>
+        <v>0.01540817162531533</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01540817162531532</v>
+        <v>0.01540817162531533</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01499201345884942</v>
+        <v>0.01499201345884943</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01340226870351091</v>
+        <v>0.01340226870351093</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01540817162531532</v>
+        <v>0.01540817162531533</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01570714987397141</v>
+        <v>0.01570714987397142</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01616700550703157</v>
+        <v>0.01616700550703159</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0088367743662422</v>
+        <v>0.008836774366242205</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05777764656677118</v>
+        <v>0.05777764656677151</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05300955914536695</v>
+        <v>0.05300955914536692</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0917135773187784</v>
+        <v>0.09171357731877844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05300955914536695</v>
+        <v>0.05300955914536692</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05300955914536695</v>
+        <v>0.05300955914536692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1140831256167157</v>
+        <v>0.1140831256167156</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2422086232194359</v>
+        <v>0.242208623219436</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05300955914536695</v>
+        <v>0.05300955914536692</v>
       </c>
       <c r="J2" t="n">
         <v>0.2085323700656418</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08859345426517259</v>
+        <v>0.08859345426517279</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3006221624800973</v>
+        <v>0.3006221624800975</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005692137888009049</v>
+        <v>0.005692137888009038</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005876651308820709</v>
+        <v>0.005876651308820691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005876651308820708</v>
+        <v>0.005876651308820695</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006493052249563077</v>
+        <v>0.006493052249563081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006378043051102113</v>
+        <v>0.006378043051102122</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006514283297246267</v>
+        <v>0.006514283297246286</v>
       </c>
     </row>
     <row r="4">
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01008132140334891</v>
+        <v>0.01672143510734116</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009698309706462809</v>
+        <v>0.009698309706462876</v>
       </c>
       <c r="D4" t="n">
         <v>0.01682920653991103</v>
@@ -6151,22 +6151,22 @@
         <v>0.009258992387161625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009896495789342121</v>
+        <v>0.009896495789342107</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01006009035566571</v>
+        <v>0.01670020405965796</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01716829691074724</v>
+        <v>0.01011350097322564</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009945081157204759</v>
+        <v>0.01658519486119698</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01682341969651332</v>
+        <v>0.01682341969651331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009998124147940298</v>
+        <v>0.009998124147940299</v>
       </c>
       <c r="L4" t="n">
         <v>0.0101365369095957</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01077834638093547</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01064210613479133</v>
+        <v>0.01064210613479131</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01077764625816931</v>
+        <v>0.01077764625816932</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01063267299386829</v>
+        <v>0.01063267299386827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01063267299386829</v>
+        <v>0.01063267299386827</v>
       </c>
       <c r="G5" t="n">
         <v>0.01075711533325227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01077834638093547</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01064210613479133</v>
+        <v>0.01064210613479131</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01077834638093547</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01077834638093547</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01077834638093547</v>
+        <v>0.01077834638093548</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01724745956465505</v>
+        <v>0.01724745956465506</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02581122743180729</v>
+        <v>0.02581122743180733</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02775924416854228</v>
+        <v>0.02775924416854233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0234305977668455</v>
+        <v>0.02343059776684552</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01738199055252119</v>
+        <v>0.01738199055252116</v>
       </c>
       <c r="G6" t="n">
         <v>0.02593267477260185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02595390582028522</v>
+        <v>0.02595390582028521</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02581766557414087</v>
+        <v>0.02581766557414088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02595561688542515</v>
+        <v>0.02595561688542513</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01708573285563039</v>
+        <v>0.01708573285563038</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03504851695456856</v>
+        <v>0.03504851695456859</v>
       </c>
     </row>
     <row r="7">
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02278823969557124</v>
+        <v>0.02278823969557127</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02797383967704003</v>
+        <v>0.02797383967704005</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02811008227367241</v>
+        <v>0.02811008227367243</v>
       </c>
       <c r="E7" t="n">
         <v>0.03411512787704463</v>
@@ -6274,22 +6274,22 @@
         <v>0.02797383591206999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02808884887550104</v>
+        <v>0.02808884887550105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02811007992318424</v>
+        <v>0.02811007992318425</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02797383967704003</v>
+        <v>0.02797383967704005</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02811007992318424</v>
+        <v>0.02811007992318425</v>
       </c>
       <c r="K7" t="n">
         <v>0.02502658578343235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02811007992318424</v>
+        <v>0.02811007992318425</v>
       </c>
     </row>
     <row r="8">
@@ -6302,34 +6302,34 @@
         <v>0.01655519313327904</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01668880886496856</v>
+        <v>0.01668880886496855</v>
       </c>
       <c r="D8" t="n">
         <v>0.01564424996522457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01668880886496856</v>
+        <v>0.01668880886496855</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01668880886496856</v>
+        <v>0.01668880886496855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01519276132541993</v>
+        <v>0.01519276132541994</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01244897464464122</v>
+        <v>0.01244897464464121</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01668880886496856</v>
+        <v>0.01668880886496855</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01338646563238575</v>
+        <v>0.01338646563238576</v>
       </c>
       <c r="K8" t="n">
         <v>0.01576779930636939</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01490039027648756</v>
+        <v>0.0117603316980386</v>
       </c>
     </row>
     <row r="9">
@@ -6354,7 +6354,7 @@
         <v>0.01690935248591564</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01627882622430356</v>
+        <v>0.01627882622430357</v>
       </c>
       <c r="H9" t="n">
         <v>0.01517722619251927</v>
@@ -6363,13 +6363,13 @@
         <v>0.01690935248591564</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01555579017290014</v>
+        <v>0.01555579017290013</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01652413253564378</v>
+        <v>0.01652413253564377</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01489634808732653</v>
+        <v>0.01489634808732652</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0621110999221961</v>
+        <v>0.06211109992219609</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07518351383021819</v>
+        <v>0.07518351383021822</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06125588512178418</v>
+        <v>0.06125588512178417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07518351383021819</v>
+        <v>0.07518351383021822</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07518351383021819</v>
+        <v>0.07518351383021822</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08735374863258041</v>
+        <v>0.08735374863258155</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04470733885210875</v>
+        <v>0.04470733885210876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07518351383021819</v>
+        <v>0.07518351383021822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1569848479640741</v>
+        <v>0.1569848479640743</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09750887604861559</v>
+        <v>0.09750887604861555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04809896448050024</v>
+        <v>0.04809896448050027</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005726458914782732</v>
+        <v>0.005726458914782736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00588502929811846</v>
+        <v>0.005885029298118466</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005885029298118467</v>
+        <v>0.005885029298118473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006311678267799273</v>
+        <v>0.006311678267799289</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00621140770053254</v>
+        <v>0.006211407700532546</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006330199977848983</v>
+        <v>0.006330199977848967</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01595977328055099</v>
+        <v>0.01595977328055101</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009662555930617824</v>
+        <v>0.009662555930617833</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009883432152001735</v>
+        <v>0.00988348727367586</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009227055377286568</v>
+        <v>0.00922705537728658</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009775855600220155</v>
+        <v>0.009775855600220151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009909806299695189</v>
+        <v>0.0159412515705013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009870072367013132</v>
+        <v>0.01623805197279781</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009809535732428428</v>
+        <v>0.01584098100323457</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01598956937640373</v>
+        <v>0.01029718166788824</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009947232174158434</v>
+        <v>0.009947232174158436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00985627280782291</v>
+        <v>0.009856272807822914</v>
       </c>
     </row>
     <row r="5">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0101561329661378</v>
+        <v>0.01015613296613779</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01003734068882137</v>
+        <v>0.01003734068882138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01015547461582263</v>
+        <v>0.01015547461582262</v>
       </c>
       <c r="E5" t="n">
         <v>0.01002887423747511</v>
@@ -6593,19 +6593,19 @@
         <v>0.01013761125608811</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0101561329661378</v>
+        <v>0.01015613296613779</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01003734068882137</v>
+        <v>0.01003734068882138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0101561329661378</v>
+        <v>0.01015613296613779</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0101561329661378</v>
+        <v>0.01015613296613779</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0101561329661378</v>
+        <v>0.01015613296613779</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01602703644671295</v>
+        <v>0.01602703644671294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02378042550252394</v>
+        <v>0.02378042550252391</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02553848719085038</v>
+        <v>0.02553848719085041</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02162633129047015</v>
+        <v>0.02162633129047014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01615330396696868</v>
+        <v>0.01615330396696869</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02388642870060078</v>
+        <v>0.02388642870060076</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0239049504106491</v>
+        <v>0.02390495041064913</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02378615813333403</v>
+        <v>0.02378615813333401</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02390649864561931</v>
+        <v>0.02390649864561933</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01588070015036553</v>
+        <v>0.01588070015036554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03213409028566166</v>
+        <v>0.03213409028566168</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.020224691642447</v>
+        <v>0.02022469164244701</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469566819537634</v>
+        <v>0.02469566819537635</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02481446457378956</v>
+        <v>0.02481446457378962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02999216714106579</v>
+        <v>0.02999216714106581</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02469566765705632</v>
+        <v>0.02469566765705633</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02479593876264306</v>
+        <v>0.02479593876264311</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02481446047269273</v>
+        <v>0.02481446047269279</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469566819537634</v>
+        <v>0.02469566819537635</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02481446047269273</v>
+        <v>0.02481446047269279</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02204723963472349</v>
+        <v>0.02215513211194076</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02481446047269273</v>
+        <v>0.02481446047269279</v>
       </c>
     </row>
     <row r="8">
@@ -6695,19 +6695,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0163227981181522</v>
+        <v>0.01632279811815221</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01593297184592378</v>
+        <v>0.01593297184592379</v>
       </c>
       <c r="D8" t="n">
         <v>0.01624280870050056</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01593297184592378</v>
+        <v>0.01593297184592379</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01593297184592378</v>
+        <v>0.01593297184592379</v>
       </c>
       <c r="G8" t="n">
         <v>0.01560341242310701</v>
@@ -6716,7 +6716,7 @@
         <v>0.01682208203455821</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01593297184592378</v>
+        <v>0.01593297184592379</v>
       </c>
       <c r="J8" t="n">
         <v>0.01400958404512797</v>
@@ -6725,7 +6725,7 @@
         <v>0.01530277069021867</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01732424885082221</v>
+        <v>0.01676514303767644</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01672576357417256</v>
+        <v>0.01672576357417258</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01657744419468104</v>
+        <v>0.01657744419468105</v>
       </c>
       <c r="D9" t="n">
         <v>0.01669322327785567</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01657744419468104</v>
+        <v>0.01657744419468105</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01657744419468104</v>
+        <v>0.01657744419468105</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01642700502110402</v>
+        <v>0.01642700502110404</v>
       </c>
       <c r="H9" t="n">
         <v>0.01692994281243581</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01657744419468104</v>
+        <v>0.01657744419468105</v>
       </c>
       <c r="J9" t="n">
         <v>0.01578501693179646</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01631044011873511</v>
+        <v>0.01631044011873512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01713393800829329</v>
+        <v>0.01690663103871511</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09571661922626903</v>
+        <v>0.09571661922626896</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08448659935808742</v>
+        <v>0.08448659935808743</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04612730253318386</v>
+        <v>0.04612730253318384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08448659935808742</v>
+        <v>0.08448659935808743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08448659935808742</v>
+        <v>0.08448659935808743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08329153802561604</v>
+        <v>0.08329153802561577</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04125026386576734</v>
+        <v>0.04125026386576722</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08448659935808742</v>
+        <v>0.08448659935808743</v>
       </c>
       <c r="J2" t="n">
-        <v>0.137668923458998</v>
+        <v>0.1376689234589979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08921748421698565</v>
+        <v>0.08921748421698543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03819448740465449</v>
+        <v>0.06691660886201162</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005818423239062591</v>
+        <v>0.005818423239062585</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005971679511946073</v>
+        <v>0.005971679511946064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005971679511946066</v>
+        <v>0.005971679511946065</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006330141299112449</v>
+        <v>0.006330141299112434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006228878010932424</v>
+        <v>0.006228878010932407</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00634881174003449</v>
+        <v>0.006348811740034472</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01003040324760099</v>
+        <v>0.01003040324760105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009788857697305812</v>
+        <v>0.009788857697305657</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009903372253542304</v>
+        <v>0.009903372253542262</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009345461604652347</v>
+        <v>0.00934546160465234</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009878024488260388</v>
+        <v>0.009878024488260381</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01610356794062879</v>
+        <v>0.01001173280667902</v>
       </c>
       <c r="H4" t="n">
         <v>0.01633782658345228</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009910469518499028</v>
+        <v>0.009910469518498978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01609208355478795</v>
+        <v>0.01038667216976504</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01005305943748741</v>
+        <v>0.01005305943748742</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009994568346965339</v>
+        <v>0.009994568346965332</v>
       </c>
     </row>
     <row r="5">
@@ -6974,25 +6974,25 @@
         <v>0.01013018487118383</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01001025114208176</v>
+        <v>0.01001025114208175</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01012952430386276</v>
+        <v>0.01012952430386275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01000157747693222</v>
+        <v>0.0100015774769322</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01000157747693222</v>
+        <v>0.0100015774769322</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01011151443026179</v>
+        <v>0.01011151443026177</v>
       </c>
       <c r="H5" t="n">
         <v>0.01013018487118383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01001025114208176</v>
+        <v>0.01001025114208175</v>
       </c>
       <c r="J5" t="n">
         <v>0.01013018487118383</v>
@@ -7014,34 +7014,34 @@
         <v>0.01595893556384975</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02364554836977639</v>
+        <v>0.0236455483697764</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02539138749015342</v>
+        <v>0.02539138749015338</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02150936584378639</v>
+        <v>0.0215093658437864</v>
       </c>
       <c r="F6" t="n">
         <v>0.01608186527288933</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02375274786013484</v>
+        <v>0.02375274786013482</v>
       </c>
       <c r="H6" t="n">
         <v>0.02377141830105511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02365148457195483</v>
+        <v>0.02365148457195479</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02377295367697333</v>
+        <v>0.02377295367697329</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01581381468612527</v>
+        <v>0.01581381468612526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03193220978853392</v>
+        <v>0.03193220978853388</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01920370633677836</v>
+        <v>0.01920370633677833</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02338153752671163</v>
+        <v>0.02338153752671158</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02350147506928082</v>
+        <v>0.0235014750692808</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02834106998983693</v>
+        <v>0.02834106998983688</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02338153706799215</v>
+        <v>0.02338153706799212</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02348280081489165</v>
+        <v>0.02348280081489162</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02350147125581372</v>
+        <v>0.02350147125581367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02338153752671163</v>
+        <v>0.02338153752671158</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02350147125581372</v>
+        <v>0.02350147125581367</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02091030269608886</v>
+        <v>0.02091030269608883</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02350147125581372</v>
+        <v>0.02350147125581367</v>
       </c>
     </row>
     <row r="8">
@@ -7094,34 +7094,34 @@
         <v>0.01472504082873558</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01446062513950029</v>
+        <v>0.01446062513950028</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01598267636968188</v>
+        <v>0.01598267636968187</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01446062513950029</v>
+        <v>0.01446062513950028</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01446062513950029</v>
+        <v>0.01446062513950028</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01504282129472917</v>
+        <v>0.01504282129472916</v>
       </c>
       <c r="H8" t="n">
         <v>0.01622197183521583</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01446062513950029</v>
+        <v>0.01446062513950028</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01382594598510547</v>
+        <v>0.01382594598510546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01475911270687692</v>
+        <v>0.0147591127068769</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01561086640779007</v>
+        <v>0.01632415054455105</v>
       </c>
     </row>
     <row r="9">
@@ -7134,34 +7134,34 @@
         <v>0.01565848301169002</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01524985235520904</v>
+        <v>0.01524985235520903</v>
       </c>
       <c r="D9" t="n">
         <v>0.016170736606886</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01524985235520904</v>
+        <v>0.01524985235520903</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01524985235520904</v>
+        <v>0.01524985235520903</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0157838067540575</v>
+        <v>0.01578380675405749</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01626888414858235</v>
+        <v>0.01626888414858233</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01524985235520904</v>
+        <v>0.01524985235520903</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01529349276651844</v>
+        <v>0.01529349276651843</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01567247807320487</v>
+        <v>0.01567247807320486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01631029086020841</v>
+        <v>0.0163102908602084</v>
       </c>
     </row>
   </sheetData>
@@ -7250,34 +7250,34 @@
         <v>0.1534878398514368</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08220904438191992</v>
+        <v>0.08220904438191995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2641006983932205</v>
+        <v>0.2641006983932203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08220904438191992</v>
+        <v>0.08220904438191995</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08220904438191992</v>
+        <v>0.08220904438191995</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2556727300849509</v>
+        <v>0.25567273008495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6857262642249898</v>
+        <v>0.6857262642249897</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08220904438191992</v>
+        <v>0.08220904438191995</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2475036427026197</v>
+        <v>0.2475036427026193</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1264406264832024</v>
+        <v>0.1264406264832021</v>
       </c>
       <c r="L2" t="n">
-        <v>1.08476333890798</v>
+        <v>0.2225906508229461</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006023630834756192</v>
+        <v>0.006023630834756185</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006217574446497121</v>
+        <v>0.006217574446497114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006217574446497121</v>
+        <v>0.006217574446497094</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006921139261006534</v>
+        <v>0.006921139261006521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006784113615635049</v>
+        <v>0.006784113615635036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00694646671841981</v>
+        <v>0.006946466718419799</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01083275234754195</v>
+        <v>0.01083275234754193</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01027451913167803</v>
+        <v>0.0102745191316778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01100809176863981</v>
+        <v>0.01100809176863988</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009822421206978167</v>
+        <v>0.0098224212069782</v>
       </c>
       <c r="F4" t="n">
         <v>0.01061670707978579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01844228721766852</v>
+        <v>0.01844228721766851</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01903247796293362</v>
+        <v>0.01903247796293354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01830526157229702</v>
+        <v>0.01830526157229703</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01859552779040559</v>
+        <v>0.01859552779040556</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0106306422830478</v>
+        <v>0.01063064228304784</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0111202946579898</v>
+        <v>0.01112029465798978</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01181479784875141</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01165244474596666</v>
+        <v>0.01165244474596664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01181409113246688</v>
+        <v>0.01181409113246686</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0116425918979414</v>
+        <v>0.01164259189794135</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0116425918979414</v>
+        <v>0.01164259189794135</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01178947039133812</v>
+        <v>0.0117894703913381</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01181479784875141</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01165244474596666</v>
+        <v>0.01165244474596664</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01181479784875141</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01181479784875141</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01181479784875141</v>
+        <v>0.0118147978487514</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01882497275480009</v>
+        <v>0.01882497275480006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02821319769043754</v>
+        <v>0.02821319769038428</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03036397227600451</v>
+        <v>0.03036397227600434</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02559990610179751</v>
+        <v>0.02559990610179745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0189601133850315</v>
+        <v>0.01896011338503144</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02835688823576084</v>
+        <v>0.02835688823576078</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0283822156931753</v>
+        <v>0.02838221569317525</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02821986259038938</v>
+        <v>0.02821986259038925</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02838409396393611</v>
+        <v>0.02838409396393608</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0186474420606243</v>
+        <v>0.01864744206062426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03836555510475936</v>
+        <v>0.0383655551047592</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02675646139488926</v>
+        <v>0.02675646139488918</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03294742574841939</v>
+        <v>0.03294742574841936</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03310977883081195</v>
+        <v>0.03310977883081186</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04027900626752165</v>
+        <v>0.04027900626752159</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03294741527245007</v>
+        <v>0.03294741527244997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03308445139379088</v>
+        <v>0.03308445139379076</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03310977885120417</v>
+        <v>0.03310977885120421</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03294742574841939</v>
+        <v>0.03294742574841936</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03310977885120417</v>
+        <v>0.03310977885120421</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02942864175703584</v>
+        <v>0.02942864175703578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03310977885120417</v>
+        <v>0.03310977885120421</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01481744814277615</v>
+        <v>0.01481744814277613</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01642818812970992</v>
+        <v>0.01642818812970991</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01209675814120396</v>
+        <v>0.01209675814120392</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01642818812970992</v>
+        <v>0.01642818812970991</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01642818812970992</v>
+        <v>0.01642818812970991</v>
       </c>
       <c r="G8" t="n">
         <v>0.01249339866725565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003210724909880783</v>
+        <v>0.003210724909880797</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01642818812970992</v>
+        <v>0.01642818812970991</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01309175325110726</v>
+        <v>0.01309175325110724</v>
       </c>
       <c r="K8" t="n">
         <v>0.01549155765742371</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002927113009827059</v>
+        <v>-0.002927113009827051</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01645238876259898</v>
+        <v>0.01645238876259895</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01705735825148181</v>
+        <v>0.0170573582514818</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01534443339253101</v>
+        <v>0.01534443339253097</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01705735825148181</v>
+        <v>0.0170573582514818</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01705735825148181</v>
+        <v>0.0170573582514818</v>
       </c>
       <c r="G9" t="n">
         <v>0.0154844508487506</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01173908336007339</v>
+        <v>0.01173908336007336</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01705735825148181</v>
+        <v>0.0170573582514818</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01575150759436398</v>
+        <v>0.01575150759436396</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01672709738115639</v>
+        <v>0.01672709738115637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009241213744327211</v>
+        <v>0.01607114857218254</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03667350620756225</v>
+        <v>0.03667350620756223</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06082485173358164</v>
+        <v>0.06082485173358167</v>
       </c>
       <c r="D2" t="n">
-        <v>0.22195697498993</v>
+        <v>0.2219569749899299</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06082485173358164</v>
+        <v>0.06082485173358167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06082485173358164</v>
+        <v>0.06082485173358167</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1588652974792445</v>
+        <v>0.1588652974792442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1013099793809687</v>
+        <v>0.1013099793809689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06082485173358164</v>
+        <v>0.06082485173358167</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1766579140926513</v>
+        <v>0.1766579140926514</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05636705571802663</v>
+        <v>0.05636705571802667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07112096148045337</v>
+        <v>0.5938535837851517</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005764919539658974</v>
+        <v>0.005764919539658978</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005930473637661455</v>
+        <v>0.00593047363766146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005930473637661453</v>
+        <v>0.005930473637661457</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00643461143678475</v>
+        <v>0.006434611436784756</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006315982616431845</v>
+        <v>0.006315982616431848</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006456549770878642</v>
+        <v>0.006456549770878647</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01672355920436598</v>
+        <v>0.016723559204366</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009721800302615465</v>
+        <v>0.009721800302615517</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0103693982141645</v>
+        <v>0.01036945338677202</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009284522403174279</v>
+        <v>0.009284522403174284</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00994708106123581</v>
+        <v>0.009947081061235808</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01010284958341192</v>
+        <v>0.01670162087027212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01704307279128361</v>
+        <v>0.01704307279128358</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01658299204991918</v>
+        <v>0.01658299204991921</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01052242894925218</v>
+        <v>0.0105224289492522</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009986769853961458</v>
+        <v>0.009986769853961425</v>
       </c>
       <c r="L4" t="n">
         <v>0.01024309775679527</v>
@@ -7766,25 +7766,25 @@
         <v>0.01057355664955254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01043298949510575</v>
+        <v>0.01043298949510574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01057289860157944</v>
+        <v>0.01057289860157947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01042305497707066</v>
+        <v>0.01042305497707063</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01042305497707066</v>
+        <v>0.01042305497707063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01055161831545866</v>
+        <v>0.01055161831545864</v>
       </c>
       <c r="H5" t="n">
         <v>0.01057355664955254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01043298949510575</v>
+        <v>0.01043298949510574</v>
       </c>
       <c r="J5" t="n">
         <v>0.01057355664955254</v>
@@ -7806,19 +7806,19 @@
         <v>0.01676004885832682</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02494207484732297</v>
+        <v>0.02494207484732294</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02681689558236888</v>
+        <v>0.02681689558236895</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0226645771661081</v>
+        <v>0.02266457716610808</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01687798460820277</v>
+        <v>0.01687798460820278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02506775185569792</v>
+        <v>0.02506775185569789</v>
       </c>
       <c r="H6" t="n">
         <v>0.02508969018979101</v>
@@ -7827,13 +7827,13 @@
         <v>0.02494912303534499</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02509132720194606</v>
+        <v>0.02509132720194602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01660532149422985</v>
+        <v>0.01660532149422982</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03379069707284486</v>
+        <v>0.03379069707284481</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02186190842324576</v>
+        <v>0.02186190842324577</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02675778703371953</v>
+        <v>0.02675778703371955</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02689835960689412</v>
+        <v>0.02689835960689413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03256974118757735</v>
+        <v>0.03256974118757734</v>
       </c>
       <c r="F7" t="n">
         <v>0.02675778513981857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02687641585407247</v>
+        <v>0.02687641585407244</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02689835418816634</v>
+        <v>0.02689835418816636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02675778703371953</v>
+        <v>0.02675778703371955</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02689835418816634</v>
+        <v>0.02689835418816636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205565685633247</v>
+        <v>0.02398022001141849</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02689835418816634</v>
+        <v>0.02689835418816636</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01718431818131129</v>
+        <v>0.01718431818131128</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01647147268226701</v>
+        <v>0.016471472682267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01211325435319017</v>
+        <v>0.01211325435319015</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01647147268226701</v>
+        <v>0.016471472682267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01647147268226701</v>
+        <v>0.016471472682267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01400612823544513</v>
+        <v>0.01400612823544512</v>
       </c>
       <c r="H8" t="n">
         <v>0.01568466055491712</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01647147268226701</v>
+        <v>0.016471472682267</v>
       </c>
       <c r="J8" t="n">
         <v>0.01397668839165649</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01663642694961523</v>
+        <v>0.01663642694961522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005211535985127114</v>
+        <v>0.0052115359851271</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01719903186195467</v>
+        <v>0.01719903186195466</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01687081781305345</v>
+        <v>0.01687081781305344</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01513377380815651</v>
+        <v>0.0151337738081565</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01687081781305345</v>
+        <v>0.01687081781305344</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01687081781305345</v>
+        <v>0.01687081781305344</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01588955400618787</v>
+        <v>0.01588955400618785</v>
       </c>
       <c r="H9" t="n">
         <v>0.01659030866283574</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01687081781305345</v>
+        <v>0.01687081781305344</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01589408776261563</v>
+        <v>0.01589408776261564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01697594698841716</v>
+        <v>0.01697594698841715</v>
       </c>
       <c r="L9" t="n">
         <v>0.0123322175363578</v>

--- a/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication terrestrial results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3200248077715542</v>
+        <v>0.01915534362145954</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1725035862797109</v>
+        <v>0.0192093416889943</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6462009332075392</v>
+        <v>0.01948015965642369</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1725035862797109</v>
+        <v>0.0192093416889943</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1725035862797109</v>
+        <v>0.0192093416889943</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4239741791252248</v>
+        <v>0.01919850395960057</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9202012239982696</v>
+        <v>0.01966979755994739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1725035862797109</v>
+        <v>0.0192093416889943</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3995039208146753</v>
+        <v>0.01920894990849905</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1795558205968481</v>
+        <v>0.01900243287457087</v>
       </c>
       <c r="L2" t="n">
-        <v>1.390530346894881</v>
+        <v>0.01914063382620311</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0074708738366793</v>
+        <v>0.01947351770479526</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007685811386972561</v>
+        <v>0.01947351770479526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007685811386972561</v>
+        <v>0.01947351770479526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008073727342082612</v>
+        <v>0.01921049587841588</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007944096396387577</v>
+        <v>0.01947351770479526</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008097900671048828</v>
+        <v>0.01925648497621167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01290651139053425</v>
+        <v>0.3200248077715544</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0123329089388432</v>
+        <v>0.1725035862797113</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01355884042104223</v>
+        <v>0.6462009332075391</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01179987543123616</v>
+        <v>0.1725035862797113</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01273679224207375</v>
+        <v>0.1725035862797113</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02224109456465918</v>
+        <v>0.4239741791252243</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02284888807473538</v>
+        <v>0.9202012239982695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02211146361896416</v>
+        <v>0.1725035862797113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02226539882086545</v>
+        <v>0.3995039208146752</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01262172279810774</v>
+        <v>0.1795558205968483</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01328506123010095</v>
+        <v>1.390530346894884</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01424437823063958</v>
+        <v>0.008097900671048822</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01409057395597834</v>
+        <v>0.007470873836679311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01424359705562575</v>
+        <v>0.008097900671048822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01408095937872988</v>
+        <v>0.007685811386972558</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01408095937872988</v>
+        <v>0.007685811386972555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01422020490167337</v>
+        <v>0.00807372734208261</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01424437823063958</v>
+        <v>0.008097900671048822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01409057395597834</v>
+        <v>0.007944096396387572</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01424437823063958</v>
+        <v>0.008097900671048822</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01424437823063958</v>
+        <v>0.008097900671048822</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01424437823063958</v>
+        <v>0.008097900671048822</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02254152165706283</v>
+        <v>0.01290651139053427</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03391187091881299</v>
+        <v>0.01233290893884331</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03646246913400731</v>
+        <v>0.01355884042104224</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03075892031486312</v>
+        <v>0.01179987543123614</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02274793435741453</v>
+        <v>0.01273679224207377</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03404745340566809</v>
+        <v>0.02224109456465917</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03407162673463469</v>
+        <v>0.02284888807473539</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03391782245997305</v>
+        <v>0.02211146361896414</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03407389272907204</v>
+        <v>0.02226539882086547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02232734403580608</v>
+        <v>0.01262172279810779</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04611578561840538</v>
+        <v>0.01328506123010094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03831753556804572</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04754518483409999</v>
+        <v>0.01409057395597833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0476989915561748</v>
+        <v>0.01424359705562575</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05837116993258096</v>
+        <v>0.01408095937872989</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04754517236932478</v>
+        <v>0.01408095937872989</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0476748157797951</v>
+        <v>0.01422020490167337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04769898910876127</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04754518483409999</v>
+        <v>0.01409057395597833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04769898910876127</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03588606388314973</v>
+        <v>0.01424437823063958</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04769898910876127</v>
+        <v>0.01424437823063958</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01240184846061422</v>
+        <v>0.02254152165706284</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01592179478394062</v>
+        <v>0.03391187091881299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005601250150773633</v>
+        <v>0.03646246913400737</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01592179478394062</v>
+        <v>0.03075892031486314</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01592179478394062</v>
+        <v>0.02274793435741452</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01053026178132812</v>
+        <v>0.0340474534056681</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001956564190251749</v>
+        <v>0.03407162673463469</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01592179478394062</v>
+        <v>0.03391782245997306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01134161377967442</v>
+        <v>0.03407389272907205</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561093601513007</v>
+        <v>0.02232734403580606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01281113818404143</v>
+        <v>0.0461157856184054</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.03831753556804571</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.04754518483410002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.04769899155617482</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.05837116993258092</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04754517236932481</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.04767481577979509</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0476989891087613</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.04754518483410002</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0476989891087613</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03588606388314975</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0476989891087613</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01240184846061423</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01592179478394063</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.005601250150773646</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01592179478394063</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01592179478394063</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01053026178132811</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001956564190251759</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01592179478394063</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01134161377967444</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01561093601513008</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01281113818404145</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.01603646216243224</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>0.0175932964413361</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.01326698429419801</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.0175932964413361</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.0175932964413361</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01524896978316085</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01179827847075925</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01524896978316087</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01179827847075927</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.0175932964413361</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01560765829087672</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.01560765829087673</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01734369647960353</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.008511433752000282</v>
+      <c r="L11" t="n">
+        <v>0.008511433752000287</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03171765838396698</v>
+        <v>0.01658816512680665</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07383882030974867</v>
+        <v>0.01614416841361859</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06120226852768299</v>
+        <v>0.01662583960495409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07383882030974867</v>
+        <v>0.01614416841361859</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07383882030974867</v>
+        <v>0.01614416841361859</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08995692349474327</v>
+        <v>0.01664804596463541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06651331966262716</v>
+        <v>0.01662405005629157</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07383882030974867</v>
+        <v>0.01614416841361859</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1220467140547726</v>
+        <v>0.01668813244391179</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05188621860173552</v>
+        <v>0.0166157776174098</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0396109165952484</v>
+        <v>0.01661195685028233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005789862899941017</v>
+        <v>0.01645613257310367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005944703782980213</v>
+        <v>0.01645613257310367</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005944703782980208</v>
+        <v>0.01645613257310367</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006317830237695896</v>
+        <v>0.01694974520445958</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006213388540333786</v>
+        <v>0.01645613257310367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006337093769356484</v>
+        <v>0.01696058513380617</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009950433764423876</v>
+        <v>0.0317176583839669</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009718103612711996</v>
+        <v>0.0738388203097487</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01605165463394408</v>
+        <v>0.06120226852768298</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009276655793716417</v>
+        <v>0.0738388203097487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009822441168807667</v>
+        <v>0.0738388203097487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01597748818379158</v>
+        <v>0.08995692349474356</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01634702124659337</v>
+        <v>0.06651331966262714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009826728535401169</v>
+        <v>0.0738388203097487</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01033386821761948</v>
+        <v>0.1220467140547722</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009927643566777403</v>
+        <v>0.05188621860173552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009949422574165786</v>
+        <v>0.03961091659524844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01016978460595656</v>
+        <v>0.006337093769356487</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01004607937693381</v>
+        <v>0.005789862899941017</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0101691243684182</v>
+        <v>0.006337093769356487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003730854149147</v>
+        <v>0.005944703782980205</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003730854149147</v>
+        <v>0.005944703782980206</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01015052107429594</v>
+        <v>0.006317830237695901</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01016978460595656</v>
+        <v>0.006337093769356487</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01004607937693381</v>
+        <v>0.006213388540333775</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01016978460595656</v>
+        <v>0.006337093769356487</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01016978460595656</v>
+        <v>0.006337093769356487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01016978460595656</v>
+        <v>0.006337093769356487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01604999951170839</v>
+        <v>0.009950433764423859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0238112881394702</v>
+        <v>0.009718103612711901</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02557725918634797</v>
+        <v>0.01605165463394409</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02165363793150426</v>
+        <v>0.009276655793716485</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01617158868063236</v>
+        <v>0.009822441168807658</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02392174378189804</v>
+        <v>0.01597748818379151</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0239410073135584</v>
+        <v>0.01634702124659333</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02381730208453592</v>
+        <v>0.009826728535401169</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02394255812184684</v>
+        <v>0.01033386821761942</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01590341999060053</v>
+        <v>0.009927643566777396</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03218382479716106</v>
+        <v>0.00994942257416576</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01928206968125574</v>
+        <v>0.01016978460595653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.023486795271042</v>
+        <v>0.01004607937693382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02361050431112975</v>
+        <v>0.01016912436841817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02848171503665616</v>
+        <v>0.01003730854149147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02348679441755738</v>
+        <v>0.01003730854149147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02359123696840409</v>
+        <v>0.01015052107429595</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02361050050006472</v>
+        <v>0.01016978460595653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.023486795271042</v>
+        <v>0.01004607937693382</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02361050050006472</v>
+        <v>0.01016978460595653</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02110259228750656</v>
+        <v>0.01016978460595653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02361050050006472</v>
+        <v>0.01016978460595653</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01635101157193901</v>
+        <v>0.01604999951170842</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01473413886682383</v>
+        <v>0.02381128813947021</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01556213059460178</v>
+        <v>0.02557725918634792</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01473413886682383</v>
+        <v>0.02165363793150427</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01473413886682383</v>
+        <v>0.01617158868063235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01486816337811961</v>
+        <v>0.02392174378189798</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01562506165035026</v>
+        <v>0.02394100731355838</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01473413886682383</v>
+        <v>0.02381730208453589</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01427719688578538</v>
+        <v>0.02394255812184684</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0157735739889792</v>
+        <v>0.01590341999060049</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01628248934125434</v>
+        <v>0.03218382479716104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01928206968125572</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02348679527104199</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02361050431112976</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02848171503665617</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02348679441755742</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02359123696840408</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02361050050006471</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02348679527104199</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0236105005000647</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02110259228750653</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0236105005000647</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01635101157193903</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01473413886682383</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01556213059460178</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01473413886682383</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01473413886682383</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01486816337811963</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01562506165035029</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01473413886682383</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01427719688578536</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01577357398897921</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01628248934125438</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01631080721356141</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01536065578959292</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01598953833300589</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01536065578959292</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01536065578959292</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01570091960004304</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01601638261525831</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01536065578959292</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01546718223961134</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>0.01631080721356142</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01536065578959293</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01598953833300591</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01536065578959293</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01536065578959293</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01570091960004305</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01601638261525833</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01536065578959293</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01546718223961135</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01607568376373346</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.01628341755470585</v>
+      <c r="L11" t="n">
+        <v>0.01628341755470587</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06932163909801392</v>
+        <v>0.03473330842115212</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1056636416547755</v>
+        <v>0.0125684085093685</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1853413815752257</v>
+        <v>0.0188591979959335</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09129560488911352</v>
+        <v>0.01528966439899339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09129560488911352</v>
+        <v>0.01528966439899339</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1677645278485818</v>
+        <v>0.01563818158665926</v>
       </c>
       <c r="H2" t="n">
-        <v>0.400958677990027</v>
+        <v>0.01905277083994072</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09129560488911352</v>
+        <v>0.01528966439899339</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3184141441699984</v>
+        <v>0.02044126533427076</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0842501575992252</v>
+        <v>0.02047454020775541</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2755977986354497</v>
+        <v>0.0202854856018275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006443548947301362</v>
+        <v>0.03535177640026115</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005548624677623853</v>
+        <v>0.01279645569868557</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006443548947301358</v>
+        <v>0.01909526732267649</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006056539126451196</v>
+        <v>0.01557617369912947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006056539126451196</v>
+        <v>0.01557617369912947</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006419338588373701</v>
+        <v>0.01584756543269746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006443548947301361</v>
+        <v>0.01909526732267649</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006287756124814338</v>
+        <v>0.01557617369912947</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006443548947301361</v>
+        <v>0.02056853269269775</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006443548947301358</v>
+        <v>0.02084990904960937</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006443548947301358</v>
+        <v>0.02047997676479263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01705216493481322</v>
+        <v>0.06932163909801396</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009906801803048032</v>
+        <v>0.1056636416547763</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01026157793173455</v>
+        <v>0.185341381575226</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00935399869793657</v>
+        <v>0.09129560488911355</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009991520519516968</v>
+        <v>0.09129560488911355</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01013561670891362</v>
+        <v>0.1677645278485825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01767201654512473</v>
+        <v>0.4009586779900277</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01000403424535427</v>
+        <v>0.09129560488911355</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01711872710094959</v>
+        <v>0.3184141441699984</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009992369460111537</v>
+        <v>0.0842501575992252</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01019802931563762</v>
+        <v>0.2755977986354498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01108280400470998</v>
+        <v>0.006443548947301366</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01106944484616779</v>
+        <v>0.005548624677623878</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01108215876851229</v>
+        <v>0.006443548947301366</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01092773090313196</v>
+        <v>0.00605653912645119</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01092773090313196</v>
+        <v>0.006056539126451196</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01105859364578228</v>
+        <v>0.006419338588373679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01108280400470998</v>
+        <v>0.006443548947301366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01092701118222295</v>
+        <v>0.006287756124814335</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01108280400470998</v>
+        <v>0.006443548947301366</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01108280400470998</v>
+        <v>0.006443548947301366</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01108280400470998</v>
+        <v>0.006443548947301366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.017826153040114</v>
+        <v>0.01705216493481325</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02702522554889992</v>
+        <v>0.009906801803047966</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02894487379351923</v>
+        <v>0.01026157793173456</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02436367348920617</v>
+        <v>0.009353998697936567</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01796309014640703</v>
+        <v>0.009991520519516987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02701108730493804</v>
+        <v>0.01013561670891363</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02703529766388028</v>
+        <v>0.01767201654512475</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02687950484137867</v>
+        <v>0.0100040342453543</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0270371075230308</v>
+        <v>0.0171187271009496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01765508845085936</v>
+        <v>0.009992369460111537</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03665501927809692</v>
+        <v>0.01019802931563764</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02378384936160442</v>
+        <v>0.01108280400471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02942643195259483</v>
+        <v>0.01106944484616779</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02943979348168608</v>
+        <v>0.0110821587685123</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03581083117551992</v>
+        <v>0.01092773090313198</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02928399340090544</v>
+        <v>0.01092773090313198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0294155807522094</v>
+        <v>0.01105859364578228</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02943979111113709</v>
+        <v>0.01108280400471</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02928399828865006</v>
+        <v>0.01092701118222295</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02943979111113709</v>
+        <v>0.01108280400471</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02616271724590455</v>
+        <v>0.01108280400471</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0294397911111371</v>
+        <v>0.01108280400471</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03390945247101712</v>
+        <v>0.01782615304011398</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01058904246727309</v>
+        <v>0.02702522554889996</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01498340745328789</v>
+        <v>0.02894487379351923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0136544553766314</v>
+        <v>0.02436367348920618</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0136544553766314</v>
+        <v>0.01796309014640698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225089245784049</v>
+        <v>0.02701108730493807</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01108058176715215</v>
+        <v>0.02703529766388025</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01365445537663141</v>
+        <v>0.02687950484137876</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01374784033338289</v>
+        <v>0.02703710752303082</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01908199363347013</v>
+        <v>0.01765508845085937</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01512965722338236</v>
+        <v>0.03665501927809689</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02378384936160448</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02942643195259482</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02943979348168609</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03581083117551997</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02928399340090549</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02941558075220942</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02943979111113708</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02928399828865009</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02943979111113708</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02616271724590457</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02943979111113708</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03390945247101715</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01058904246727309</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01498340745328789</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01365445537663142</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01365445537663141</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01225089245784047</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01108058176715214</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01365445537663142</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01374784033338292</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01908199363347013</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01512965722338237</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03407704643693241</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01156402845446723</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01698828865164179</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01441527643810383</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01441527643810383</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.0340770464369324</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01156402845446724</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0169882886516418</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01441527643810384</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01441527643810384</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01400168392118264</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.01540606337088974</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.01441527643810383</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01733782857452565</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01967013305939991</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01785107316002911</v>
+      <c r="I11" t="n">
+        <v>0.01441527643810384</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01733782857452566</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01967013305939989</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0178510731600291</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03566263228073646</v>
+        <v>0.0345482577576664</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07282172610564916</v>
+        <v>0.01231804950491316</v>
       </c>
       <c r="D2" t="n">
-        <v>0.127972620645674</v>
+        <v>0.01860277345557435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05700351401274982</v>
+        <v>0.01514631427208453</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05700351401274982</v>
+        <v>0.01514631427208453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1026380547335815</v>
+        <v>0.01541552741341962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2031333632804171</v>
+        <v>0.01866688054821991</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05700351401274982</v>
+        <v>0.01514631427208453</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2046314211194552</v>
+        <v>0.02049632094558394</v>
       </c>
       <c r="K2" t="n">
-        <v>0.04265089424436951</v>
+        <v>0.02029313325713466</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09325557312266913</v>
+        <v>0.01753554444700416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.03519756446989945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005366565638422484</v>
+        <v>0.01257280700371659</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.01889026036726296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006369052987261419</v>
+        <v>0.01546400986881857</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006369052987261419</v>
+        <v>0.01546400986881857</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006120303489705606</v>
+        <v>0.01568537333699106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.01889026036726296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006001591968932133</v>
+        <v>0.01546400986881857</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.02073343523412089</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.02070861445326387</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006142162204126492</v>
+        <v>0.01785988572838949</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01611586754294746</v>
+        <v>0.03566263228073651</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00959046625009034</v>
+        <v>0.07282172610564919</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01617797826330676</v>
+        <v>0.1279726206456744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00913982247756529</v>
+        <v>0.05700351401274976</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009687876379596901</v>
+        <v>0.05700351401274976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01609400882852658</v>
+        <v>0.102638054733581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0167220253041131</v>
+        <v>0.203133363280417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00965016916788569</v>
+        <v>0.05700351401274976</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01021792016524645</v>
+        <v>0.2046314211194549</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009709443606204241</v>
+        <v>0.04265089424436959</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009765505509768868</v>
+        <v>0.09325557312266926</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01030576999393318</v>
+        <v>0.006142162204126424</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01029407269388478</v>
+        <v>0.005366565638422484</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01030517064710297</v>
+        <v>0.006142162204126424</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01019978632987534</v>
+        <v>0.006369052987261413</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01019978632987534</v>
+        <v>0.006369052987261402</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01028391127951228</v>
+        <v>0.006120303489705587</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01030576999393318</v>
+        <v>0.006142162204126424</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01016519975873881</v>
+        <v>0.006001591968932135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01030576999393318</v>
+        <v>0.006142162204126424</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01030576999393318</v>
+        <v>0.006142162204126424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01030576999393318</v>
+        <v>0.006142162204126424</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01656055382757956</v>
+        <v>0.01611586754294749</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0250629319684797</v>
+        <v>0.009590466250090626</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02679728182882806</v>
+        <v>0.01617797826330673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0226113515216412</v>
+        <v>0.009139822477565299</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01670973315043243</v>
+        <v>0.009687876379596911</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02501732415053141</v>
+        <v>0.01609400882852656</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02503918286499119</v>
+        <v>0.01672202530411302</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02489861262975792</v>
+        <v>0.009650169167885699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02504084915588883</v>
+        <v>0.0102179201652465</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01640305894047098</v>
+        <v>0.00970944360620426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03389581986358139</v>
+        <v>0.009765505509768879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02021832057680241</v>
+        <v>0.01030576999393319</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02490854761999739</v>
+        <v>0.0102940726938848</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02492024798986126</v>
+        <v>0.01030517064710298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03020559552837916</v>
+        <v>0.01019978632987535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0247796723434725</v>
+        <v>0.01019978632987535</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02489838620562492</v>
+        <v>0.01028391127951225</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02492024492004585</v>
+        <v>0.01030576999393319</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02477967468485144</v>
+        <v>0.01016519975873881</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02492024492004585</v>
+        <v>0.01030576999393319</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02219593278084146</v>
+        <v>0.01030576999393319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02492024492004585</v>
+        <v>0.01030576999393319</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03446507729901041</v>
+        <v>0.01656055382757951</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0110123455074196</v>
+        <v>0.02506293196847957</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01593926284127374</v>
+        <v>0.02679728182882805</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01425414714373325</v>
+        <v>0.02261135152164124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01425414714373325</v>
+        <v>0.0167097331504324</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0134211634060226</v>
+        <v>0.02501732415053138</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01467646645691796</v>
+        <v>0.02503918286499116</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01425414714373325</v>
+        <v>0.02489861262975796</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01615871317859079</v>
+        <v>0.02504084915588889</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01984327464660158</v>
+        <v>0.01640305894047102</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01604831699786582</v>
+        <v>0.03389581986358133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02021832057680237</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02490854761999737</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02492024798986122</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03020559552837914</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02477967234347249</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02489838620562483</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0249202449200458</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02477967468485146</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0249202449200458</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0221959327808414</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0249202449200458</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03446507729901042</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0110123455074196</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01593926284127367</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01425414714373325</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01425414714373325</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01342116340602261</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01467646645691797</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01425414714373325</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01615871317859077</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01984327464660153</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01604831699786581</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03421497376061383</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.03421497376061381</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01160803455120232</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.01726006017697815</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01459582287656699</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01459582287656699</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01438530467922006</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01674959089044853</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01459582287656699</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01841480783154359</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01989940088742899</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01671127490148891</v>
+      <c r="D11" t="n">
+        <v>0.01726006017697814</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01459582287656697</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01459582287656697</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01438530467922008</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01674959089044854</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01459582287656697</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01841480783154353</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01989940088742893</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01671127490148893</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,320 +2415,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01754400429429657</v>
+        <v>0.03440816950054371</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05426225857546724</v>
+        <v>0.01205337004433786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08315767618002008</v>
+        <v>0.01834203449271238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02437973236168144</v>
+        <v>0.01407664620772939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02437973236168144</v>
+        <v>0.01407664620772939</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06108203974178943</v>
+        <v>0.0147528872926678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1016559286407238</v>
+        <v>0.01835210807433097</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02437973236168144</v>
+        <v>0.01407664620772939</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09880409661338992</v>
+        <v>0.01720925411520839</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02331256625590554</v>
+        <v>0.02007378949111134</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03768973529605314</v>
+        <v>0.01714774724464857</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005998144059690678</v>
+        <v>0.03507722593868844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005253650529548798</v>
+        <v>0.01232646998172064</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005998144059690677</v>
+        <v>0.01867950635446309</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006178528710492401</v>
+        <v>0.01441664826865835</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006178528710492403</v>
+        <v>0.01441664826865835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005977871753131908</v>
+        <v>0.01506122145254537</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005998144059690677</v>
+        <v>0.01867950635446309</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005868080534416852</v>
+        <v>0.01441664826865835</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005998144059690677</v>
+        <v>0.01751501665320657</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005998144059690677</v>
+        <v>0.02050968886935664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005998144059690677</v>
+        <v>0.01752480281917438</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009631053651396266</v>
+        <v>0.01754400429429664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009470729881832068</v>
+        <v>0.05426225857546736</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00966605218299213</v>
+        <v>0.08315767618002012</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008976249033266583</v>
+        <v>0.02437973236168146</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009529526621254093</v>
+        <v>0.02437973236168146</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0157907594130491</v>
+        <v>0.06108203974178915</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01637150214330458</v>
+        <v>0.1016559286407242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01568096819433401</v>
+        <v>0.02437973236168146</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01586317281572165</v>
+        <v>0.09880409661338997</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009609066119792861</v>
+        <v>0.02331256625590561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009584489144395816</v>
+        <v>0.03768973529605318</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009952521264511882</v>
+        <v>0.005998144059690682</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009942077908646969</v>
+        <v>0.005253650529548811</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009951924278397958</v>
+        <v>0.005998144059690682</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009866750908424966</v>
+        <v>0.006178528710492416</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009866750908424966</v>
+        <v>0.006178528710492419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009932248957953112</v>
+        <v>0.005977871753131913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009952521264511882</v>
+        <v>0.005998144059690682</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009822457739238059</v>
+        <v>0.005868080534416859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009952521264511882</v>
+        <v>0.005998144059690682</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009952521264511882</v>
+        <v>0.005998144059690682</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009952521264511882</v>
+        <v>0.005998144059690682</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0160804237447783</v>
+        <v>0.009631053651396299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02437325926199103</v>
+        <v>0.009470729881832092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02605148430024164</v>
+        <v>0.009666052182991597</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02199012290741785</v>
+        <v>0.00897624903326661</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01623892387970491</v>
+        <v>0.009529526621254128</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02431873988066171</v>
+        <v>0.0157907594130491</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02433901218725545</v>
+        <v>0.01637150214330462</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02420894866194663</v>
+        <v>0.01568096819433404</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02434063523280307</v>
+        <v>0.01586317281572169</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01592701622479147</v>
+        <v>0.009609066119792974</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03296579838392246</v>
+        <v>0.009584489144395848</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.018164809531677</v>
+        <v>0.009952521264511903</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02232539049541153</v>
+        <v>0.009942077908646993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02233583700018852</v>
+        <v>0.009951924278397984</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02701904510657758</v>
+        <v>0.009866750908424997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02220576897336915</v>
+        <v>0.009866750908424997</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02231556154471766</v>
+        <v>0.009932248957953138</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0223358338512765</v>
+        <v>0.009952521264511903</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02220577032600264</v>
+        <v>0.009822457739238084</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0223358338512765</v>
+        <v>0.009952521264511903</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01982107833891018</v>
+        <v>0.009952521264511903</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0223358338512765</v>
+        <v>0.009952521264511903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03476870185255929</v>
+        <v>0.01608042374477837</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01120204079907874</v>
+        <v>0.02437325926199105</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01681738368983917</v>
+        <v>0.02605148430024163</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01399038906330048</v>
+        <v>0.02199012290741786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01399038906330048</v>
+        <v>0.01623892387970491</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01377671342028826</v>
+        <v>0.0243187398806617</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01664514933455588</v>
+        <v>0.02433901218725543</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01399038906330048</v>
+        <v>0.02420894866194665</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01538726844001866</v>
+        <v>0.02434063523280312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02010964492375656</v>
+        <v>0.01592701622479151</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01688115927417427</v>
+        <v>0.0329657983839225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01816480953167704</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02232539049541164</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02233583700018861</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02701904510657767</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02220576897336922</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02231556154471777</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02233583385127655</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02220577032600271</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02233583385127655</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01982107833891025</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02233583385127655</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03476870185255931</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01120204079907874</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01681738368983918</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01399038906330049</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01399038906330049</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01377671342028827</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01664514933455589</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01399038906330049</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01538726844001869</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02010964492375662</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01688115927417428</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03426779005814697</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.034267790058147</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.0115417511828926</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.01749476274607566</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01388269691088407</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01388269691088407</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0141684320445066</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01742646914716201</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01388269691088407</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01624112189747666</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01989176822099888</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="D11" t="n">
+        <v>0.01749476274607567</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01388269691088408</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01388269691088408</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01416843204450661</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01742646914716202</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01388269691088408</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01624112189747668</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01989176822099891</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.01685488738050324</v>
       </c>
     </row>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02443023302757101</v>
+        <v>0.03410070886460505</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02013607259759961</v>
+        <v>0.01210912808457633</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1026720407202198</v>
+        <v>0.01839259137925285</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05311527490082856</v>
+        <v>0.01499897241077094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05311527490082856</v>
+        <v>0.01499897241077094</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1090403211372298</v>
+        <v>0.01528941459069432</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3136411234500877</v>
+        <v>0.01859076752053306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05311527490082856</v>
+        <v>0.01499897241077094</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2987465353176096</v>
+        <v>0.02018605281438978</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05876428188221008</v>
+        <v>0.02026789491176031</v>
       </c>
       <c r="L2" t="n">
-        <v>0.257394049326249</v>
+        <v>0.02008329005079411</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.03475879873001809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005189054282197531</v>
+        <v>0.01242417962102292</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.01871457319539178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005938217678950697</v>
+        <v>0.01532376280829967</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005938217678950697</v>
+        <v>0.01532376280829967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006075155434047164</v>
+        <v>0.01555804095122376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.01871457319539178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00594883455376789</v>
+        <v>0.01532376280829967</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.02033105118897333</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.02066912432234459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006098353289801029</v>
+        <v>0.02029321034292011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009570606516941639</v>
+        <v>0.02443023302757099</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009255556826542981</v>
+        <v>0.02013607259759963</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009603491696131332</v>
+        <v>0.1026720407202199</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008844461088363684</v>
+        <v>0.05311527490082903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009426063025988701</v>
+        <v>0.05311527490082903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00954740866118778</v>
+        <v>0.1090403211372296</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01667374375391158</v>
+        <v>0.3136411234500879</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0159703997537597</v>
+        <v>0.05311527490082903</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01000082907865955</v>
+        <v>0.2987465353176098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009445167161775531</v>
+        <v>0.05876428188221008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009617419824393148</v>
+        <v>0.257394049326249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0104711047239384</v>
+        <v>0.006098353289801032</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01045804900118981</v>
+        <v>0.00518905428219749</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0104704627066159</v>
+        <v>0.006098353289801032</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01038069739671472</v>
+        <v>0.005938217678950693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01038069739671472</v>
+        <v>0.005938217678950693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01044790686818453</v>
+        <v>0.006075155434047163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0104711047239384</v>
+        <v>0.006098353289801032</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01032158598790526</v>
+        <v>0.005948834553767889</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0104711047239384</v>
+        <v>0.006098353289801032</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0104711047239384</v>
+        <v>0.006098353289801032</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0104711047239384</v>
+        <v>0.006098353289801032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01698536058598364</v>
+        <v>0.009570606516941643</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02586127361838941</v>
+        <v>0.009255556826543812</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02764627115695391</v>
+        <v>0.009603491696131311</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02330351689825455</v>
+        <v>0.008844461088363738</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01715138378963755</v>
+        <v>0.00942606302598871</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0257921234286239</v>
+        <v>0.009547408661187794</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02581532128438241</v>
+        <v>0.01667374375391155</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02566580254834461</v>
+        <v>0.01597039975375972</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02581705662315587</v>
+        <v>0.01000082907865952</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01682133953281389</v>
+        <v>0.009445167161775504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03503895358181913</v>
+        <v>0.009617419824393117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02187163180912522</v>
+        <v>0.01047110472393839</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02705316889173424</v>
+        <v>0.01045804900118984</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02706622672656266</v>
+        <v>0.01047046270661587</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03291115310320303</v>
+        <v>0.01038069739671474</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02691670216745269</v>
+        <v>0.01038069739671474</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02704302675872897</v>
+        <v>0.01044790686818453</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.01047110472393839</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02691670587844969</v>
+        <v>0.01032158598790527</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.01047110472393839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02405645803065128</v>
+        <v>0.01047110472393839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02706622461448283</v>
+        <v>0.01047110472393839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03431480207805999</v>
+        <v>0.01698536058598363</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01213199274176581</v>
+        <v>0.02586127361838949</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01650581600410646</v>
+        <v>0.02764627115695396</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01426820738076993</v>
+        <v>0.02330351689825457</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01426820738076993</v>
+        <v>0.01715138378963758</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01327141788772327</v>
+        <v>0.02579212342862394</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01247285226955435</v>
+        <v>0.02581532128438246</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01426820738076993</v>
+        <v>0.02566580254834464</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0139347738907986</v>
+        <v>0.02581705662315591</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01948032708772404</v>
+        <v>0.01682133953281387</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01530000727861151</v>
+        <v>0.03503895358181919</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0218716318091253</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02705316889173432</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02706622672656274</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03291115310320315</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02691670216745275</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02704302675872899</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02706622461448291</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02691670587844974</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02706622461448291</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02405645803065132</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02706622461448291</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03431480207805998</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01213199274176582</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01650581600410647</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01426820738076993</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01426820738076993</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01327141788772327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01247285226955434</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01426820738076993</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01393477389079864</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0194803270877241</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01530000727861151</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03389868897303071</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01197618212337</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01738759981832649</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01451869132738935</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01451869132738935</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01424899380976625</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01575076460809263</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01451869132738935</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01727572625999398</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01972698838153592</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01781136674413967</v>
+      <c r="B11" t="n">
+        <v>0.0338986889730307</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01197618212337001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01738759981832651</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01451869132738936</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01451869132738936</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01424899380976626</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01575076460809264</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01451869132738936</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01727572625999401</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01972698838153598</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01781136674413968</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01469266076226581</v>
+        <v>0.03376331250800629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0164524213115163</v>
+        <v>0.01185385697022456</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02189983158972843</v>
+        <v>0.01801300130430388</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03594032844841771</v>
+        <v>0.0147382018635888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03594032844841771</v>
+        <v>0.0147382018635888</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02870244859230287</v>
+        <v>0.01489518850083001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03485154433951674</v>
+        <v>0.01802448867304867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03594032844841771</v>
+        <v>0.0147382018635888</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1014326194051136</v>
+        <v>0.01980254339748134</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01968717565083522</v>
+        <v>0.01990072479730656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04589758143603024</v>
+        <v>0.01715823277107646</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.0344259250345859</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005036213104221773</v>
+        <v>0.01216795040521388</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.01841819660979854</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006154773740727679</v>
+        <v>0.01507522812962288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006154773740727678</v>
+        <v>0.01507522812962288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005718718681627691</v>
+        <v>0.01524348058224879</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.01841819660979854</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005611829457015641</v>
+        <v>0.01507522812962288</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.02014705262490482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.02033862332091315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0057383483939557</v>
+        <v>0.01752741472116614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009095003687727062</v>
+        <v>0.01469266076226581</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008912936201063124</v>
+        <v>0.01645242131151626</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01497291759548522</v>
+        <v>0.02189983158972839</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008578973916397959</v>
+        <v>0.03594032844841773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009022414174055219</v>
+        <v>0.03594032844841773</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009075373975399061</v>
+        <v>0.02870244859230375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01539373479638963</v>
+        <v>0.03485154433951673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01484524564885834</v>
+        <v>0.03594032844841773</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01496451119499656</v>
+        <v>0.1014326194051135</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009063137248967434</v>
+        <v>0.01968717565083521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009064244763347678</v>
+        <v>0.04589758143603018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009482849849344846</v>
+        <v>0.005738348393955684</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009473230527116652</v>
+        <v>0.005036213104221765</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009482241145564512</v>
+        <v>0.005738348393955681</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009431490829727168</v>
+        <v>0.00615477374072769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009431490829727168</v>
+        <v>0.006154773740727692</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009463220137016851</v>
+        <v>0.005718718681627684</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009482849849344846</v>
+        <v>0.005738348393955684</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009356330912404811</v>
+        <v>0.005611829457015655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009482849849344846</v>
+        <v>0.005738348393955684</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009482849849344846</v>
+        <v>0.005738348393955684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009482849849344846</v>
+        <v>0.005738348393955684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01537474211672333</v>
+        <v>0.009095003687727039</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02329434388080852</v>
+        <v>0.008912936201063119</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02485865176958352</v>
+        <v>0.01497291759548521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02102117315440473</v>
+        <v>0.008578973916397932</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01554241747364229</v>
+        <v>0.009022414174055221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321021530059296</v>
+        <v>0.009075373975399053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02322984501293616</v>
+        <v>0.01539373479638963</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02310332607598095</v>
+        <v>0.01484524564885834</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02323138876409447</v>
+        <v>0.01496451119499656</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01522882954772868</v>
+        <v>0.009063137248967734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03143515681960678</v>
+        <v>0.009064244763347665</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01808628822454987</v>
+        <v>0.009482849849344841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.022245519205877</v>
+        <v>0.009473230527116639</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02225514154462051</v>
+        <v>0.009482241145564511</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02693938691484158</v>
+        <v>0.009431490829727168</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0221286193834948</v>
+        <v>0.009431490829727168</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0222355088157772</v>
+        <v>0.009463220137016832</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02225513852810518</v>
+        <v>0.009482849849344841</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02212861959116516</v>
+        <v>0.00935633091240479</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02225513852810518</v>
+        <v>0.009482849849344841</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01983969155862145</v>
+        <v>0.009482849849344841</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02225513852810518</v>
+        <v>0.009482849849344841</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03418286467798955</v>
+        <v>0.01537474211672332</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01193768076083247</v>
+        <v>0.02329434388080858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01804752854687246</v>
+        <v>0.02485865176958344</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.02102117315440478</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.01554241747364232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01472270094334752</v>
+        <v>0.02321021530059296</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0178184079667748</v>
+        <v>0.02322984501293615</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01436668882565508</v>
+        <v>0.02310332607598093</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0179553468635823</v>
+        <v>0.02323138876409448</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02002348059799822</v>
+        <v>0.01522882954772865</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01670778218826463</v>
+        <v>0.03143515681960675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01808628822454986</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02224551920587705</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0222551415446205</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02693938691484161</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02212861938349479</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02223550881577722</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0222551385281052</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02212861959116518</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0222551385281052</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01983969155862149</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0222551385281052</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03418286467798956</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01193768076083247</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01804752854687246</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01436668882565507</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01436668882565507</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01472270094334751</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01781840796677479</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01436668882565507</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01795534686358227</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02002348059799823</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01670778218826463</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03365271927116754</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01174908354820521</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01784434615442351</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01441581422230267</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01441581422230267</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01465823210550366</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01775158292905986</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01441581422230267</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0188053102915278</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01975733385408002</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>0.03365271927116751</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0117490835482052</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01784434615442349</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01441581422230266</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01441581422230266</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01465823210550367</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01775158292905985</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01441581422230266</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01880531029152779</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01975733385408001</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.01678529735659236</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01305614759776515</v>
+        <v>0.03343676853251255</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01556989171540091</v>
+        <v>0.0116364357475448</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01962447481022692</v>
+        <v>0.01784615370714094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0248883504862945</v>
+        <v>0.01365544755886232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0248883504862945</v>
+        <v>0.01365544755886232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01947722552275833</v>
+        <v>0.01425417995712801</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02213250556716191</v>
+        <v>0.0178469723616509</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0248883504862945</v>
+        <v>0.01365544755886232</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03168558803245445</v>
+        <v>0.01646979490366802</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01492466610695831</v>
+        <v>0.0196321564848064</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01957772479904769</v>
+        <v>0.01677402357300314</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005634330187880427</v>
+        <v>0.03409710316398022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005015384967029112</v>
+        <v>0.01194913509447892</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005634330187880427</v>
+        <v>0.0182524304763761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005912470534889181</v>
+        <v>0.01398930518472344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005912470534889182</v>
+        <v>0.01398930518472345</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00561580363181582</v>
+        <v>0.01460397604748405</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005634330187880426</v>
+        <v>0.0182524304763761</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00551527302001355</v>
+        <v>0.01398930518472345</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005634330187880426</v>
+        <v>0.01684130989441633</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005634330187880427</v>
+        <v>0.02007244154905371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005634330187880427</v>
+        <v>0.01716550157746552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01483693823155871</v>
+        <v>0.01305614759776527</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008874541359925841</v>
+        <v>0.01556989171540091</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008979878643483208</v>
+        <v>0.01962447481022701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008486221699435472</v>
+        <v>0.02488835048629459</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008947015611471517</v>
+        <v>0.02488835048629459</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01481841167549417</v>
+        <v>0.0194772255227586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008992336716212919</v>
+        <v>0.02213250556716202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01471788106369177</v>
+        <v>0.02488835048629459</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009373953151422044</v>
+        <v>0.03168558803245452</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009027852603792271</v>
+        <v>0.01492466610695847</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980211993040773</v>
+        <v>0.01957772479904771</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00922112016263427</v>
+        <v>0.005634330187880542</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009211941865994276</v>
+        <v>0.005015384967029051</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009220506126847591</v>
+        <v>0.005634330187880542</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009163256856446211</v>
+        <v>0.005912470534889183</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009163256856446211</v>
+        <v>0.005912470534889184</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009202593606569656</v>
+        <v>0.005615803631815958</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00922112016263427</v>
+        <v>0.005634330187880542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009102062994767339</v>
+        <v>0.005515273020013559</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00922112016263427</v>
+        <v>0.005634330187880543</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00922112016263427</v>
+        <v>0.005634330187880542</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00922112016263427</v>
+        <v>0.005634330187880542</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01502549467862041</v>
+        <v>0.01483693823155877</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02273884883681684</v>
+        <v>0.008874541359925943</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02427598890873318</v>
+        <v>0.008979878643483272</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02052696590113575</v>
+        <v>0.008486221699435558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01518617536660866</v>
+        <v>0.008947015611471499</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02266874334795187</v>
+        <v>0.01481841167549421</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02268726990403314</v>
+        <v>0.00899233671621295</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02256821273614945</v>
+        <v>0.01471788106369179</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02268877566085957</v>
+        <v>0.009373953151422053</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01488317327035187</v>
+        <v>0.009027852603792283</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03069063479284784</v>
+        <v>0.008980211993040889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01683380052436988</v>
+        <v>0.009221120162634299</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02065953048093008</v>
+        <v>0.009211941865994262</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02066871160804129</v>
+        <v>0.009220506126847643</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0249750567314498</v>
+        <v>0.009163256856446211</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02054965141134852</v>
+        <v>0.009163256856446211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02065018222150551</v>
+        <v>0.009202593606569724</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02066870877757</v>
+        <v>0.009221120162634299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02054965160970312</v>
+        <v>0.009102062994767313</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02066870877757</v>
+        <v>0.009221120162634299</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01844674906530442</v>
+        <v>0.009221120162634299</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02066870877757</v>
+        <v>0.009221120162634299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0338907720018842</v>
+        <v>0.01502549467862042</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01173807249312139</v>
+        <v>0.02273884883681681</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01793543334125653</v>
+        <v>0.02427598890873321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01354602797210378</v>
+        <v>0.02052696590113572</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01354602797210378</v>
+        <v>0.01518617536660864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01429988427947812</v>
+        <v>0.02266874334795182</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01792464820108216</v>
+        <v>0.02268726990403315</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01354602797210378</v>
+        <v>0.02256821273614945</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01626343253988382</v>
+        <v>0.02268877566085965</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987117204436594</v>
+        <v>0.01488317327035193</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0168993476019157</v>
+        <v>0.03069063479284781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01683380052436989</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02065953048093007</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02066871160804125</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02497505673144978</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02054965141134854</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02065018222150551</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02066870877757012</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02054965160970312</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02066870877757012</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01844674906530434</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02066870877757012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03389077200188425</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01173807249312138</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01793543334125654</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01354602797210378</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01354602797210378</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01429988427947816</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01792464820108219</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01354602797210378</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01626343253988382</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01987117204436597</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01689934760191569</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03334288719622042</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01154040159131052</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01770191900045167</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01345375501447969</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01345375501447969</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01411581723360232</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.017697830381812</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01345375501447969</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.03334288719622043</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01154040159131051</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01770191900045164</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0134537550144797</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0134537550144797</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01411581723360236</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01769783038181203</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0134537550144797</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01620685886576988</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01954057821876558</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01665292266594552</v>
+      <c r="K11" t="n">
+        <v>0.01954057821876562</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01665292266594557</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02139601711706897</v>
+        <v>0.03387025580268504</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01827196383736493</v>
+        <v>0.01202993869040199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03561803360860368</v>
+        <v>0.01817382070175814</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04814996855239512</v>
+        <v>0.01485365098798328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04814996855239512</v>
+        <v>0.01485365098798328</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05586561352728539</v>
+        <v>0.01504523712183208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2613026517835408</v>
+        <v>0.01839407204215411</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04814996855239512</v>
+        <v>0.01485365098798328</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06935054329283184</v>
+        <v>0.01957722139143979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03251767670775916</v>
+        <v>0.02003947740548267</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2092248825258979</v>
+        <v>0.01990384637567828</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.03452902889523517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005097037290959923</v>
+        <v>0.01234675387511589</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.0185684647390403</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005888606372785381</v>
+        <v>0.01518226254165936</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005888606372785382</v>
+        <v>0.01518226254165936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005951676441429237</v>
+        <v>0.01536894937128034</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.0185684647390403</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005834425575268198</v>
+        <v>0.01518226254165936</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.01995951729735167</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.02046737808902018</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005973177899667545</v>
+        <v>0.02015933904669326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009263995279809537</v>
+        <v>0.02139601711706898</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009024195211041712</v>
+        <v>0.01827196383736495</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009231990762864977</v>
+        <v>0.0356180336086037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008633892735647226</v>
+        <v>0.04814996855239516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009138743019248625</v>
+        <v>0.04814996855239516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009242493821571237</v>
+        <v>0.05586561352728667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01615540272323946</v>
+        <v>0.2613026517835406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009125242955410178</v>
+        <v>0.04814996855239516</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009607639518358989</v>
+        <v>0.06935054329283202</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009154594300674796</v>
+        <v>0.03251767670775905</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0092970938055783</v>
+        <v>0.2092248825258979</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01009945309639319</v>
+        <v>0.005973177899667528</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01008874956843792</v>
+        <v>0.005097037290959947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01009881349247932</v>
+        <v>0.005973177899667528</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01003025567124654</v>
+        <v>0.005888606372785371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01003025567124654</v>
+        <v>0.005888606372785388</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01007795163815491</v>
+        <v>0.00595167644142928</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01009945309639319</v>
+        <v>0.005973177899667528</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009960700771993805</v>
+        <v>0.005834425575268213</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01009945309639319</v>
+        <v>0.005973177899667528</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01009945309639319</v>
+        <v>0.005973177899667528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01009945309639319</v>
+        <v>0.005973177899667528</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01644264373429125</v>
+        <v>0.009263995279809504</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0250209022945642</v>
+        <v>0.009024195211041796</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02672936665571589</v>
+        <v>0.009231990762864925</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02255527480319372</v>
+        <v>0.008633892735647155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01661583787578834</v>
+        <v>0.009138743019248616</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02494117989449661</v>
+        <v>0.009242493821571262</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02496268135273777</v>
+        <v>0.01615540272323946</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02482392902833544</v>
+        <v>0.009125242955410163</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02496435578268355</v>
+        <v>0.009607639518358925</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01628437966145279</v>
+        <v>0.009154594300674669</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03386257307775793</v>
+        <v>0.009297093805578312</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02050514186035934</v>
+        <v>0.01009945309639314</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02532631851707976</v>
+        <v>0.01008874956843793</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02533702302269739</v>
+        <v>0.01009881349247929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03077415389017501</v>
+        <v>0.01003025567124655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02519826652467272</v>
+        <v>0.01003025567124655</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02531552058679672</v>
+        <v>0.01007795163815488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02533702204503498</v>
+        <v>0.01009945309639314</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02519826972063561</v>
+        <v>0.0099607007719938</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02533702204503498</v>
+        <v>0.01009945309639314</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02253741210097736</v>
+        <v>0.01009945309639314</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02533702204503498</v>
+        <v>0.01009945309639314</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03415122909217654</v>
+        <v>0.01644264373429124</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01209373716043794</v>
+        <v>0.02502090229456422</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01790644875325068</v>
+        <v>0.02672936665571591</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.02255527480319374</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.01661583787578836</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01427229651562812</v>
+        <v>0.02494117989449653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01339078954369531</v>
+        <v>0.02496268135273779</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01423764923145975</v>
+        <v>0.02482392902833547</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01859342025321832</v>
+        <v>0.02496435578268354</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01987970321746414</v>
+        <v>0.01628437966145279</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01612580737390198</v>
+        <v>0.03386257307775793</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02050514186035934</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02532631851707977</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02533702302269736</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03077415389017505</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02519826652467274</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02531552058679672</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02533702204503495</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02519826972063562</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02533702204503495</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02253741210097736</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02533702204503495</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03415122909217651</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01209373716043795</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01790644875325069</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01423764923145975</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01423764923145975</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0142722965156281</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01339078954369531</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01423764923145975</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01859342025321835</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01987970321746409</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01612580737390196</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.03369835568831688</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01191481527890708</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.03369835568831683</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01191481527890709</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.01787260131850409</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01442384892153846</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01442384892153846</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01454625657768502</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01603821332800034</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01442384892153846</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01895564288286613</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01977208346611602</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01806857661045549</v>
+      <c r="E11" t="n">
+        <v>0.01442384892153845</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01442384892153845</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01454625657768504</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01603821332800032</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01442384892153845</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01895564288286615</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01977208346611597</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01806857661045548</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01637788248865744</v>
+        <v>0.03252762080947923</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01702646375701892</v>
+        <v>0.01188632239388481</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02062721120133768</v>
+        <v>0.01797141398041936</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03456644372086105</v>
+        <v>0.01472598229200823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03456644372086105</v>
+        <v>0.01472598229200823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02251032810071185</v>
+        <v>0.01476759042204524</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02372825352167917</v>
+        <v>0.01797273974260491</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03456644372086105</v>
+        <v>0.01472598229200823</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03760486951072425</v>
+        <v>0.01964657484013099</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02194137942198481</v>
+        <v>0.01996469701501585</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02130760939791624</v>
+        <v>0.01711005643039046</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.03316863289335179</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005007851209893855</v>
+        <v>0.01220025394394923</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.01837743615067976</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006188714664728935</v>
+        <v>0.01506436199793555</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006188714664728935</v>
+        <v>0.01506436199793555</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005691902781972472</v>
+        <v>0.01512096358032691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.01837743615067976</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005586397700253472</v>
+        <v>0.01506436199793555</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.02006084624573464</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.02040093788573186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005711270204445756</v>
+        <v>0.01750401435820027</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0149129590637728</v>
+        <v>0.0163778824886575</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008877390106382665</v>
+        <v>0.01702646375701891</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009032267351266766</v>
+        <v>0.02062721120133774</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008552312685018302</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008983892858996652</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009032332192055821</v>
+        <v>0.02251032810071266</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01532147154003818</v>
+        <v>0.02372825352167927</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01478808655958051</v>
+        <v>0.03456644372086105</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009397109408732703</v>
+        <v>0.03760486951072421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009032116011430773</v>
+        <v>0.02194137942198482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009012744769876626</v>
+        <v>0.02130760939791635</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009387237433805666</v>
+        <v>0.005711270204445812</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009377995710604641</v>
+        <v>0.005007851209893852</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009386630867326056</v>
+        <v>0.005711270204445812</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009353645048142808</v>
+        <v>0.006188714664728943</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009353645048142808</v>
+        <v>0.006188714664728943</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009367870011332364</v>
+        <v>0.00569190278197247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009387237433805666</v>
+        <v>0.005711270204445812</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009262364929613369</v>
+        <v>0.005586397700253472</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009387237433805666</v>
+        <v>0.005711270204445807</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009387237433805666</v>
+        <v>0.005711270204445812</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009387237433805666</v>
+        <v>0.005711270204445812</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01523078983670679</v>
+        <v>0.01491295906377281</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02308124342956636</v>
+        <v>0.00887739010638278</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02461217964891879</v>
+        <v>0.009032267351266799</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02083093988692853</v>
+        <v>0.0085523126850183</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01540703523404357</v>
+        <v>0.008983892858996673</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02298161266083943</v>
+        <v>0.009032332192055839</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02300098008332481</v>
+        <v>0.01532147154003816</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02287610757912044</v>
+        <v>0.01478808655958054</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02300250714659913</v>
+        <v>0.009397109408732696</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01508645456378532</v>
+        <v>0.009032116011430863</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03111759352710051</v>
+        <v>0.009012744769876627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01791253261333253</v>
+        <v>0.009387237433805637</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02202694045117529</v>
+        <v>0.009377995710604648</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02203618513805123</v>
+        <v>0.009386630867326069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02666991644935741</v>
+        <v>0.009353645048142813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02191130962388278</v>
+        <v>0.009353645048142813</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02201681475190305</v>
+        <v>0.009367870011332371</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0220361821743763</v>
+        <v>0.009387237433805637</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02191130967018403</v>
+        <v>0.009262364929613361</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0220361821743763</v>
+        <v>0.009387237433805637</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01684377054005875</v>
+        <v>0.009387237433805637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0220361821743763</v>
+        <v>0.009387237433805637</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03288542354812124</v>
+        <v>0.01523078983670677</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01195595600823172</v>
+        <v>0.02308124342956637</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01803727408127816</v>
+        <v>0.02461217964891883</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01438850185206194</v>
+        <v>0.02083093988692851</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01438850185206194</v>
+        <v>0.01540703523404358</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01474630502830657</v>
+        <v>0.02298161266083949</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01801649643616657</v>
+        <v>0.02300098008332489</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01438850185206194</v>
+        <v>0.02287610757912048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01934710503856341</v>
+        <v>0.02300250714659918</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02003048196639647</v>
+        <v>0.01508645456378536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01720253680894133</v>
+        <v>0.0311175935271006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01791253261333253</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02202694045117532</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02203618513805127</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02666991644935744</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02191130962388281</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02201681475190308</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02203618217437636</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02191130967018409</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02203618217437636</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01684377054005876</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02203618217437636</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.03288542354812127</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01195595600823173</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01803727408127815</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01438850185206194</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01438850185206194</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01474630502830655</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01801649643616658</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01438850185206194</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01934710503856342</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02003048196639647</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01720253680894135</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.0323987596548647</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01177516605460205</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.03239875965486466</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01177516605460203</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.01781663915480942</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01441846377179724</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01441846377179724</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01459711958691005</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0178085110222548</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01441846377179724</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="E11" t="n">
+        <v>0.01441846377179725</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01441846377179725</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01459711958691004</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01780851102225479</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01441846377179725</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.0193218203163098</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.01979613839114528</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01697288318472572</v>
+      <c r="K11" t="n">
+        <v>0.01979613839114526</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0169728831847257</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01452925536178795</v>
+        <v>0.02903601547891271</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0158268126198933</v>
+        <v>0.01169148058425814</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01881726918486955</v>
+        <v>0.01781986727358295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02494009599691089</v>
+        <v>0.01364571866892579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02494009599691089</v>
+        <v>0.01364571866892579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01945991174890782</v>
+        <v>0.01387858439143962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02135012597240802</v>
+        <v>0.01782080630119856</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02494009599691089</v>
+        <v>0.01364571866892579</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03202120472592161</v>
+        <v>0.01644091142966678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01945715033856498</v>
+        <v>0.01967013372318059</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01951742819007203</v>
+        <v>0.01675776152206679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.02962460841766091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004989146035842907</v>
+        <v>0.01200469980228831</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.01822661833300665</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005926883031751219</v>
+        <v>0.01397929752403453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005926883031751219</v>
+        <v>0.01397929752403453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005597644528369807</v>
+        <v>0.01422236448202163</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.01822661833300665</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005498288719621207</v>
+        <v>0.01397929752403453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.01681152477268674</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.02010561655012981</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005615961176891413</v>
+        <v>0.01714898190568026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0148318959575536</v>
+        <v>0.01452925536178794</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008872817520469076</v>
+        <v>0.01582681261989331</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008976806403708635</v>
+        <v>0.01881726918486959</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008490877820592112</v>
+        <v>0.0249400959969109</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008950485785739573</v>
+        <v>0.0249400959969109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009008309990757565</v>
+        <v>0.01945991174890822</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01521274449956766</v>
+        <v>0.02135012597240805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008908954182008984</v>
+        <v>0.0249400959969109</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01482093559746565</v>
+        <v>0.03202120472592165</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009037656284100118</v>
+        <v>0.01945715033856494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008980151751440365</v>
+        <v>0.01951742819007206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009154556249630508</v>
+        <v>0.005615961176891392</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0091454240020472</v>
+        <v>0.004989146035842924</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009153944208555413</v>
+        <v>0.005615961176891392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009107388487643227</v>
+        <v>0.005926883031751217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009107388487643227</v>
+        <v>0.005926883031751217</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009136239601108929</v>
+        <v>0.005597644528369789</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009154556249630508</v>
+        <v>0.005615961176891392</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00903688379236032</v>
+        <v>0.005498288719621196</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009154556249630508</v>
+        <v>0.005615961176891392</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009154556249630508</v>
+        <v>0.005615961176891392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009154556249630508</v>
+        <v>0.005615961176891392</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01492095495190048</v>
+        <v>0.01483189595755355</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02258033324909286</v>
+        <v>0.008872817520469076</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02409549736516707</v>
+        <v>0.008976806403708586</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02038605389605647</v>
+        <v>0.008490877820592111</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01508657945318924</v>
+        <v>0.008950485785739584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02250150599820324</v>
+        <v>0.009008309990757569</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02251982264674063</v>
+        <v>0.01521274449956764</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02240215018945461</v>
+        <v>0.008908954182009002</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02252131604035937</v>
+        <v>0.01482093559746564</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01477980208331732</v>
+        <v>0.00903765628410012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03045747535955904</v>
+        <v>0.008980151751440384</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01678348020978125</v>
+        <v>0.009154556249630507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02059687013984993</v>
+        <v>0.009145424002047204</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02060600522066553</v>
+        <v>0.009153944208555359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02489944184432968</v>
+        <v>0.009107388487643239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02048832977859198</v>
+        <v>0.009107388487643239</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02058768573891163</v>
+        <v>0.009136239601108915</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02060600238743328</v>
+        <v>0.009154556249630507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02048832993016303</v>
+        <v>0.009036883792360341</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02060600238743328</v>
+        <v>0.009154556249630507</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01830136255128872</v>
+        <v>0.009154556249630507</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02060600238743328</v>
+        <v>0.009154556249630507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02938326219594543</v>
+        <v>0.01492095495190045</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01178739990999202</v>
+        <v>0.02258033324909284</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0179290702857276</v>
+        <v>0.02409549736516705</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01353455985729419</v>
+        <v>0.02038605389605648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01353455985729419</v>
+        <v>0.01508657945318923</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01391845053449591</v>
+        <v>0.02250150599820321</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01791544757057361</v>
+        <v>0.02251982264674062</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01353455985729419</v>
+        <v>0.02240215018945462</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01622563685781334</v>
+        <v>0.02252131604035937</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01979397711978833</v>
+        <v>0.01477980208331733</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01688387918997558</v>
+        <v>0.03045747535955902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01678348020978126</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02059687013984998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02060600522066557</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02489944184432972</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02048832977859199</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02058768573891166</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02060600238743329</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02048832993016309</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02060600238743329</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01830136255128872</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02060600238743329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02938326219594543</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01178739990999202</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01792907028572759</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0135345598572942</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0135345598572942</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01391845053449592</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01791544757057358</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0135345598572942</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01622563685781332</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01979397711978832</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0168838791899756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.02892620217890741</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.02892620217890739</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01159260844076965</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0176844819638416</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01768448196384159</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01344336161326409</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01344336161326409</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.01374030257679912</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.01767922261264912</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.01344336161326409</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01617433056128538</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01952833678923921</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01663713894158898</v>
+      <c r="J11" t="n">
+        <v>0.01617433056128537</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01952833678923923</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01663713894158896</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.238943124323766</v>
+        <v>0.01832996107999471</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09524105664293595</v>
+        <v>0.01808253101274666</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2870188602747542</v>
+        <v>0.01837648212314537</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09524105664293595</v>
+        <v>0.01808253101274666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09524105664293595</v>
+        <v>0.01808253101274666</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2972813302547633</v>
+        <v>0.01833970250112595</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7618618037462793</v>
+        <v>0.01881697658770666</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09524105664293595</v>
+        <v>0.01808253101274666</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3608618313939032</v>
+        <v>0.01843635479729782</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1331362577190282</v>
+        <v>0.01820624132197771</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3137813506713617</v>
+        <v>0.01837317061232878</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006159380652871534</v>
+        <v>0.01840520495136429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006355381061930058</v>
+        <v>0.01840520495136429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006355381061930057</v>
+        <v>0.01840520495136429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007071625880220763</v>
+        <v>0.01844804856453564</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006930522161783395</v>
+        <v>0.01840520495136429</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007097714620081565</v>
+        <v>0.01848987515049683</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01111195738076439</v>
+        <v>0.2389431243237645</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01051993262966376</v>
+        <v>0.09524105664293626</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01125858932725746</v>
+        <v>0.2870188602747548</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01005879807142514</v>
+        <v>0.09524105664293626</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01088955738618471</v>
+        <v>0.09524105664293626</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01108586864090359</v>
+        <v>0.2972813302547629</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01952137590291943</v>
+        <v>0.7618618037462805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0188556902341937</v>
+        <v>0.09524105664293626</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0115828477601816</v>
+        <v>0.3608618313939032</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01086493091182923</v>
+        <v>0.1331362577190279</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01144635977971159</v>
+        <v>0.3137813506713611</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01219132608665814</v>
+        <v>0.007097714620081574</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01202413362836001</v>
+        <v>0.006159380652871526</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01219061582344472</v>
+        <v>0.007097714620081574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01201490627370035</v>
+        <v>0.006355381061930055</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01201490627370035</v>
+        <v>0.006355381061930058</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01216523734679737</v>
+        <v>0.007071625880220762</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01219132608665814</v>
+        <v>0.007097714620081574</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01202413362836001</v>
+        <v>0.006930522161783398</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01219132608665814</v>
+        <v>0.007097714620081574</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01219132608665814</v>
+        <v>0.007097714620081574</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01219132608665814</v>
+        <v>0.007097714620081574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01938429305466473</v>
+        <v>0.01111195738076437</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02906983802882184</v>
+        <v>0.01051993262966363</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0312873079612012</v>
+        <v>0.01125858932725744</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02637401867096111</v>
+        <v>0.01005879807142513</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0195245265985846</v>
+        <v>0.01088955738618469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02921694509660377</v>
+        <v>0.01108586864090358</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02924303383646497</v>
+        <v>0.01952137590291941</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02907584137816635</v>
+        <v>0.01885569023419367</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02924497136012547</v>
+        <v>0.01158284776018158</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01920116188326454</v>
+        <v>0.01086493091182927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03954131295628511</v>
+        <v>0.01144635977971155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02783777072219436</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03429948172116127</v>
+        <v>0.01202413362836</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03446667488250336</v>
+        <v>0.01219061582344468</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04194908291088666</v>
+        <v>0.01201490627370034</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0342994709371302</v>
+        <v>0.01201490627370034</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03444058543959865</v>
+        <v>0.01216523734679736</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03446667417945944</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03429948172116127</v>
+        <v>0.01202413362836</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03446667417945944</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03062586177830535</v>
+        <v>0.01219132608665816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03446667417945944</v>
+        <v>0.01219132608665816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01301487821921214</v>
+        <v>0.01938429305466474</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01632827272988695</v>
+        <v>0.02906983802882175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01204337982147767</v>
+        <v>0.03128730796120122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01632827272988695</v>
+        <v>0.02637401867096111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01632827272988695</v>
+        <v>0.01952452659858459</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01192449536045164</v>
+        <v>0.02921694509660383</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003107281604186642</v>
+        <v>0.02924303383646496</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01632827272988695</v>
+        <v>0.02907584137816636</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01084603797643394</v>
+        <v>0.02924497136012546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01561126653778334</v>
+        <v>0.01920116188326454</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01220760844604424</v>
+        <v>0.03954131295628506</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02783777072219434</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.03429948172116126</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03446667488250332</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04194908291088661</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03429947093713017</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03444058543959861</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03446667417945942</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.03429948172116126</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.03446667417945942</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.03062586177830531</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03446667417945942</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01301487821921213</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01632827272988694</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01204337982147764</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01632827272988694</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01632827272988694</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01192449536045163</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.003107281604186616</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01632827272988694</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01084603797643394</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01561126653778333</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01220760844604423</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01583882002848023</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0171375202331842</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01544330620468003</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0171375202331842</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0171375202331842</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01537146500393719</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01181784750271856</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0171375202331842</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0149583845236355</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01689646522961174</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.008106591467124207</v>
+      <c r="B11" t="n">
+        <v>0.01583882002848022</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01713752023318419</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01544330620468001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01713752023318419</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01713752023318419</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01537146500393717</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01181784750271853</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01713752023318419</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01495838452363548</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01689646522961172</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.008106591467124192</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1774303745276819</v>
+        <v>0.01818173071782404</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09567154855820094</v>
+        <v>0.01797201763278891</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2564896721441022</v>
+        <v>0.01827856093100622</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09567154855820094</v>
+        <v>0.01797201763278891</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09567154855820094</v>
+        <v>0.01797201763278891</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2568097637464242</v>
+        <v>0.01823526770522914</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5957086622644435</v>
+        <v>0.01860436848651772</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09567154855820094</v>
+        <v>0.01797201763278891</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2486215197754174</v>
+        <v>0.01824848648988043</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1161748839000135</v>
+        <v>0.01811477496013728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3347929526472379</v>
+        <v>0.01833230851740103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006835208131330633</v>
+        <v>0.01839912629607383</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00608792906185533</v>
+        <v>0.01828287262598743</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006835208131330628</v>
+        <v>0.01839912629607383</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006260893544026586</v>
+        <v>0.01828287262598743</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006260893544026587</v>
+        <v>0.01828287262598743</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006811009695643132</v>
+        <v>0.01836229425329224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006835208131330628</v>
+        <v>0.01839912629607383</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006680242835001669</v>
+        <v>0.01828287262598743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006835208131330628</v>
+        <v>0.01839912629607383</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006835208131330628</v>
+        <v>0.01839912629607383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006835208131330628</v>
+        <v>0.01839912629607383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01077736902422674</v>
+        <v>0.1774303745276823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01028074988130887</v>
+        <v>0.0956715485582012</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01091977529491971</v>
+        <v>0.2564896721441023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009830170392009277</v>
+        <v>0.0956715485582012</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01058325054972301</v>
+        <v>0.0956715485582012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0107531705885392</v>
+        <v>0.2568097637464244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01845128697611773</v>
+        <v>0.5957086622644444</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01791425847420193</v>
+        <v>0.0956715485582012</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01121272884043814</v>
+        <v>0.2486215197754171</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01062474910446137</v>
+        <v>0.1161748839000135</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01103031717855166</v>
+        <v>0.3347929526472372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01143192842232787</v>
+        <v>0.006835208131330647</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01127696312599888</v>
+        <v>0.006087929061855324</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01143126554451479</v>
+        <v>0.006835208131330644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01126587497442955</v>
+        <v>0.006260893544026576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01126587497442955</v>
+        <v>0.006260893544026588</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01140772998664031</v>
+        <v>0.006811009695643101</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01143192842232787</v>
+        <v>0.006835208131330644</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01127696312599888</v>
+        <v>0.006680242835001658</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01143192842232787</v>
+        <v>0.006835208131330644</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01143192842232787</v>
+        <v>0.006835208131330644</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01143192842232787</v>
+        <v>0.006835208131330644</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01800105983813534</v>
+        <v>0.01077736902422674</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02681015863462875</v>
+        <v>0.01028074988130886</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02883356369905247</v>
+        <v>0.0109197752949197</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02435706131244217</v>
+        <v>0.009830170392009273</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01812427656436542</v>
+        <v>0.010583250549723</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02694894523341287</v>
+        <v>0.01075317058853923</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02697314366910187</v>
+        <v>0.01845128697611776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02681817837277145</v>
+        <v>0.01791425847420192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0269749069393383</v>
+        <v>0.01121272884043817</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01783439877480479</v>
+        <v>0.01062474910446136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03634523546279594</v>
+        <v>0.01103031717855167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02439150538428111</v>
+        <v>0.01143192842232783</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02990898011201973</v>
+        <v>0.01127696312599888</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03006394694605352</v>
+        <v>0.01143126554451478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03645484650108916</v>
+        <v>0.01126587497442955</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02990897170113852</v>
+        <v>0.01126587497442955</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03003974697266117</v>
+        <v>0.01140772998664034</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03006394540834874</v>
+        <v>0.01143192842232783</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02990898011201973</v>
+        <v>0.01127696312599888</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03006394540834874</v>
+        <v>0.01143192842232783</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02677731202776604</v>
+        <v>0.01143192842232783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03006394540834874</v>
+        <v>0.01143192842232783</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01415658409643564</v>
+        <v>0.01800105983813532</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01600155056878718</v>
+        <v>0.02681015863462874</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01213049806876919</v>
+        <v>0.02883356369905247</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01600155056878718</v>
+        <v>0.02435706131244214</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01600155056878718</v>
+        <v>0.01812427656436541</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01225585350590065</v>
+        <v>0.02694894523341287</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005548936987645458</v>
+        <v>0.02697314366910189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01600155056878718</v>
+        <v>0.02681817837277145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01280219226782458</v>
+        <v>0.02697490693933827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01556314208800613</v>
+        <v>0.01783439877480476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01111453795856696</v>
+        <v>0.03634523546279593</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02439150538428111</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02990898011201975</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03006394694605355</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03645484650108918</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02990897170113853</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03003974697266118</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03006394540834873</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02990898011201975</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.03006394540834873</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.026777312027766</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03006394540834873</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01415658409643563</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01600155056878719</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01213049806876918</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01600155056878719</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01600155056878719</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01225585350590065</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.005548936987645452</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01600155056878719</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01280219226782457</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01556314208800611</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01111453795856695</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01625136049680888</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01693400882662077</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01542631511064976</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01693400882662077</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01693400882662077</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01545681770509391</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0127574914000593</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01693400882662077</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01570186367065657</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01682439310772105</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.008761883053660671</v>
+      <c r="B11" t="n">
+        <v>0.01625136049680886</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01693400882662078</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01542631511064972</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01693400882662078</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01693400882662078</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01545681770509392</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01275749140005929</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01693400882662078</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01570186367065656</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01682439310772102</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.008761883053660637</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1486442751462755</v>
+        <v>0.01733738981764837</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1198356427697941</v>
+        <v>0.01675250278982809</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2077814287750752</v>
+        <v>0.01741272016578851</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1198356427697941</v>
+        <v>0.01675250278982809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1198356427697941</v>
+        <v>0.01675250278982809</v>
       </c>
       <c r="G2" t="n">
-        <v>0.217778805653631</v>
+        <v>0.01739142248570029</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4134816518931386</v>
+        <v>0.0176144251320385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1198356427697941</v>
+        <v>0.01675250278982809</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1621959267236876</v>
+        <v>0.01733632917107744</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09693985202474062</v>
+        <v>0.0172810784450711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.225194315713206</v>
+        <v>0.01815692168794758</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006217573401584203</v>
+        <v>0.01701123466668901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006382512115142887</v>
+        <v>0.01701123466668901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006382512115142884</v>
+        <v>0.01701123466668901</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006828681865320541</v>
+        <v>0.01754592731206549</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006707172617743452</v>
+        <v>0.01701123466668901</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006851130598088958</v>
+        <v>0.01757147359217524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01082078423171837</v>
+        <v>0.1486442751462753</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01045655167494516</v>
+        <v>0.1198356427697942</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01088151829783068</v>
+        <v>0.2077814287750751</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009999506167517205</v>
+        <v>0.1198356427697942</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01066999379658871</v>
+        <v>0.1198356427697942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0179392120772654</v>
+        <v>0.2177788056536304</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01831679567070513</v>
+        <v>0.4134816518931386</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0106768262513729</v>
+        <v>0.1198356427697942</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01797652996593504</v>
+        <v>0.1621959267236877</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01070574553140051</v>
+        <v>0.0969398520247408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0110927451811815</v>
+        <v>0.2251943157132072</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01130806557867218</v>
+        <v>0.0068511305980889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01116410759832671</v>
+        <v>0.0062175734015842</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01130740053172412</v>
+        <v>0.006851130598088898</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01115243260293484</v>
+        <v>0.006382512115142881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01115243260293484</v>
+        <v>0.006382512115142881</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01128561684590381</v>
+        <v>0.006828681865320545</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01130806557867217</v>
+        <v>0.006851130598088898</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01116410759832671</v>
+        <v>0.006707172617743448</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01130806557867217</v>
+        <v>0.006851130598088898</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01130806557867217</v>
+        <v>0.006851130598088898</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01130806557867217</v>
+        <v>0.006851130598088898</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01771734370458515</v>
+        <v>0.0108207842317184</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0263148853979868</v>
+        <v>0.010456551674945</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02828185414801128</v>
+        <v>0.01088151829783066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02392255258876731</v>
+        <v>0.009999506167517236</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0178441829457763</v>
+        <v>0.01066999379658871</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02644501170830846</v>
+        <v>0.0179392120772654</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02646746044107902</v>
+        <v>0.01831679567070517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02632350246073138</v>
+        <v>0.01067682625137275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0264691800884812</v>
+        <v>0.01797652996593503</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01755480579398677</v>
+        <v>0.01070574553140056</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03560768904406867</v>
+        <v>0.01109274518118152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02260556911960589</v>
+        <v>0.01130806557867221</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02762199179382339</v>
+        <v>0.01116410759832672</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0277659521103016</v>
+        <v>0.01130740053172414</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03357695615210962</v>
+        <v>0.01115243260293484</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02762198570490277</v>
+        <v>0.01115243260293484</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02774350104140044</v>
+        <v>0.01128561684590384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02776594977416879</v>
+        <v>0.01130806557867221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02762199179382339</v>
+        <v>0.01116410759832672</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02776594977416879</v>
+        <v>0.01130806557867221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02477600593910513</v>
+        <v>0.01130806557867221</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02776594977416879</v>
+        <v>0.01130806557867221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01393995873913702</v>
+        <v>0.01771734370458523</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0140566813723812</v>
+        <v>0.02631488539798684</v>
       </c>
       <c r="D8" t="n">
-        <v>0.012363923252805</v>
+        <v>0.02828185414801138</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0140566813723812</v>
+        <v>0.02392255258876729</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0140566813723812</v>
+        <v>0.0178441829457763</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01227253781414092</v>
+        <v>0.02644501170830846</v>
       </c>
       <c r="H8" t="n">
-        <v>0.008314051774868152</v>
+        <v>0.02646746044107905</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0140566813723812</v>
+        <v>0.02632350246073138</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01399088483075402</v>
+        <v>0.02646918008848122</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01512297878964878</v>
+        <v>0.0175548057939868</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002912223207905703</v>
+        <v>0.03560768904406876</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02260556911960592</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02762199179382341</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02776595211030165</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03357695615210964</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02762198570490278</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02774350104140052</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0277659497741689</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02762199179382341</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0277659497741689</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02477600593910518</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0277659497741689</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.013939958739137</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0140566813723812</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01236392325280498</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0140566813723812</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0140566813723812</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01227253781414093</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.008314051774868127</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0140566813723812</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01399088483075401</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01512297878964877</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.002912223207905722</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01568503898656482</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.01568503898656481</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01540817162531533</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.01504326816589678</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.01540817162531533</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01540817162531533</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01499201345884943</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.01499201345884942</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.01340226870351093</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.01540817162531533</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01570714987397142</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01616700550703159</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.008836774366242205</v>
+      <c r="J11" t="n">
+        <v>0.01570714987397143</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01616700550703158</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.008836774366242207</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05777764656677151</v>
+        <v>0.01738471543657951</v>
       </c>
       <c r="C2" t="n">
-        <v>0.05300955914536692</v>
+        <v>0.01739736323279744</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09171357731877844</v>
+        <v>0.01742823200426015</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05300955914536692</v>
+        <v>0.01739736323279744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05300955914536692</v>
+        <v>0.01739736323279744</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1140831256167156</v>
+        <v>0.01742982688039525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.242208623219436</v>
+        <v>0.01758555594966156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05300955914536692</v>
+        <v>0.01739736323279744</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2085323700656418</v>
+        <v>0.01753755854301214</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08859345426517279</v>
+        <v>0.0174223864952331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3006221624800975</v>
+        <v>0.01746579186151188</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005692137888009038</v>
+        <v>0.01776135244494266</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005876651308820691</v>
+        <v>0.01776135244494266</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005876651308820695</v>
+        <v>0.01776135244494266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006493052249563081</v>
+        <v>0.0177224153794035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006378043051102122</v>
+        <v>0.01776135244494266</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006514283297246286</v>
+        <v>0.01774197000588715</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01672143510734116</v>
+        <v>0.05777764656677117</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009698309706462876</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01682920653991103</v>
+        <v>0.09171357731877833</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009258992387161625</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009896495789342107</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01670020405965796</v>
+        <v>0.1140831256167157</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01011350097322564</v>
+        <v>0.2422086232194359</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01658519486119698</v>
+        <v>0.05300955914536695</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01682341969651331</v>
+        <v>0.2085323700656421</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009998124147940299</v>
+        <v>0.08859345426517273</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0101365369095957</v>
+        <v>0.3006221624800968</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.006514283297246274</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01064210613479131</v>
+        <v>0.005692137888009044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01077764625816932</v>
+        <v>0.006514283297246274</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01063267299386827</v>
+        <v>0.005876651308820699</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01063267299386827</v>
+        <v>0.005876651308820699</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01075711533325227</v>
+        <v>0.006493052249563084</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.00651428329724628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01064210613479131</v>
+        <v>0.006378043051102109</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.006514283297246274</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.006514283297246274</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01077834638093548</v>
+        <v>0.006514283297246274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01724745956465506</v>
+        <v>0.01672143510734115</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02581122743180733</v>
+        <v>0.009698309706462809</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02775924416854233</v>
+        <v>0.01682920653991104</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02343059776684552</v>
+        <v>0.009258992387161619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01738199055252116</v>
+        <v>0.009896495789342112</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02593267477260185</v>
+        <v>0.01670020405965796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02595390582028521</v>
+        <v>0.01011350097322565</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02581766557414088</v>
+        <v>0.01658519486119698</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02595561688542513</v>
+        <v>0.01682341969651331</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01708573285563038</v>
+        <v>0.009998124147940299</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03504851695456859</v>
+        <v>0.0101365369095957</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02278823969557127</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02797383967704005</v>
+        <v>0.01064210613479131</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02811008227367243</v>
+        <v>0.01077764625816933</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03411512787704463</v>
+        <v>0.01063267299386828</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02797383591206999</v>
+        <v>0.01063267299386828</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02808884887550105</v>
+        <v>0.01075711533325229</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02797383967704005</v>
+        <v>0.01064210613479131</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02502658578343235</v>
+        <v>0.01077834638093548</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02811007992318425</v>
+        <v>0.01077834638093548</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01655519313327904</v>
+        <v>0.01724745956465507</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01668880886496855</v>
+        <v>0.0258112274318073</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01564424996522457</v>
+        <v>0.02775924416854231</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01668880886496855</v>
+        <v>0.02343059776684551</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01668880886496855</v>
+        <v>0.01738199055252118</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01519276132541994</v>
+        <v>0.02593267477260185</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01244897464464121</v>
+        <v>0.02595390582028525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01668880886496855</v>
+        <v>0.02581766557414087</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01338646563238576</v>
+        <v>0.02595561688542517</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01576779930636939</v>
+        <v>0.01708573285563041</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0117603316980386</v>
+        <v>0.03504851695456855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02278823969557123</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02797383967704003</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02811008227367244</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03411512787704463</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02797383591206997</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02808884887550104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02811007992318423</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02797383967704003</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02811007992318423</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02502658578343234</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02811007992318423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01655519313327905</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01668880886496858</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01564424996522458</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01668880886496858</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01668880886496858</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01519276132541995</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01244897464464121</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01668880886496858</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01338646563238575</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0157677993063694</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01176033169803861</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01684472817750933</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01690935248591564</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01647376270072153</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01690935248591564</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01690935248591564</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.01684472817750934</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01690935248591565</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01647376270072155</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01690935248591565</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01690935248591565</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.01627882622430357</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.01517722619251927</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.01690935248591564</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01555579017290013</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01652413253564377</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.01489634808732652</v>
+      <c r="I11" t="n">
+        <v>0.01690935248591565</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01555579017290014</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01652413253564378</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.01489634808732654</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,320 +7651,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06211109992219609</v>
+        <v>0.01735233865842726</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07518351383021822</v>
+        <v>0.01739002533454933</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06125588512178417</v>
+        <v>0.01735619380205303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07518351383021822</v>
+        <v>0.01739002533454933</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07518351383021822</v>
+        <v>0.01739002533454933</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08735374863258155</v>
+        <v>0.0173761049392013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04470733885210876</v>
+        <v>0.01732934212360233</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07518351383021822</v>
+        <v>0.01739002533454933</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1569848479640743</v>
+        <v>0.01746411179105303</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09750887604861555</v>
+        <v>0.01740113093333411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04809896448050027</v>
+        <v>0.01733193777491666</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005726458914782736</v>
+        <v>0.01771885195275033</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005885029298118466</v>
+        <v>0.01771885195275033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005885029298118473</v>
+        <v>0.01771885195275033</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006311678267799289</v>
+        <v>0.01768933169929813</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006211407700532546</v>
+        <v>0.01771885195275033</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006330199977848967</v>
+        <v>0.01769987657038528</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01595977328055101</v>
+        <v>0.0621110999221961</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009662555930617833</v>
+        <v>0.07518351383021814</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00988348727367586</v>
+        <v>0.06125588512178411</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00922705537728658</v>
+        <v>0.07518351383021814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009775855600220151</v>
+        <v>0.07518351383021814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0159412515705013</v>
+        <v>0.08735374863258076</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01623805197279781</v>
+        <v>0.04470733885210876</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01584098100323457</v>
+        <v>0.07518351383021814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01029718166788824</v>
+        <v>0.1569848479640739</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009947232174158436</v>
+        <v>0.09750887604861551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009856272807822914</v>
+        <v>0.04809896448050022</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01015613296613779</v>
+        <v>0.006330199977848981</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01003734068882138</v>
+        <v>0.005726458914782732</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01015547461582262</v>
+        <v>0.006330199977848981</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01002887423747511</v>
+        <v>0.005885029298118461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01002887423747511</v>
+        <v>0.005885029298118462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01013761125608811</v>
+        <v>0.0063116782677993</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01015613296613779</v>
+        <v>0.006330199977848981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01003734068882138</v>
+        <v>0.006211407700532546</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01015613296613779</v>
+        <v>0.006330199977848981</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01015613296613779</v>
+        <v>0.006330199977848981</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01015613296613779</v>
+        <v>0.006330199977848981</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01602703644671294</v>
+        <v>0.015959773280551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02378042550252391</v>
+        <v>0.009662555930617787</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02553848719085041</v>
+        <v>0.009883487273675861</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02162633129047014</v>
+        <v>0.009227055377286578</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01615330396696869</v>
+        <v>0.009775855600220151</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02388642870060076</v>
+        <v>0.0159412515705013</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02390495041064913</v>
+        <v>0.0162380519727978</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02378615813333401</v>
+        <v>0.01584098100323456</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02390649864561933</v>
+        <v>0.01029718166788823</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01588070015036554</v>
+        <v>0.009947232174158429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03213409028566168</v>
+        <v>0.009856272807822903</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02022469164244701</v>
+        <v>0.0101561329661378</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02469566819537635</v>
+        <v>0.01003734068882137</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02481446457378962</v>
+        <v>0.01015547461582262</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02999216714106581</v>
+        <v>0.0100288742374751</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02469566765705633</v>
+        <v>0.0100288742374751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02479593876264311</v>
+        <v>0.01013761125608811</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.0101561329661378</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02469566819537635</v>
+        <v>0.01003734068882137</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.0101561329661378</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02215513211194076</v>
+        <v>0.0101561329661378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02481446047269279</v>
+        <v>0.0101561329661378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01632279811815221</v>
+        <v>0.01602703644671294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01593297184592379</v>
+        <v>0.02378042550252391</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01624280870050056</v>
+        <v>0.0255384871908504</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01593297184592379</v>
+        <v>0.02162633129047014</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01593297184592379</v>
+        <v>0.01615330396696868</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01560341242310701</v>
+        <v>0.02388642870060077</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01682208203455821</v>
+        <v>0.0239049504106491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01593297184592379</v>
+        <v>0.02378615813333398</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01400958404512797</v>
+        <v>0.0239064986456193</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01530277069021867</v>
+        <v>0.01588070015036553</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01676514303767644</v>
+        <v>0.03213409028566168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02022469164244699</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02469566819537629</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02481446457378958</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02999216714106577</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02469566765705627</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02479593876264304</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02481446047269276</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02469566819537629</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02481446047269276</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02215513211194073</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02481446047269276</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01632279811815222</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01593297184592378</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01624280870050058</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01593297184592378</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01593297184592378</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01560341242310702</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01682208203455822</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01593297184592378</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01400958404512798</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01530277069021867</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01676514303767645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01672576357417258</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01657744419468105</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01669322327785567</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01657744419468105</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01657744419468105</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01642700502110404</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01692994281243581</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01657744419468105</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01578501693179646</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01631044011873512</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>0.01672576357417259</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01657744419468104</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01669322327785568</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01657744419468104</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01657744419468104</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01642700502110403</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01692994281243582</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01657744419468104</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01578501693179648</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01631044011873511</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.01690663103871511</v>
       </c>
     </row>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09571661922626896</v>
+        <v>0.01668357745278292</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08448659935808743</v>
+        <v>0.01615824102908486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04612730253318384</v>
+        <v>0.01662360286900165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08448659935808743</v>
+        <v>0.01615824102908486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08448659935808743</v>
+        <v>0.01615824102908486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08329153802561577</v>
+        <v>0.01666080846586314</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04125026386576722</v>
+        <v>0.01661287021129066</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08448659935808743</v>
+        <v>0.01615824102908486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1376689234589979</v>
+        <v>0.0167276782267083</v>
       </c>
       <c r="K2" t="n">
-        <v>0.08921748421698543</v>
+        <v>0.01668206970116282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06691660886201162</v>
+        <v>0.01664234101831347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005818423239062585</v>
+        <v>0.01645706978034476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005971679511946064</v>
+        <v>0.01645706978034476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005971679511946065</v>
+        <v>0.01645706978034476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006330141299112434</v>
+        <v>0.01697028408450098</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006228878010932407</v>
+        <v>0.01645706978034476</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006348811740034472</v>
+        <v>0.01697797986478441</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01003040324760105</v>
+        <v>0.09571661922626895</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009788857697305657</v>
+        <v>0.08448659935808751</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009903372253542262</v>
+        <v>0.04612730253318376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00934546160465234</v>
+        <v>0.08448659935808751</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009878024488260381</v>
+        <v>0.08448659935808751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01001173280667902</v>
+        <v>0.08329153802561617</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01633782658345228</v>
+        <v>0.04125026386576724</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009910469518498978</v>
+        <v>0.08448659935808751</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01038667216976504</v>
+        <v>0.137668923458998</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01005305943748742</v>
+        <v>0.08921748421698557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009994568346965332</v>
+        <v>0.06691660886201163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01013018487118383</v>
+        <v>0.006348811740034456</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01001025114208175</v>
+        <v>0.005818423239062582</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01012952430386275</v>
+        <v>0.006348811740034456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0100015774769322</v>
+        <v>0.00597167951194606</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0100015774769322</v>
+        <v>0.005971679511946061</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01011151443026177</v>
+        <v>0.006330141299112418</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01013018487118383</v>
+        <v>0.006348811740034456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01001025114208175</v>
+        <v>0.0062288780109324</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01013018487118383</v>
+        <v>0.006348811740034456</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01013018487118383</v>
+        <v>0.006348811740034456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01013018487118383</v>
+        <v>0.006348811740034456</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01595893556384975</v>
+        <v>0.01003040324760106</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0236455483697764</v>
+        <v>0.009788857697305682</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02539138749015338</v>
+        <v>0.009903372253542262</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0215093658437864</v>
+        <v>0.009345461604652423</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01608186527288933</v>
+        <v>0.009878024488260374</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02375274786013482</v>
+        <v>0.01001173280667901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02377141830105511</v>
+        <v>0.01633782658345226</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02365148457195479</v>
+        <v>0.00991046951849898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02377295367697329</v>
+        <v>0.01038667216976501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01581381468612526</v>
+        <v>0.01005305943748738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03193220978853388</v>
+        <v>0.009994568346965322</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01920370633677833</v>
+        <v>0.0101301848711838</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02338153752671158</v>
+        <v>0.01001025114208175</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0235014750692808</v>
+        <v>0.01012952430386273</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02834106998983688</v>
+        <v>0.0100015774769322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02338153706799212</v>
+        <v>0.0100015774769322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02348280081489162</v>
+        <v>0.01011151443026177</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02350147125581367</v>
+        <v>0.0101301848711838</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02338153752671158</v>
+        <v>0.01001025114208175</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02350147125581367</v>
+        <v>0.0101301848711838</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02091030269608883</v>
+        <v>0.0101301848711838</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02350147125581367</v>
+        <v>0.0101301848711838</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01472504082873558</v>
+        <v>0.01595893556384973</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01446062513950028</v>
+        <v>0.02364554836977641</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01598267636968187</v>
+        <v>0.02539138749015335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01446062513950028</v>
+        <v>0.02150936584378641</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01446062513950028</v>
+        <v>0.01608186527288933</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01504282129472916</v>
+        <v>0.02375274786013479</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01622197183521583</v>
+        <v>0.02377141830105504</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01446062513950028</v>
+        <v>0.02365148457195485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01382594598510546</v>
+        <v>0.02377295367697329</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0147591127068769</v>
+        <v>0.01581381468612526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01632415054455105</v>
+        <v>0.03193220978853382</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.01920370633677835</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02338153752671161</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02350147506928081</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02834106998983692</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02338153706799215</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02348280081489164</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02350147125581368</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02338153752671161</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02350147125581367</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02091030269608883</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02350147125581367</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01472504082873557</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01446062513950029</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01598267636968186</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01446062513950029</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01446062513950029</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01504282129472915</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01622197183521581</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01446062513950029</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01382594598510545</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0147591127068769</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01632415054455105</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01565848301169002</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.01565848301169</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.01524985235520903</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.016170736606886</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.01617073660688599</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.01524985235520903</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.01524985235520903</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.01578380675405749</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01626888414858233</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.01578380675405748</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01626888414858231</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.01524985235520903</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.01529349276651843</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.01529349276651841</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01567247807320486</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.0163102908602084</v>
+      <c r="L11" t="n">
+        <v>0.01631029086020839</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1534878398514368</v>
+        <v>0.01802902955905733</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08220904438191995</v>
+        <v>0.0178622728455517</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2641006983932203</v>
+        <v>0.01815899681002931</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08220904438191995</v>
+        <v>0.0178622728455517</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08220904438191995</v>
+        <v>0.0178622728455517</v>
       </c>
       <c r="G2" t="n">
-        <v>0.25567273008495</v>
+        <v>0.01810109490731977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6857262642249897</v>
+        <v>0.01859682021593141</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08220904438191995</v>
+        <v>0.0178622728455517</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2475036427026193</v>
+        <v>0.01811334506599499</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1264406264832021</v>
+        <v>0.01799701620019055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2225906508229461</v>
+        <v>0.01889168641378116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006023630834756185</v>
+        <v>0.01819721880334429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006217574446497114</v>
+        <v>0.01819721880334429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006217574446497094</v>
+        <v>0.01819721880334429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006921139261006521</v>
+        <v>0.01824422445137611</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006784113615635036</v>
+        <v>0.01819721880334429</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006946466718419799</v>
+        <v>0.01828256848074328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01083275234754193</v>
+        <v>0.1534878398514366</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0102745191316778</v>
+        <v>0.08220904438191931</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01100809176863988</v>
+        <v>0.2641006983932206</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0098224212069782</v>
+        <v>0.08220904438191931</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01061670707978579</v>
+        <v>0.08220904438191931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01844228721766851</v>
+        <v>0.2556727300849506</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01903247796293354</v>
+        <v>0.6857262642249897</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01830526157229703</v>
+        <v>0.08220904438191931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01859552779040556</v>
+        <v>0.2475036427026192</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01063064228304784</v>
+        <v>0.1264406264832022</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01112029465798978</v>
+        <v>0.2225906508229478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0118147978487514</v>
+        <v>0.006946466718419785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01165244474596664</v>
+        <v>0.006023630834756166</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01181409113246686</v>
+        <v>0.006946466718419785</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01164259189794135</v>
+        <v>0.006217574446497098</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01164259189794135</v>
+        <v>0.006217574446497101</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0117894703913381</v>
+        <v>0.006921139261006516</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0118147978487514</v>
+        <v>0.006946466718419785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01165244474596664</v>
+        <v>0.006784113615635016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0118147978487514</v>
+        <v>0.006946466718419785</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0118147978487514</v>
+        <v>0.006946466718419785</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0118147978487514</v>
+        <v>0.006946466718419785</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01882497275480006</v>
+        <v>0.01083275234754194</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02821319769038428</v>
+        <v>0.01027451913167776</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03036397227600434</v>
+        <v>0.01100809176863989</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02559990610179745</v>
+        <v>0.009822421206978139</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01896011338503144</v>
+        <v>0.01061670707978577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02835688823576078</v>
+        <v>0.0184422872176685</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02838221569317525</v>
+        <v>0.01903247796293359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02821986259038925</v>
+        <v>0.01830526157229701</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02838409396393608</v>
+        <v>0.01859552779040556</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01864744206062426</v>
+        <v>0.0106306422830478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0383655551047592</v>
+        <v>0.0111202946579898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02675646139488918</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03294742574841936</v>
+        <v>0.01165244474596663</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03310977883081186</v>
+        <v>0.01181409113246687</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04027900626752159</v>
+        <v>0.01164259189794137</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03294741527244997</v>
+        <v>0.01164259189794137</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03308445139379076</v>
+        <v>0.01178947039133811</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03310977885120421</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03294742574841936</v>
+        <v>0.01165244474596663</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03310977885120421</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02942864175703578</v>
+        <v>0.0118147978487514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03310977885120421</v>
+        <v>0.0118147978487514</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01481744814277613</v>
+        <v>0.01882497275480005</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01642818812970991</v>
+        <v>0.0282131976903843</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01209675814120392</v>
+        <v>0.03036397227600441</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01642818812970991</v>
+        <v>0.02559990610179744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01642818812970991</v>
+        <v>0.01896011338503143</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01249339866725565</v>
+        <v>0.02835688823576075</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003210724909880797</v>
+        <v>0.02838221569317525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01642818812970991</v>
+        <v>0.02821986259038929</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01309175325110724</v>
+        <v>0.02838409396393602</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01549155765742371</v>
+        <v>0.01864744206062426</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.002927113009827051</v>
+        <v>0.03836555510475925</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02675646139488922</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.03294742574841936</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03310977883081189</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04027900626752161</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03294741527245001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03308445139379082</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.03310977885120413</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.03294742574841936</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.03310977885120413</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02942864175703582</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03310977885120413</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01481744814277612</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0164281881297099</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0120967581412039</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0164281881297099</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0164281881297099</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01249339866725565</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.003210724909880775</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0164281881297099</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.01309175325110724</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01549155765742369</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.002927113009827091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01645238876259895</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0170573582514818</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.01534443339253097</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0170573582514818</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0170573582514818</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0154844508487506</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.01173908336007336</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0170573582514818</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.01645238876259896</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01705735825148179</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01534443339253098</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01705735825148179</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01705735825148179</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01548445084875058</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01173908336007339</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01705735825148179</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.01575150759436396</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.01672709738115637</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.01607114857218254</v>
+      <c r="L11" t="n">
+        <v>0.01607114857218255</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,320 +9079,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03667350620756223</v>
+        <v>0.01752873511369942</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06082485173358167</v>
+        <v>0.0174960346573499</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2219569749899299</v>
+        <v>0.01777082726221792</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06082485173358167</v>
+        <v>0.0174960346573499</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06082485173358167</v>
+        <v>0.0174960346573499</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1588652974792442</v>
+        <v>0.01765310884452163</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1013099793809689</v>
+        <v>0.01760236091371511</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06082485173358167</v>
+        <v>0.0174960346573499</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1766579140926514</v>
+        <v>0.01768327279076294</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05636705571802667</v>
+        <v>0.01755494249660935</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5938535837851517</v>
+        <v>0.01756372593898204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005764919539658978</v>
+        <v>0.01784556601264246</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00593047363766146</v>
+        <v>0.01784556601264246</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005930473637661457</v>
+        <v>0.01784556601264246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006434611436784756</v>
+        <v>0.01788204578823068</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006315982616431848</v>
+        <v>0.01784556601264246</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006456549770878647</v>
+        <v>0.01790893563741221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.016723559204366</v>
+        <v>0.03667350620756219</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009721800302615517</v>
+        <v>0.06082485173358165</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01036945338677202</v>
+        <v>0.2219569749899296</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009284522403174284</v>
+        <v>0.06082485173358165</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009947081061235808</v>
+        <v>0.06082485173358165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01670162087027212</v>
+        <v>0.1588652974792444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01704307279128358</v>
+        <v>0.1013099793809689</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01658299204991921</v>
+        <v>0.06082485173358165</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0105224289492522</v>
+        <v>0.1766579140926516</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009986769853961425</v>
+        <v>0.05636705571802666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01024309775679527</v>
+        <v>0.5938535837851505</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01057355664955254</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01043298949510574</v>
+        <v>0.005764919539658997</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01057289860157947</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01042305497707063</v>
+        <v>0.00593047363766146</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01042305497707063</v>
+        <v>0.005930473637661464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01055161831545864</v>
+        <v>0.006434611436784761</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01057355664955254</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01043298949510574</v>
+        <v>0.006315982616431858</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01057355664955254</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01057355664955254</v>
+        <v>0.006456549770878647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01057355664955254</v>
+        <v>0.006456549770878647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01676004885832682</v>
+        <v>0.01672355920436599</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02494207484732294</v>
+        <v>0.009721800302615448</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02681689558236895</v>
+        <v>0.01036945338677202</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02266457716610808</v>
+        <v>0.009284522403174282</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01687798460820278</v>
+        <v>0.00994708106123582</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02506775185569789</v>
+        <v>0.01670162087027211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02508969018979101</v>
+        <v>0.01704307279128362</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02494912303534499</v>
+        <v>0.01658299204991921</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02509132720194602</v>
+        <v>0.0105224289492522</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01660532149422982</v>
+        <v>0.009986769853961438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03379069707284481</v>
+        <v>0.01024309775679526</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02186190842324577</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02675778703371955</v>
+        <v>0.01043298949510573</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02689835960689413</v>
+        <v>0.01057289860157947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03256974118757734</v>
+        <v>0.01042305497707066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02675778513981857</v>
+        <v>0.01042305497707066</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02687641585407244</v>
+        <v>0.01055161831545866</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02689835418816636</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02675778703371955</v>
+        <v>0.01043298949510573</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02689835418816636</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02398022001141849</v>
+        <v>0.01057355664955254</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02689835418816636</v>
+        <v>0.01057355664955254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01718431818131128</v>
+        <v>0.01676004885832685</v>
       </c>
       <c r="C8" t="n">
-        <v>0.016471472682267</v>
+        <v>0.02494207484732304</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01211325435319015</v>
+        <v>0.02681689558236902</v>
       </c>
       <c r="E8" t="n">
-        <v>0.016471472682267</v>
+        <v>0.02266457716610815</v>
       </c>
       <c r="F8" t="n">
-        <v>0.016471472682267</v>
+        <v>0.01687798460820285</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01400612823544512</v>
+        <v>0.02506775185569798</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01568466055491712</v>
+        <v>0.0250896901897911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.016471472682267</v>
+        <v>0.02494912303534506</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01397668839165649</v>
+        <v>0.02509132720194612</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01663642694961522</v>
+        <v>0.01660532149422988</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0052115359851271</v>
+        <v>0.03379069707284495</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02186190842324574</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.02675778703371951</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02689835960689407</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03256974118757729</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02675778513981852</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.02687641585407246</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02689835418816631</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02675778703371951</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.02689835418816631</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.02398022001141851</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.02689835418816631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0171843181813113</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01647147268226701</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01211325435319017</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01647147268226701</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.01647147268226701</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01400612823544516</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01568466055491713</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01647147268226701</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0139766883916565</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01663642694961524</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.005211535985127123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01719903186195466</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.01687081781305344</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.0151337738081565</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01687081781305344</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01687081781305344</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.01588955400618785</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>0.01719903186195468</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01687081781305345</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01513377380815652</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01687081781305345</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01687081781305345</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01588955400618786</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.01659030866283574</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.01687081781305344</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.01589408776261564</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I11" t="n">
+        <v>0.01687081781305345</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.01589408776261565</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01697594698841715</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>0.0123322175363578</v>
       </c>
     </row>
